--- a/ProjectManagement/Checklist.xlsx
+++ b/ProjectManagement/Checklist.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28025"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7E78E06-F8D7-40F8-A963-0154E943A1F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="165" windowWidth="14805" windowHeight="7950"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Checklist" sheetId="1" r:id="rId1"/>
@@ -15,7 +16,7 @@
   <externalReferences>
     <externalReference r:id="rId5"/>
   </externalReferences>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -70,9 +71,6 @@
     <t>Resulting objects</t>
   </si>
   <si>
-    <t>Object Detection with Jetson Nano integrated in a Kuka KR6</t>
-  </si>
-  <si>
     <t>Name, Vorname</t>
   </si>
   <si>
@@ -82,9 +80,6 @@
     <t>Matr.-Nr</t>
   </si>
   <si>
-    <t>&lt;1234567&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">      Projektpartner</t>
   </si>
   <si>
@@ -431,12 +426,18 @@
   </si>
   <si>
     <t>10 th weeek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tawar Ranjeetsing </t>
+  </si>
+  <si>
+    <t>ML24-03 Car Licence Plate Identification with a Jetson Nano</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1015,7 +1016,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1180,17 +1181,13 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" textRotation="180"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
@@ -1198,15 +1195,24 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="180"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFCCFFCC"/>
+      <color rgb="FFCCFF99"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1235,7 +1241,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="Rectangle 26" descr="10%"/>
+        <xdr:cNvPr id="2" name="Rectangle 26" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1283,7 +1295,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Text Box 11"/>
+        <xdr:cNvPr id="3" name="Text Box 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1333,7 +1351,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="Text Box 12"/>
+        <xdr:cNvPr id="4" name="Text Box 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1404,7 +1428,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="Line 1"/>
+        <xdr:cNvPr id="5" name="Line 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeShapeType="1"/>
         </xdr:cNvSpPr>
@@ -1452,7 +1482,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="Line 2"/>
+        <xdr:cNvPr id="6" name="Line 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeShapeType="1"/>
         </xdr:cNvSpPr>
@@ -1500,7 +1536,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="AutoShape 3"/>
+        <xdr:cNvPr id="7" name="AutoShape 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1545,7 +1587,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="AutoShape 4"/>
+        <xdr:cNvPr id="8" name="AutoShape 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1590,7 +1638,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="AutoShape 5"/>
+        <xdr:cNvPr id="9" name="AutoShape 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1635,7 +1689,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="AutoShape 6"/>
+        <xdr:cNvPr id="10" name="AutoShape 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1680,7 +1740,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="AutoShape 7"/>
+        <xdr:cNvPr id="11" name="AutoShape 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1725,7 +1791,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="Text Box 9"/>
+        <xdr:cNvPr id="12" name="Text Box 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1775,7 +1847,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="Text Box 10"/>
+        <xdr:cNvPr id="13" name="Text Box 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1825,7 +1903,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="14" name="Text Box 13"/>
+        <xdr:cNvPr id="14" name="Text Box 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1896,7 +1980,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="15" name="Rectangle 14" descr="10%"/>
+        <xdr:cNvPr id="15" name="Rectangle 14" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1944,7 +2034,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="16" name="Rectangle 15" descr="10%"/>
+        <xdr:cNvPr id="16" name="Rectangle 15" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000010000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1992,22 +2088,34 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="17" name="Group 21"/>
+        <xdr:cNvPr id="17" name="Group 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000011000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGrpSpPr>
           <a:grpSpLocks/>
         </xdr:cNvGrpSpPr>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="8115300" y="5038725"/>
-          <a:ext cx="1838325" cy="190500"/>
+          <a:off x="8420100" y="4846320"/>
+          <a:ext cx="1929765" cy="182880"/>
           <a:chOff x="691" y="481"/>
           <a:chExt cx="144" cy="27"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="18" name="Rectangle 16" descr="10%"/>
+          <xdr:cNvPr id="18" name="Rectangle 16" descr="10%">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000012000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr>
             <a:spLocks noChangeArrowheads="1"/>
           </xdr:cNvSpPr>
@@ -2040,7 +2148,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="19" name="Rectangle 17" descr="10%"/>
+          <xdr:cNvPr id="19" name="Rectangle 17" descr="10%">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000013000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr>
             <a:spLocks noChangeArrowheads="1"/>
           </xdr:cNvSpPr>
@@ -2073,7 +2187,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="20" name="Freeform 19"/>
+          <xdr:cNvPr id="20" name="Freeform 19">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000014000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr>
             <a:spLocks/>
           </xdr:cNvSpPr>
@@ -2150,7 +2270,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="21" name="Freeform 20"/>
+          <xdr:cNvPr id="21" name="Freeform 20">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000015000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr>
             <a:spLocks/>
           </xdr:cNvSpPr>
@@ -2243,7 +2369,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="22" name="Rectangle 22"/>
+        <xdr:cNvPr id="22" name="Rectangle 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000016000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2286,7 +2418,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="23" name="Text Box 23"/>
+        <xdr:cNvPr id="23" name="Text Box 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000017000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2382,7 +2520,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="24" name="Text Box 24"/>
+        <xdr:cNvPr id="24" name="Text Box 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000018000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2446,7 +2590,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="25" name="AutoShape 27"/>
+        <xdr:cNvPr id="25" name="AutoShape 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000019000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2513,7 +2663,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="26" name="AutoShape 28"/>
+        <xdr:cNvPr id="26" name="AutoShape 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2595,7 +2751,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="27" name="AutoShape 29"/>
+        <xdr:cNvPr id="27" name="AutoShape 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2677,7 +2839,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="28" name="AutoShape 30"/>
+        <xdr:cNvPr id="28" name="AutoShape 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2744,7 +2912,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="29" name="AutoShape 31"/>
+        <xdr:cNvPr id="29" name="AutoShape 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2811,7 +2985,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="30" name="AutoShape 32"/>
+        <xdr:cNvPr id="30" name="AutoShape 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2878,7 +3058,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="31" name="AutoShape 33"/>
+        <xdr:cNvPr id="31" name="AutoShape 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2960,7 +3146,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="32" name="AutoShape 34"/>
+        <xdr:cNvPr id="32" name="AutoShape 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000020000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3042,7 +3234,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="33" name="AutoShape 35"/>
+        <xdr:cNvPr id="33" name="AutoShape 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000021000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3109,7 +3307,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="34" name="AutoShape 36"/>
+        <xdr:cNvPr id="34" name="AutoShape 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000022000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3201,7 +3405,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="35" name="AutoShape 37"/>
+        <xdr:cNvPr id="35" name="AutoShape 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000023000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3268,7 +3478,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="36" name="AutoShape 38"/>
+        <xdr:cNvPr id="36" name="AutoShape 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000024000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3313,7 +3529,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="37" name="AutoShape 39"/>
+        <xdr:cNvPr id="37" name="AutoShape 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000025000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3380,7 +3602,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="38" name="AutoShape 40"/>
+        <xdr:cNvPr id="38" name="AutoShape 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000026000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3447,7 +3675,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="39" name="AutoShape 41"/>
+        <xdr:cNvPr id="39" name="AutoShape 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000027000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3539,7 +3773,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="40" name="AutoShape 42"/>
+        <xdr:cNvPr id="40" name="AutoShape 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000028000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3606,7 +3846,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="41" name="Text Box 44"/>
+        <xdr:cNvPr id="41" name="Text Box 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000029000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3702,7 +3948,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="42" name="AutoShape 45"/>
+        <xdr:cNvPr id="42" name="AutoShape 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00002A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3784,7 +4036,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="43" name="AutoShape 46"/>
+        <xdr:cNvPr id="43" name="AutoShape 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00002B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3851,7 +4109,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="44" name="AutoShape 47"/>
+        <xdr:cNvPr id="44" name="AutoShape 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00002C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3918,7 +4182,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="45" name="AutoShape 48"/>
+        <xdr:cNvPr id="45" name="AutoShape 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00002D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3985,7 +4255,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="46" name="AutoShape 49"/>
+        <xdr:cNvPr id="46" name="AutoShape 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00002E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4052,7 +4328,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="47" name="AutoShape 50"/>
+        <xdr:cNvPr id="47" name="AutoShape 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00002F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4119,7 +4401,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="48" name="AutoShape 51"/>
+        <xdr:cNvPr id="48" name="AutoShape 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000030000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4186,7 +4474,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="49" name="AutoShape 52"/>
+        <xdr:cNvPr id="49" name="AutoShape 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000031000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4253,7 +4547,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="50" name="AutoShape 53"/>
+        <xdr:cNvPr id="50" name="AutoShape 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000032000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4320,7 +4620,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="51" name="AutoShape 54"/>
+        <xdr:cNvPr id="51" name="AutoShape 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000033000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4387,7 +4693,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="52" name="AutoShape 55"/>
+        <xdr:cNvPr id="52" name="AutoShape 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000034000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4454,7 +4766,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="53" name="AutoShape 56"/>
+        <xdr:cNvPr id="53" name="AutoShape 56">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000035000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4521,7 +4839,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="54" name="AutoShape 57"/>
+        <xdr:cNvPr id="54" name="AutoShape 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000036000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4588,7 +4912,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="55" name="AutoShape 58"/>
+        <xdr:cNvPr id="55" name="AutoShape 58">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000037000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4655,7 +4985,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="56" name="AutoShape 59"/>
+        <xdr:cNvPr id="56" name="AutoShape 59">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000038000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4727,7 +5063,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="Rectangle 1" descr="10%"/>
+        <xdr:cNvPr id="2" name="Rectangle 1" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4775,7 +5117,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Text Box 2"/>
+        <xdr:cNvPr id="3" name="Text Box 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4825,7 +5173,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="Text Box 3"/>
+        <xdr:cNvPr id="4" name="Text Box 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4896,7 +5250,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="Line 4"/>
+        <xdr:cNvPr id="5" name="Line 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeShapeType="1"/>
         </xdr:cNvSpPr>
@@ -4944,7 +5304,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="Line 5"/>
+        <xdr:cNvPr id="6" name="Line 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeShapeType="1"/>
         </xdr:cNvSpPr>
@@ -4992,7 +5358,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="AutoShape 6"/>
+        <xdr:cNvPr id="7" name="AutoShape 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5037,7 +5409,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="AutoShape 7"/>
+        <xdr:cNvPr id="8" name="AutoShape 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5082,7 +5460,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="AutoShape 8"/>
+        <xdr:cNvPr id="9" name="AutoShape 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5127,7 +5511,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="AutoShape 9"/>
+        <xdr:cNvPr id="10" name="AutoShape 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5172,7 +5562,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="AutoShape 10"/>
+        <xdr:cNvPr id="11" name="AutoShape 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5217,7 +5613,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="Text Box 11"/>
+        <xdr:cNvPr id="12" name="Text Box 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00000C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5267,7 +5669,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="Text Box 12"/>
+        <xdr:cNvPr id="13" name="Text Box 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5317,7 +5725,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="14" name="Text Box 13"/>
+        <xdr:cNvPr id="14" name="Text Box 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00000E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5388,7 +5802,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="15" name="Rectangle 14" descr="10%"/>
+        <xdr:cNvPr id="15" name="Rectangle 14" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00000F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5436,7 +5856,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="16" name="Rectangle 15" descr="10%"/>
+        <xdr:cNvPr id="16" name="Rectangle 15" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000010000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5484,22 +5910,34 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="17" name="Group 16"/>
+        <xdr:cNvPr id="17" name="Group 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000011000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGrpSpPr>
           <a:grpSpLocks/>
         </xdr:cNvGrpSpPr>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="8115300" y="5038725"/>
-          <a:ext cx="1838325" cy="190500"/>
+          <a:off x="8976360" y="4846320"/>
+          <a:ext cx="1929765" cy="182880"/>
           <a:chOff x="691" y="481"/>
           <a:chExt cx="144" cy="27"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="18" name="Rectangle 17" descr="10%"/>
+          <xdr:cNvPr id="18" name="Rectangle 17" descr="10%">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000012000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr>
             <a:spLocks noChangeArrowheads="1"/>
           </xdr:cNvSpPr>
@@ -5532,7 +5970,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="19" name="Rectangle 18" descr="10%"/>
+          <xdr:cNvPr id="19" name="Rectangle 18" descr="10%">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000013000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr>
             <a:spLocks noChangeArrowheads="1"/>
           </xdr:cNvSpPr>
@@ -5565,7 +6009,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="20" name="Freeform 19"/>
+          <xdr:cNvPr id="20" name="Freeform 19">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000014000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr>
             <a:spLocks/>
           </xdr:cNvSpPr>
@@ -5642,7 +6092,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="21" name="Freeform 20"/>
+          <xdr:cNvPr id="21" name="Freeform 20">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000015000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr>
             <a:spLocks/>
           </xdr:cNvSpPr>
@@ -5735,7 +6191,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="22" name="Rectangle 21"/>
+        <xdr:cNvPr id="22" name="Rectangle 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000016000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5765,95 +6227,111 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>7619</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>885825</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="23" name="Text Box 22"/>
+        <xdr:cNvPr id="23" name="Text Box 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000017000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="66675" y="1085850"/>
-          <a:ext cx="1257300" cy="476250"/>
+          <a:off x="800099" y="1089660"/>
+          <a:ext cx="1341121" cy="617220"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="9"/>
+          <a:schemeClr val="accent3">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
         </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-          </a:solidFill>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
       </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="ctr">
+          <a:noAutofit/>
+        </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr algn="ctr" rtl="0">
+          <a:pPr marL="0" indent="0" algn="ctr" rtl="0">
             <a:defRPr sz="1000"/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="de-DE" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="de-DE" sz="1100">
               <a:solidFill>
-                <a:srgbClr val="000000"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:ea typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>Hermann Meyer</a:t>
+            <a:t>Ranjeetsing Tawar</a:t>
           </a:r>
         </a:p>
         <a:p>
-          <a:pPr algn="ctr" rtl="0">
+          <a:pPr marL="0" indent="0" algn="ctr" rtl="0">
             <a:defRPr sz="1000"/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="de-DE" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="de-DE" sz="1100">
               <a:solidFill>
-                <a:srgbClr val="000000"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:ea typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>Matr.-Nr.   1112569</a:t>
+            <a:t>Matr.-Nr.   7026116</a:t>
           </a:r>
         </a:p>
         <a:p>
-          <a:pPr algn="ctr" rtl="0">
+          <a:pPr marL="0" indent="0" algn="ctr" rtl="0">
             <a:defRPr sz="1000"/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="de-DE" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="de-DE" sz="1100">
               <a:solidFill>
-                <a:srgbClr val="000000"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:ea typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>7. Sem   PVT</a:t>
+            <a:t>1. Sem   MBIDA</a:t>
           </a:r>
-          <a:endParaRPr lang="de-DE"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -5874,7 +6352,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="24" name="Text Box 23"/>
+        <xdr:cNvPr id="24" name="Text Box 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000018000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5925,73 +6409,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>914400</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="25" name="AutoShape 24"/>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1352550" y="666750"/>
-          <a:ext cx="1590675" cy="295275"/>
-        </a:xfrm>
-        <a:prstGeom prst="wedgeRoundRectCallout">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val -57736"/>
-            <a:gd name="adj2" fmla="val 114514"/>
-            <a:gd name="adj3" fmla="val 16667"/>
-          </a:avLst>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="9"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-          </a:solidFill>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="27432" bIns="22860" anchor="ctr" upright="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="de-DE" sz="800" b="0" i="1" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
-            </a:rPr>
-            <a:t>Personal Data</a:t>
-          </a:r>
-          <a:endParaRPr lang="de-DE"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
       <xdr:row>3</xdr:row>
@@ -6005,7 +6422,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="26" name="AutoShape 25"/>
+        <xdr:cNvPr id="26" name="AutoShape 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00001A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6087,7 +6510,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="27" name="AutoShape 26"/>
+        <xdr:cNvPr id="27" name="AutoShape 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00001B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6169,7 +6598,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="28" name="AutoShape 27"/>
+        <xdr:cNvPr id="28" name="AutoShape 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00001C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6236,7 +6671,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="29" name="AutoShape 28"/>
+        <xdr:cNvPr id="29" name="AutoShape 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00001D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6290,73 +6731,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1219200</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="30" name="AutoShape 29"/>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1657350" y="1162050"/>
-          <a:ext cx="1790700" cy="381000"/>
-        </a:xfrm>
-        <a:prstGeom prst="wedgeRoundRectCallout">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val 75926"/>
-            <a:gd name="adj2" fmla="val 183333"/>
-            <a:gd name="adj3" fmla="val 16667"/>
-          </a:avLst>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="9"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-          </a:solidFill>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="27432" bIns="22860" anchor="ctr" upright="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="de-DE" sz="800" b="0" i="1" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
-            </a:rPr>
-            <a:t>Weeks since start of project =&gt; duration</a:t>
-          </a:r>
-          <a:endParaRPr lang="de-DE"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>381000</xdr:colOff>
       <xdr:row>19</xdr:row>
@@ -6370,7 +6744,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="31" name="AutoShape 30"/>
+        <xdr:cNvPr id="31" name="AutoShape 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00001F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6452,7 +6832,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="32" name="AutoShape 31"/>
+        <xdr:cNvPr id="32" name="AutoShape 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000020000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6519,7 +6905,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="33" name="AutoShape 32"/>
+        <xdr:cNvPr id="33" name="AutoShape 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000021000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6586,7 +6978,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="34" name="AutoShape 33"/>
+        <xdr:cNvPr id="34" name="AutoShape 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000022000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6668,7 +7066,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="35" name="AutoShape 34"/>
+        <xdr:cNvPr id="35" name="AutoShape 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000023000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6750,7 +7154,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="36" name="AutoShape 35"/>
+        <xdr:cNvPr id="36" name="AutoShape 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000024000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6795,7 +7205,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="37" name="AutoShape 36"/>
+        <xdr:cNvPr id="37" name="AutoShape 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000025000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6862,7 +7278,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="38" name="AutoShape 37"/>
+        <xdr:cNvPr id="38" name="AutoShape 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000026000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6929,7 +7351,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="39" name="AutoShape 38"/>
+        <xdr:cNvPr id="39" name="AutoShape 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000027000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7026,7 +7454,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="40" name="AutoShape 39"/>
+        <xdr:cNvPr id="40" name="AutoShape 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000028000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7093,7 +7527,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="41" name="Text Box 40"/>
+        <xdr:cNvPr id="41" name="Text Box 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000029000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7189,7 +7629,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="42" name="AutoShape 41"/>
+        <xdr:cNvPr id="42" name="AutoShape 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00002A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7256,7 +7702,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="43" name="AutoShape 42"/>
+        <xdr:cNvPr id="43" name="AutoShape 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00002B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7323,7 +7775,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="44" name="AutoShape 43"/>
+        <xdr:cNvPr id="44" name="AutoShape 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00002C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7390,7 +7848,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="45" name="Rectangle 44"/>
+        <xdr:cNvPr id="45" name="Rectangle 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00002D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7433,7 +7897,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="46" name="AutoShape 45"/>
+        <xdr:cNvPr id="46" name="AutoShape 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00002E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7500,7 +7970,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="47" name="AutoShape 46"/>
+        <xdr:cNvPr id="47" name="AutoShape 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00002F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7554,73 +8030,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>295275</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="48" name="AutoShape 47"/>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="85725" y="762000"/>
-          <a:ext cx="209550" cy="209550"/>
-        </a:xfrm>
-        <a:prstGeom prst="wedgeEllipseCallout">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val 13634"/>
-            <a:gd name="adj2" fmla="val 122727"/>
-          </a:avLst>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="00FF00" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="11"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-          </a:solidFill>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="de-DE" sz="900" b="1" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:ea typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>2</a:t>
-          </a:r>
-          <a:endParaRPr lang="de-DE"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>342900</xdr:colOff>
       <xdr:row>4</xdr:row>
@@ -7634,7 +8043,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="49" name="AutoShape 48"/>
+        <xdr:cNvPr id="49" name="AutoShape 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000031000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7701,7 +8116,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="50" name="AutoShape 49"/>
+        <xdr:cNvPr id="50" name="AutoShape 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000032000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7768,7 +8189,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="51" name="AutoShape 50"/>
+        <xdr:cNvPr id="51" name="AutoShape 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000033000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7835,7 +8262,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="52" name="AutoShape 51"/>
+        <xdr:cNvPr id="52" name="AutoShape 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000034000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7902,7 +8335,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="53" name="AutoShape 52"/>
+        <xdr:cNvPr id="53" name="AutoShape 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000035000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7969,7 +8408,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="54" name="AutoShape 53"/>
+        <xdr:cNvPr id="54" name="AutoShape 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000036000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -8036,7 +8481,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="55" name="AutoShape 54"/>
+        <xdr:cNvPr id="55" name="AutoShape 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000037000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -8103,7 +8554,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="56" name="AutoShape 55"/>
+        <xdr:cNvPr id="56" name="AutoShape 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000038000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -8170,7 +8627,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="57" name="AutoShape 56"/>
+        <xdr:cNvPr id="57" name="AutoShape 56">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000039000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -8237,7 +8700,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="58" name="AutoShape 57"/>
+        <xdr:cNvPr id="58" name="AutoShape 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00003A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -8284,6 +8753,118 @@
             <a:t>11v</a:t>
           </a:r>
           <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>198120</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>746761</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>182880</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="60" name="Text Box 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84E6D713-4F00-4C65-AF94-386134DC9AE9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2339340" y="1082040"/>
+          <a:ext cx="1341121" cy="617220"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="ctr">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="de-DE" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Ranjeetsing Tawar</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="de-DE" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Matr.-Nr.   7026116</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="de-DE" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>2. Sem   MBIDA</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -8403,7 +8984,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Report"/>
@@ -8426,9 +9007,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -8466,9 +9047,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -8503,7 +9084,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -8538,7 +9119,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -8711,63 +9292,65 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I78"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="55" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B1" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="3"/>
+      <c r="B4" s="3" t="s">
+        <v>135</v>
+      </c>
       <c r="G4" s="4"/>
       <c r="H4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="3"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="3"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="B5" s="6">
+        <v>7026116</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>21</v>
-      </c>
       <c r="I5" s="7"/>
     </row>
-    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="8"/>
       <c r="B6" s="9"/>
       <c r="H6" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I6" s="9"/>
     </row>
-    <row r="9" spans="1:9" ht="21" x14ac:dyDescent="0.35">
-      <c r="B9" s="62" t="s">
+    <row r="9" spans="1:9" ht="21" x14ac:dyDescent="0.4">
+      <c r="B9" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="62"/>
-      <c r="D9" s="62"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C9" s="64"/>
+      <c r="D9" s="64"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="21" x14ac:dyDescent="0.4">
       <c r="A13" s="61" t="s">
         <v>1</v>
       </c>
@@ -8778,644 +9361,644 @@
         <v>3</v>
       </c>
       <c r="D13" s="61" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="21" x14ac:dyDescent="0.35">
-      <c r="A14" s="62" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="62"/>
-      <c r="C14" s="62"/>
-      <c r="D14" s="62"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="21" x14ac:dyDescent="0.4">
+      <c r="A14" s="64" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="64"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="64"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1</v>
       </c>
-      <c r="B15" s="64" t="s">
+      <c r="B15" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="70" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C15" s="65" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16">
         <f t="shared" ref="A16:A78" si="0">A15+1</f>
         <v>2</v>
       </c>
-      <c r="B16" s="64" t="s">
-        <v>92</v>
-      </c>
-      <c r="C16" s="70"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="62" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" s="65"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B17" s="64" t="s">
-        <v>93</v>
-      </c>
-      <c r="C17" s="70"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="62" t="s">
+        <v>91</v>
+      </c>
+      <c r="C17" s="65"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B18" s="64" t="s">
+      <c r="B18" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="70"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C18" s="65"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B19" s="64" t="s">
+      <c r="B19" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="70"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C19" s="65"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B20" s="64" t="s">
+      <c r="B20" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="70"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C20" s="65"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B21" s="64" t="s">
-        <v>94</v>
-      </c>
-      <c r="C21" s="70"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="62" t="s">
+        <v>92</v>
+      </c>
+      <c r="C21" s="65"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B22" s="64" t="s">
+      <c r="B22" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="70"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C22" s="65"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B23" s="64" t="s">
+      <c r="B23" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="70"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C23" s="65"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B24" s="64" t="s">
+      <c r="B24" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="C24" s="70"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C24" s="65"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B25" s="64" t="s">
-        <v>105</v>
-      </c>
-      <c r="C25" s="70"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="62" t="s">
+        <v>103</v>
+      </c>
+      <c r="C25" s="65"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="68" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="C26" s="66" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B27" s="65" t="s">
+      <c r="B27" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="68"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C27" s="66"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B28" s="65" t="s">
-        <v>100</v>
-      </c>
-      <c r="C28" s="68"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>98</v>
+      </c>
+      <c r="C28" s="66"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B29" s="65" t="s">
-        <v>101</v>
-      </c>
-      <c r="C29" s="68"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>99</v>
+      </c>
+      <c r="C29" s="66"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
-      </c>
-      <c r="C30" s="68"/>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+      <c r="C30" s="66"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>102</v>
-      </c>
-      <c r="C31" s="68"/>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="C31" s="66"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B32" t="s">
-        <v>103</v>
-      </c>
-      <c r="C32" s="68"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+      <c r="C32" s="66"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B33" t="s">
-        <v>25</v>
-      </c>
-      <c r="C33" s="68"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="C33" s="66"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B34" s="64" t="s">
-        <v>26</v>
-      </c>
-      <c r="C34" s="70" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B34" s="62" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="65" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B35" s="64" t="s">
-        <v>33</v>
-      </c>
-      <c r="C35" s="70"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B35" s="62" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="65"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B36" s="64" t="s">
-        <v>27</v>
-      </c>
-      <c r="C36" s="70"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B36" s="62" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" s="65"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B37" s="64" t="s">
-        <v>104</v>
-      </c>
-      <c r="C37" s="70"/>
-    </row>
-    <row r="38" spans="1:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="A38" s="62" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="62"/>
-      <c r="C38" s="62"/>
-      <c r="D38" s="62"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B37" s="62" t="s">
+        <v>102</v>
+      </c>
+      <c r="C37" s="65"/>
+    </row>
+    <row r="38" spans="1:4" ht="21" x14ac:dyDescent="0.4">
+      <c r="A38" s="64" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="64"/>
+      <c r="C38" s="64"/>
+      <c r="D38" s="64"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39">
         <f>A37+1</f>
         <v>24</v>
       </c>
       <c r="B39" t="s">
-        <v>32</v>
-      </c>
-      <c r="C39" s="68" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="C39" s="66" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="B40" t="s">
-        <v>34</v>
-      </c>
-      <c r="C40" s="68"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="C40" s="66"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="B41" t="s">
-        <v>35</v>
-      </c>
-      <c r="C41" s="68"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="C41" s="66"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="B42" t="s">
-        <v>44</v>
-      </c>
-      <c r="C42" s="68"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="C42" s="66"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="B43" t="s">
-        <v>46</v>
-      </c>
-      <c r="C43" s="68"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+      <c r="C43" s="66"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>121</v>
-      </c>
-      <c r="C44" s="68"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+      <c r="C44" s="66"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>120</v>
-      </c>
-      <c r="C45" s="68"/>
-    </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+      <c r="C45" s="66"/>
+    </row>
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B46" s="64" t="s">
-        <v>106</v>
-      </c>
-      <c r="C46" s="69" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B46" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="C46" s="67" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B47" s="64" t="s">
-        <v>107</v>
-      </c>
-      <c r="C47" s="69"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B47" s="62" t="s">
+        <v>105</v>
+      </c>
+      <c r="C47" s="67"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B48" s="64" t="s">
-        <v>108</v>
-      </c>
-      <c r="C48" s="69"/>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B48" s="62" t="s">
+        <v>106</v>
+      </c>
+      <c r="C48" s="67"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B49" s="64" t="s">
-        <v>109</v>
-      </c>
-      <c r="C49" s="69"/>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B49" s="62" t="s">
+        <v>107</v>
+      </c>
+      <c r="C49" s="67"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B50" s="65" t="s">
-        <v>110</v>
-      </c>
-      <c r="C50" s="67" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>108</v>
+      </c>
+      <c r="C50" s="68" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B51" s="65" t="s">
-        <v>111</v>
-      </c>
-      <c r="C51" s="67"/>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>109</v>
+      </c>
+      <c r="C51" s="68"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="B52" s="65" t="s">
-        <v>122</v>
-      </c>
-      <c r="C52" s="67"/>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>120</v>
+      </c>
+      <c r="C52" s="68"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="B53" s="64" t="str">
+      <c r="B53" s="62" t="str">
         <f>[1]Report!$A$207</f>
         <v>Homework "Literature"</v>
       </c>
-      <c r="C53" s="69" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C53" s="67" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="B54" s="64" t="s">
-        <v>112</v>
-      </c>
-      <c r="C54" s="69"/>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B54" s="62" t="s">
+        <v>110</v>
+      </c>
+      <c r="C54" s="67"/>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="B55" s="64" t="s">
-        <v>116</v>
-      </c>
-      <c r="C55" s="69"/>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B55" s="62" t="s">
+        <v>114</v>
+      </c>
+      <c r="C55" s="67"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="B56" s="65" t="s">
-        <v>115</v>
-      </c>
-      <c r="C56" s="67" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
+        <v>113</v>
+      </c>
+      <c r="C56" s="68" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="B57" s="65" t="s">
-        <v>117</v>
-      </c>
-      <c r="C57" s="67"/>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
+        <v>115</v>
+      </c>
+      <c r="C57" s="68"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58">
         <f>A57+1</f>
         <v>43</v>
       </c>
-      <c r="B58" s="65" t="s">
-        <v>113</v>
-      </c>
-      <c r="C58" s="67"/>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
+        <v>111</v>
+      </c>
+      <c r="C58" s="68"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="B59" s="65" t="s">
-        <v>114</v>
-      </c>
-      <c r="C59" s="67"/>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
+        <v>112</v>
+      </c>
+      <c r="C59" s="68"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="B60" s="64" t="s">
-        <v>118</v>
-      </c>
-      <c r="C60" s="69" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B60" s="62" t="s">
+        <v>116</v>
+      </c>
+      <c r="C60" s="67" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="B61" s="64" t="s">
-        <v>119</v>
-      </c>
-      <c r="C61" s="69"/>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B61" s="62" t="s">
+        <v>117</v>
+      </c>
+      <c r="C61" s="67"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="B62" s="64" t="s">
-        <v>124</v>
-      </c>
-      <c r="C62" s="69"/>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B62" s="62" t="s">
+        <v>122</v>
+      </c>
+      <c r="C62" s="67"/>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
       <c r="B63" t="s">
-        <v>123</v>
-      </c>
-      <c r="C63" s="67" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+      <c r="C63" s="68" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="B64" s="66" t="s">
-        <v>125</v>
-      </c>
-      <c r="C64" s="67"/>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B64" s="63" t="s">
+        <v>123</v>
+      </c>
+      <c r="C64" s="68"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="B65" s="66" t="s">
-        <v>126</v>
-      </c>
-      <c r="C65" s="67"/>
-    </row>
-    <row r="66" spans="1:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="A66" s="62" t="s">
-        <v>41</v>
-      </c>
-      <c r="B66" s="62"/>
-      <c r="C66" s="62"/>
-      <c r="D66" s="62"/>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B65" s="63" t="s">
+        <v>124</v>
+      </c>
+      <c r="C65" s="68"/>
+    </row>
+    <row r="66" spans="1:4" ht="21" x14ac:dyDescent="0.4">
+      <c r="A66" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="B66" s="64"/>
+      <c r="C66" s="64"/>
+      <c r="D66" s="64"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67">
         <f>A65+1</f>
         <v>51</v>
       </c>
       <c r="B67" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
       <c r="B68" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
       <c r="B69" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
       <c r="B70" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71">
         <f>A70+1</f>
         <v>55</v>
       </c>
       <c r="B71" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
       <c r="B72" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
       <c r="B73" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
       <c r="B74" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -9443,11 +10026,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R44"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="11"/>
       <c r="D1" s="11"/>
       <c r="E1" s="11"/>
@@ -9464,7 +10047,7 @@
       <c r="P1" s="11"/>
       <c r="Q1" s="11"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="11"/>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
@@ -9481,7 +10064,7 @@
       <c r="P2" s="11"/>
       <c r="Q2" s="11"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="11"/>
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
@@ -9498,7 +10081,7 @@
       <c r="P3" s="11"/>
       <c r="Q3" s="11"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="11"/>
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
@@ -9515,7 +10098,7 @@
       <c r="P4" s="11"/>
       <c r="Q4" s="11"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="11"/>
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
@@ -9532,7 +10115,7 @@
       <c r="P5" s="11"/>
       <c r="Q5" s="11"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="11"/>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
@@ -9549,7 +10132,7 @@
       <c r="P6" s="11"/>
       <c r="Q6" s="11"/>
     </row>
-    <row r="7" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="11"/>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -9568,28 +10151,28 @@
       <c r="P7" s="12"/>
       <c r="Q7" s="11"/>
     </row>
-    <row r="8" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="63" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" s="63"/>
-      <c r="F8" s="63"/>
-      <c r="G8" s="63"/>
-      <c r="H8" s="63"/>
-      <c r="I8" s="63"/>
-      <c r="J8" s="63"/>
-      <c r="K8" s="63"/>
-      <c r="L8" s="63"/>
-      <c r="M8" s="63"/>
-      <c r="N8" s="63"/>
-      <c r="O8" s="63"/>
-      <c r="P8" s="63"/>
+      <c r="D8" s="69" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="69"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="69"/>
+      <c r="K8" s="69"/>
+      <c r="L8" s="69"/>
+      <c r="M8" s="69"/>
+      <c r="N8" s="69"/>
+      <c r="O8" s="69"/>
+      <c r="P8" s="69"/>
       <c r="Q8" s="11"/>
     </row>
-    <row r="9" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="11"/>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -9608,7 +10191,7 @@
       <c r="P9" s="12"/>
       <c r="Q9" s="11"/>
     </row>
-    <row r="10" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11"/>
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
@@ -9625,11 +10208,11 @@
       <c r="P10" s="11"/>
       <c r="Q10" s="11"/>
     </row>
-    <row r="11" spans="1:18" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>
       <c r="B11" s="14"/>
       <c r="C11" s="14" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D11" s="15">
         <v>10</v>
@@ -9656,7 +10239,7 @@
         <v>17</v>
       </c>
       <c r="L11" s="16" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M11" s="16">
         <v>26</v>
@@ -9665,18 +10248,18 @@
         <v>27</v>
       </c>
       <c r="O11" s="16" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="P11" s="17">
         <v>30</v>
       </c>
       <c r="Q11" s="11"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="18"/>
       <c r="B12" s="19"/>
       <c r="C12" s="19" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D12" s="20">
         <v>1</v>
@@ -9703,7 +10286,7 @@
         <v>8</v>
       </c>
       <c r="L12" s="21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M12" s="21">
         <v>16</v>
@@ -9712,22 +10295,22 @@
         <v>17</v>
       </c>
       <c r="O12" s="21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="P12" s="22">
         <v>20</v>
       </c>
       <c r="Q12" s="11"/>
     </row>
-    <row r="13" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="23" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D13" s="26"/>
       <c r="E13" s="27"/>
@@ -9744,12 +10327,12 @@
       <c r="P13" s="28"/>
       <c r="Q13" s="11"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="29">
         <v>1</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C14" s="31">
         <v>2.5</v>
@@ -9770,13 +10353,13 @@
       <c r="Q14" s="35"/>
       <c r="R14" s="36"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <f>A14+1</f>
         <v>2</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C15" s="39">
         <v>1</v>
@@ -9797,16 +10380,16 @@
       <c r="Q15" s="35"/>
       <c r="R15" s="36"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <f t="shared" ref="A16:A30" si="0">A15+1</f>
         <v>3</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D16" s="40"/>
       <c r="E16" s="41"/>
@@ -9824,7 +10407,7 @@
       <c r="Q16" s="35"/>
       <c r="R16" s="36"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -9849,14 +10432,14 @@
       <c r="Q17" s="35"/>
       <c r="R17" s="36"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="37">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B18" s="38"/>
       <c r="C18" s="39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D18" s="40"/>
       <c r="E18" s="41"/>
@@ -9874,7 +10457,7 @@
       <c r="Q18" s="35"/>
       <c r="R18" s="36"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -9897,7 +10480,7 @@
       <c r="Q19" s="35"/>
       <c r="R19" s="36"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -9920,7 +10503,7 @@
       <c r="Q20" s="35"/>
       <c r="R20" s="36"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -9943,7 +10526,7 @@
       <c r="Q21" s="35"/>
       <c r="R21" s="36"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -9966,7 +10549,7 @@
       <c r="Q22" s="35"/>
       <c r="R22" s="36"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -9989,7 +10572,7 @@
       <c r="Q23" s="35"/>
       <c r="R23" s="36"/>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="37">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -10012,7 +10595,7 @@
       <c r="Q24" s="35"/>
       <c r="R24" s="36"/>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -10035,7 +10618,7 @@
       <c r="Q25" s="35"/>
       <c r="R25" s="36"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="37">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -10058,16 +10641,16 @@
       <c r="Q26" s="35"/>
       <c r="R26" s="36"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C27" s="39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D27" s="40"/>
       <c r="E27" s="41"/>
@@ -10085,13 +10668,13 @@
       <c r="Q27" s="35"/>
       <c r="R27" s="36"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" s="37">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C28" s="39">
         <v>2</v>
@@ -10112,13 +10695,13 @@
       <c r="Q28" s="35"/>
       <c r="R28" s="36"/>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C29" s="39">
         <v>1.5</v>
@@ -10139,13 +10722,13 @@
       <c r="Q29" s="35"/>
       <c r="R29" s="36"/>
     </row>
-    <row r="30" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="43">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B30" s="44" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C30" s="45">
         <v>1</v>
@@ -10166,7 +10749,7 @@
       <c r="Q30" s="35"/>
       <c r="R30" s="36"/>
     </row>
-    <row r="31" spans="1:18" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A31" s="11"/>
       <c r="C31" s="49"/>
       <c r="D31" s="11"/>
@@ -10184,7 +10767,7 @@
       <c r="P31" s="11"/>
       <c r="Q31" s="11"/>
     </row>
-    <row r="32" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="11"/>
       <c r="C32" s="49"/>
       <c r="D32" s="11"/>
@@ -10202,10 +10785,10 @@
       <c r="P32" s="11"/>
       <c r="Q32" s="11"/>
     </row>
-    <row r="33" spans="1:18" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A33" s="50"/>
       <c r="B33" s="51" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C33" s="52"/>
       <c r="D33" s="53"/>
@@ -10213,16 +10796,16 @@
       <c r="F33" s="54"/>
       <c r="G33" s="54"/>
       <c r="H33" s="54" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I33" s="54"/>
       <c r="J33" s="54"/>
       <c r="K33" s="54" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="L33" s="54"/>
       <c r="M33" s="54" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="N33" s="54"/>
       <c r="O33" s="54"/>
@@ -10230,10 +10813,10 @@
       <c r="Q33" s="35"/>
       <c r="R33" s="36"/>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" s="37"/>
       <c r="B34" s="38" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C34" s="39"/>
       <c r="D34" s="40"/>
@@ -10243,23 +10826,23 @@
       <c r="H34" s="41"/>
       <c r="I34" s="41"/>
       <c r="J34" s="41" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K34" s="41"/>
       <c r="L34" s="41"/>
       <c r="M34" s="41"/>
       <c r="N34" s="41"/>
       <c r="O34" s="56" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="P34" s="42"/>
       <c r="Q34" s="35"/>
       <c r="R34" s="36"/>
     </row>
-    <row r="35" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="43"/>
       <c r="B35" s="44" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C35" s="45"/>
       <c r="D35" s="46"/>
@@ -10278,7 +10861,7 @@
       <c r="Q35" s="35"/>
       <c r="R35" s="36"/>
     </row>
-    <row r="36" spans="1:18" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A36" s="11"/>
       <c r="D36" s="11"/>
       <c r="E36" s="11"/>
@@ -10295,7 +10878,7 @@
       <c r="P36" s="11"/>
       <c r="Q36" s="11"/>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" s="11"/>
       <c r="D37" s="11"/>
       <c r="E37" s="11"/>
@@ -10312,7 +10895,7 @@
       <c r="P37" s="11"/>
       <c r="Q37" s="11"/>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" s="11"/>
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
@@ -10329,10 +10912,10 @@
       <c r="P38" s="11"/>
       <c r="Q38" s="11"/>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" s="11"/>
       <c r="B39" s="57" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D39" s="11"/>
       <c r="E39" s="11"/>
@@ -10349,10 +10932,10 @@
       <c r="P39" s="11"/>
       <c r="Q39" s="11"/>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" s="11"/>
       <c r="B40" s="57" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D40" s="11"/>
       <c r="E40" s="11"/>
@@ -10362,7 +10945,7 @@
       <c r="I40" s="11"/>
       <c r="J40" s="11"/>
       <c r="K40" s="58" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L40" s="11"/>
       <c r="M40" s="11"/>
@@ -10371,7 +10954,7 @@
       <c r="P40" s="11"/>
       <c r="Q40" s="11"/>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" s="11"/>
       <c r="B41" s="57"/>
       <c r="D41" s="11"/>
@@ -10389,7 +10972,7 @@
       <c r="P41" s="11"/>
       <c r="Q41" s="11"/>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" s="11"/>
       <c r="D42" s="11"/>
       <c r="E42" s="11"/>
@@ -10406,7 +10989,7 @@
       <c r="P42" s="11"/>
       <c r="Q42" s="11"/>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" s="11"/>
       <c r="B43" s="57"/>
       <c r="D43" s="11"/>
@@ -10424,7 +11007,7 @@
       <c r="P43" s="11"/>
       <c r="Q43" s="11"/>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" s="11"/>
       <c r="D44" s="11"/>
       <c r="E44" s="11"/>
@@ -10451,11 +11034,14 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:P44"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="11"/>
       <c r="D1" s="11"/>
       <c r="E1" s="11"/>
@@ -10471,7 +11057,7 @@
       <c r="O1" s="11"/>
       <c r="P1" s="11"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="11"/>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
@@ -10487,7 +11073,7 @@
       <c r="O2" s="11"/>
       <c r="P2" s="11"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="11"/>
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
@@ -10503,7 +11089,7 @@
       <c r="O3" s="11"/>
       <c r="P3" s="11"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="11"/>
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
@@ -10519,7 +11105,7 @@
       <c r="O4" s="11"/>
       <c r="P4" s="11"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="11"/>
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
@@ -10535,7 +11121,7 @@
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="11"/>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
@@ -10551,7 +11137,7 @@
       <c r="O6" s="11"/>
       <c r="P6" s="11"/>
     </row>
-    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="11"/>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -10569,27 +11155,27 @@
       <c r="O7" s="12"/>
       <c r="P7" s="12"/>
     </row>
-    <row r="8" spans="1:16" ht="18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="63" t="s">
-        <v>68</v>
-      </c>
-      <c r="E8" s="63"/>
-      <c r="F8" s="63"/>
-      <c r="G8" s="63"/>
-      <c r="H8" s="63"/>
-      <c r="I8" s="63"/>
-      <c r="J8" s="63"/>
-      <c r="K8" s="63"/>
-      <c r="L8" s="63"/>
-      <c r="M8" s="63"/>
-      <c r="N8" s="63"/>
-      <c r="O8" s="63"/>
-      <c r="P8" s="63"/>
-    </row>
-    <row r="9" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D8" s="69" t="s">
+        <v>66</v>
+      </c>
+      <c r="E8" s="69"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="69"/>
+      <c r="K8" s="69"/>
+      <c r="L8" s="69"/>
+      <c r="M8" s="69"/>
+      <c r="N8" s="69"/>
+      <c r="O8" s="69"/>
+      <c r="P8" s="69"/>
+    </row>
+    <row r="9" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="11"/>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -10607,7 +11193,7 @@
       <c r="O9" s="12"/>
       <c r="P9" s="12"/>
     </row>
-    <row r="10" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11"/>
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
@@ -10623,11 +11209,11 @@
       <c r="O10" s="11"/>
       <c r="P10" s="11"/>
     </row>
-    <row r="11" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>
       <c r="B11" s="14"/>
       <c r="C11" s="14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D11" s="15">
         <v>10</v>
@@ -10654,7 +11240,7 @@
         <v>17</v>
       </c>
       <c r="L11" s="16" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M11" s="16">
         <v>35</v>
@@ -10663,17 +11249,17 @@
         <v>36</v>
       </c>
       <c r="O11" s="16" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="P11" s="17">
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="18"/>
       <c r="B12" s="19"/>
       <c r="C12" s="19" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D12" s="20">
         <v>1</v>
@@ -10700,7 +11286,7 @@
         <v>8</v>
       </c>
       <c r="L12" s="21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M12" s="21">
         <v>26</v>
@@ -10709,21 +11295,21 @@
         <v>27</v>
       </c>
       <c r="O12" s="21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="P12" s="22">
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="25" t="s">
         <v>71</v>
-      </c>
-      <c r="B13" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" s="25" t="s">
-        <v>73</v>
       </c>
       <c r="D13" s="26"/>
       <c r="E13" s="27"/>
@@ -10739,12 +11325,12 @@
       <c r="O13" s="27"/>
       <c r="P13" s="28"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="29">
         <v>1</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C14" s="31">
         <v>2.5</v>
@@ -10763,13 +11349,13 @@
       <c r="O14" s="33"/>
       <c r="P14" s="34"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <f>A14+1</f>
         <v>2</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C15" s="39">
         <v>1</v>
@@ -10788,16 +11374,16 @@
       <c r="O15" s="41"/>
       <c r="P15" s="42"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <f t="shared" ref="A16:A30" si="0">A15+1</f>
         <v>3</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D16" s="40"/>
       <c r="E16" s="41"/>
@@ -10813,7 +11399,7 @@
       <c r="O16" s="41"/>
       <c r="P16" s="42"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -10836,14 +11422,14 @@
       <c r="O17" s="41"/>
       <c r="P17" s="42"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" s="37">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B18" s="38"/>
       <c r="C18" s="39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D18" s="40"/>
       <c r="E18" s="41"/>
@@ -10859,7 +11445,7 @@
       <c r="O18" s="41"/>
       <c r="P18" s="42"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -10880,7 +11466,7 @@
       <c r="O19" s="41"/>
       <c r="P19" s="42"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -10901,7 +11487,7 @@
       <c r="O20" s="41"/>
       <c r="P20" s="42"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -10922,7 +11508,7 @@
       <c r="O21" s="41"/>
       <c r="P21" s="42"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -10943,7 +11529,7 @@
       <c r="O22" s="41"/>
       <c r="P22" s="42"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -10964,7 +11550,7 @@
       <c r="O23" s="41"/>
       <c r="P23" s="42"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" s="37">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -10985,7 +11571,7 @@
       <c r="O24" s="41"/>
       <c r="P24" s="42"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -11006,7 +11592,7 @@
       <c r="O25" s="41"/>
       <c r="P25" s="42"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" s="37">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -11027,16 +11613,16 @@
       <c r="O26" s="41"/>
       <c r="P26" s="42"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C27" s="39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D27" s="40"/>
       <c r="E27" s="41"/>
@@ -11052,13 +11638,13 @@
       <c r="O27" s="41"/>
       <c r="P27" s="42"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" s="37">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B28" s="60" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C28" s="39">
         <v>2</v>
@@ -11077,13 +11663,13 @@
       <c r="O28" s="41"/>
       <c r="P28" s="42"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C29" s="39">
         <v>1.5</v>
@@ -11102,13 +11688,13 @@
       <c r="O29" s="41"/>
       <c r="P29" s="42"/>
     </row>
-    <row r="30" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="43">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B30" s="44" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C30" s="45">
         <v>1</v>
@@ -11127,7 +11713,7 @@
       <c r="O30" s="47"/>
       <c r="P30" s="48"/>
     </row>
-    <row r="31" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A31" s="11"/>
       <c r="C31" s="49"/>
       <c r="D31" s="11"/>
@@ -11144,7 +11730,7 @@
       <c r="O31" s="11"/>
       <c r="P31" s="11"/>
     </row>
-    <row r="32" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="11"/>
       <c r="C32" s="49"/>
       <c r="D32" s="11"/>
@@ -11161,10 +11747,10 @@
       <c r="O32" s="11"/>
       <c r="P32" s="11"/>
     </row>
-    <row r="33" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A33" s="50"/>
       <c r="B33" s="51" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C33" s="52"/>
       <c r="D33" s="53"/>
@@ -11172,25 +11758,25 @@
       <c r="F33" s="54"/>
       <c r="G33" s="54"/>
       <c r="H33" s="54" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I33" s="54"/>
       <c r="J33" s="54"/>
       <c r="K33" s="54" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L33" s="54"/>
       <c r="M33" s="54" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="N33" s="54"/>
       <c r="O33" s="54"/>
       <c r="P33" s="55"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" s="37"/>
       <c r="B34" s="38" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C34" s="39"/>
       <c r="D34" s="40"/>
@@ -11200,21 +11786,21 @@
       <c r="H34" s="41"/>
       <c r="I34" s="41"/>
       <c r="J34" s="41" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K34" s="41"/>
       <c r="L34" s="41"/>
       <c r="M34" s="41"/>
       <c r="N34" s="41"/>
       <c r="O34" s="56" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="P34" s="42"/>
     </row>
-    <row r="35" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="43"/>
       <c r="B35" s="44" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C35" s="45"/>
       <c r="D35" s="46"/>
@@ -11231,7 +11817,7 @@
       <c r="O35" s="47"/>
       <c r="P35" s="48"/>
     </row>
-    <row r="36" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A36" s="11"/>
       <c r="D36" s="11"/>
       <c r="E36" s="11"/>
@@ -11247,7 +11833,7 @@
       <c r="O36" s="11"/>
       <c r="P36" s="11"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" s="11"/>
       <c r="D37" s="11"/>
       <c r="E37" s="11"/>
@@ -11263,7 +11849,7 @@
       <c r="O37" s="11"/>
       <c r="P37" s="11"/>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" s="11"/>
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
@@ -11279,10 +11865,10 @@
       <c r="O38" s="11"/>
       <c r="P38" s="11"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" s="11"/>
       <c r="B39" s="57" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D39" s="11"/>
       <c r="E39" s="11"/>
@@ -11298,7 +11884,7 @@
       <c r="O39" s="11"/>
       <c r="P39" s="11"/>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" s="11"/>
       <c r="D40" s="11"/>
       <c r="E40" s="11"/>
@@ -11308,7 +11894,7 @@
       <c r="I40" s="11"/>
       <c r="J40" s="11"/>
       <c r="K40" s="58" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L40" s="11"/>
       <c r="M40" s="11"/>
@@ -11316,7 +11902,7 @@
       <c r="O40" s="11"/>
       <c r="P40" s="11"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" s="11"/>
       <c r="B41" s="57"/>
       <c r="D41" s="11"/>
@@ -11333,7 +11919,7 @@
       <c r="O41" s="11"/>
       <c r="P41" s="11"/>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" s="11"/>
       <c r="D42" s="11"/>
       <c r="E42" s="11"/>
@@ -11349,7 +11935,7 @@
       <c r="O42" s="11"/>
       <c r="P42" s="11"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" s="11"/>
       <c r="D43" s="11"/>
       <c r="E43" s="11"/>
@@ -11365,7 +11951,7 @@
       <c r="O43" s="11"/>
       <c r="P43" s="11"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" s="11"/>
       <c r="D44" s="11"/>
       <c r="E44" s="11"/>
@@ -11391,58 +11977,60 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A7:I25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="7" spans="1:9" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B7" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="3"/>
+      <c r="B10" s="3" t="s">
+        <v>135</v>
+      </c>
       <c r="G10" s="4"/>
       <c r="H10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I10" s="3"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="B11" s="6">
+        <v>7026116</v>
+      </c>
+      <c r="H11" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>21</v>
-      </c>
       <c r="I11" s="7"/>
     </row>
-    <row r="12" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="8"/>
       <c r="B12" s="9"/>
       <c r="H12" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I12" s="9"/>
     </row>
-    <row r="15" spans="1:9" ht="21" x14ac:dyDescent="0.35">
-      <c r="B15" s="62" t="s">
-        <v>89</v>
-      </c>
-      <c r="C15" s="62"/>
-      <c r="D15" s="62"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="21" x14ac:dyDescent="0.4">
+      <c r="B15" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" s="64"/>
+      <c r="D15" s="64"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
         <v>14</v>
       </c>
@@ -11453,45 +12041,45 @@
         <v>3</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B19" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/ProjectManagement/Checklist.xlsx
+++ b/ProjectManagement/Checklist.xlsx
@@ -3,25 +3,26 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28025"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7E78E06-F8D7-40F8-A963-0154E943A1F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{297DE719-9F34-4012-A557-27E115298C10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Checklist" sheetId="1" r:id="rId1"/>
-    <sheet name="Projekt Plan V1.0 (deut.)" sheetId="4" r:id="rId2"/>
-    <sheet name="Project Plan V1.0 (eng.)" sheetId="5" r:id="rId3"/>
-    <sheet name="Resulting objects" sheetId="2" r:id="rId4"/>
+    <sheet name="Project Plan" sheetId="6" r:id="rId2"/>
+    <sheet name="Resulting objects" sheetId="2" r:id="rId3"/>
+    <sheet name="Projekt Plan V1.0 (deut.)" sheetId="4" r:id="rId4"/>
+    <sheet name="Project Plan V1.0 (eng.)" sheetId="5" r:id="rId5"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId5"/>
+    <externalReference r:id="rId6"/>
   </externalReferences>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="177">
   <si>
     <t>Checklist</t>
   </si>
@@ -433,12 +434,132 @@
   <si>
     <t>ML24-03 Car Licence Plate Identification with a Jetson Nano</t>
   </si>
+  <si>
+    <t xml:space="preserve">cc:Hochschule Emden Leer Universit of Applied Sciences </t>
+  </si>
+  <si>
+    <t>MBIDA</t>
+  </si>
+  <si>
+    <t>Prof. Elmar Wings</t>
+  </si>
+  <si>
+    <t>Software Installation (GitHub, TexLive, TexStudio, Sumatrapdf, doxygen)</t>
+  </si>
+  <si>
+    <t>Clone Repository</t>
+  </si>
+  <si>
+    <t>Author and Checklist Update</t>
+  </si>
+  <si>
+    <t>Project Plan Creation</t>
+  </si>
+  <si>
+    <t>Introduction Writing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Problem Description </t>
+  </si>
+  <si>
+    <t>Hardware Description Section</t>
+  </si>
+  <si>
+    <t>Software Description</t>
+  </si>
+  <si>
+    <t>Data Mining Algorithm Writing</t>
+  </si>
+  <si>
+    <t>KDD research for project</t>
+  </si>
+  <si>
+    <t>Data selection Writing</t>
+  </si>
+  <si>
+    <t>Data preprocessing Writing</t>
+  </si>
+  <si>
+    <t>Data transformation Writing</t>
+  </si>
+  <si>
+    <t>Data Mining Writing</t>
+  </si>
+  <si>
+    <t>Interpretation Writing</t>
+  </si>
+  <si>
+    <t>Validation Writing</t>
+  </si>
+  <si>
+    <t>Given Documentation and Improvements Preparation</t>
+  </si>
+  <si>
+    <t>Expect Deployment Writing</t>
+  </si>
+  <si>
+    <t>Manual Preparation</t>
+  </si>
+  <si>
+    <t>Testing Basic HW Features</t>
+  </si>
+  <si>
+    <t>Implementation of Data KDD Model</t>
+  </si>
+  <si>
+    <t>Develop Initial Code for ML Model</t>
+  </si>
+  <si>
+    <t>Testing on the HW</t>
+  </si>
+  <si>
+    <t>Optimize the Model - Python</t>
+  </si>
+  <si>
+    <t>Testing the model behavior with HW</t>
+  </si>
+  <si>
+    <t>Improving Model with real cases</t>
+  </si>
+  <si>
+    <t>Result / Conclusion / Next Steps</t>
+  </si>
+  <si>
+    <t>Poster Preparation</t>
+  </si>
+  <si>
+    <t>Presentation Preparation</t>
+  </si>
+  <si>
+    <t>Final Modification</t>
+  </si>
+  <si>
+    <t>X-Mas</t>
+  </si>
+  <si>
+    <t>24th January Hardware return</t>
+  </si>
+  <si>
+    <t>16th January Final Presentation</t>
+  </si>
+  <si>
+    <t>31th January Project Deadline</t>
+  </si>
+  <si>
+    <t>Convert ML Model to C</t>
+  </si>
+  <si>
+    <t>List Of Materials Required</t>
+  </si>
+  <si>
+    <t>Write Jet bot Probable Application /Required Algorithms/Source Code (Part 2)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -503,8 +624,31 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -523,8 +667,56 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE9D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF1DE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6D9F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="39">
+  <borders count="69">
     <border>
       <left/>
       <right/>
@@ -1012,11 +1204,391 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1201,6 +1773,241 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1225,6 +2032,3274 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>144780</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>116205</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{571C32FC-C999-41CE-B5AD-463EF625FC1C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4556760" y="0"/>
+          <a:ext cx="7947660" cy="299085"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -16106"/>
+            <a:gd name="adj2" fmla="val 37181"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="9"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="36576" tIns="36576" rIns="36576" bIns="36576" anchor="ctr" upright="1"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="en-US"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="de-DE" sz="1400" b="1" i="1" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="12"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="12"/>
+            </a:rPr>
+            <a:t>Template for Project Plan of Project-T</a:t>
+          </a:r>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>8965</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>161364</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1288110" cy="636494"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="TextBox 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E297C7A-1B59-4022-875B-218233771768}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="618565" y="1075764"/>
+          <a:ext cx="1288110" cy="636494"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="ctr">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Hemanth</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> Prabhakaran</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-IN"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100"/>
+            <a:t>Matr.-Nr.  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>7026000</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN"/>
+            <a:t> </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100"/>
+            <a:t>1. Sem  MBIDA</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>367553</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1288110" cy="636494"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="TextBox 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23B28D54-B791-483B-963E-A9B4190A2B94}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3705113" y="1066800"/>
+          <a:ext cx="1288110" cy="636494"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="ctr">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100"/>
+            <a:t>Mansoor</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0"/>
+            <a:t> Phoulady</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0"/>
+            <a:t>Matr.-Nr. 7025671</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0"/>
+            <a:t>2. Sem MBIDA</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1532965</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1288110" cy="636494"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="TextBox 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F97DC29-A919-45C2-A620-C3223CFC10AB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2142565" y="1066800"/>
+          <a:ext cx="1288110" cy="636494"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="ctr">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0"/>
+          <a:r>
+            <a:rPr lang="de-DE" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Ranjeetsing Tawar</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-IN">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0"/>
+          <a:r>
+            <a:rPr lang="de-DE" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Matr.-Nr.   7026116</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-IN">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0"/>
+          <a:r>
+            <a:rPr lang="de-DE" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1. Sem   MBIDA</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-IN">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1568824</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1288110" cy="197224"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="TextBox 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C30F0D6E-29B5-4588-B6CA-A9680AE40F1E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2178424" y="548640"/>
+          <a:ext cx="1288110" cy="197224"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FAFAC2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="ctr">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100"/>
+            <a:t>All Groupmates</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>280670</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Rectangle 6" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85497EC0-E274-48C1-A045-E1471058211E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3337560" y="2468880"/>
+          <a:ext cx="280670" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill prst="pct10">
+          <a:fgClr>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0000FF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="12"/>
+          </a:fgClr>
+          <a:bgClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>208952</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>175894</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>486918</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>170329</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Rectangle 7" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{38280271-420E-457D-8794-CE2EEF78844E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3546512" y="2644774"/>
+          <a:ext cx="277966" cy="177315"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill prst="pct10">
+          <a:fgClr>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0000FF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="12"/>
+          </a:fgClr>
+          <a:bgClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>355189</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>177502</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>604744</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>169658</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Rectangle 8" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{259ADDB3-EC9B-468C-9BCD-E7ACB9CC087C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3692749" y="2829262"/>
+          <a:ext cx="249555" cy="175036"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill prst="pct10">
+          <a:fgClr>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0000FF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="12"/>
+          </a:fgClr>
+          <a:bgClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>98611</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>274320</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>179256</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="Rectangle 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31BB3058-F268-4468-A36D-7D61B45D20C0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3337560" y="2567491"/>
+          <a:ext cx="274320" cy="80645"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="008000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="17"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="en-US"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>206189</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>107576</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>394446</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>166406</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="Rectangle 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7591CC0-F766-4F97-B0AC-A0D3CD380102}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3543749" y="2759336"/>
+          <a:ext cx="188257" cy="58830"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="008000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="17"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="en-US"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>358589</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>98612</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>602429</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>179257</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="Rectangle 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22656688-F92D-4C76-9C72-C9D3EAC2DC60}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3696149" y="2933252"/>
+          <a:ext cx="243840" cy="80645"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="008000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="17"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="en-US"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>8965</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>3810</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>177240</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="Rectangle 12" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0590437B-E2FC-4327-B2E9-702E27BE3C95}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3337560" y="3209365"/>
+          <a:ext cx="2442210" cy="168275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill prst="pct10">
+          <a:fgClr>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0000FF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="12"/>
+          </a:fgClr>
+          <a:bgClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>98611</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>512445</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>174811</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="Rectangle 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3CF0FC9C-6E91-426F-9EFB-9FE57E372EB8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3337560" y="3299011"/>
+          <a:ext cx="1122045" cy="76200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="008000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="17"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>358588</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>17929</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>175708</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>4370</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="Rectangle 14" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AEE1A983-0840-4356-9F71-9AE1777C57CB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3696148" y="3035449"/>
+          <a:ext cx="426720" cy="169321"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill prst="pct10">
+          <a:fgClr>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0000FF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="12"/>
+          </a:fgClr>
+          <a:bgClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>367553</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>89647</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>168163</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>174102</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="Rectangle 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D6569E4-92F3-4A27-9448-B92873AD5CCB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="3705113" y="3107167"/>
+          <a:ext cx="410210" cy="84455"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="008000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="17"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>8963</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>8964</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>26892</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>170329</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="Rectangle 16" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5334D99-6007-4114-9E1B-277E4488E3E7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4565723" y="3392244"/>
+          <a:ext cx="627529" cy="161365"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill prst="pct10">
+          <a:fgClr>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0000FF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="12"/>
+          </a:fgClr>
+          <a:bgClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>322729</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>170329</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>403411</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>170330</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="Rectangle 17" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{184092F4-B30A-4B40-83F3-AD1C88115950}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4879489" y="3553609"/>
+          <a:ext cx="690282" cy="182881"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill prst="pct10">
+          <a:fgClr>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0000FF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="12"/>
+          </a:fgClr>
+          <a:bgClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>600635</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>179293</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>104065</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>166369</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="Rectangle 18" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8885B262-34B7-4814-9F63-10019117329C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5157395" y="3745453"/>
+          <a:ext cx="722630" cy="169956"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill prst="pct10">
+          <a:fgClr>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0000FF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="12"/>
+          </a:fgClr>
+          <a:bgClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>179293</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>170328</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="Rectangle 19" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A280F9CE-D43F-49D2-BEDA-F2A0E99142E8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5775960" y="3928333"/>
+          <a:ext cx="731520" cy="173915"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill prst="pct10">
+          <a:fgClr>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0000FF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="12"/>
+          </a:fgClr>
+          <a:bgClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>722630</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>166370</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="Rectangle 20" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F1CD2AB-BC79-4D57-B3C6-27BFD500463D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5775960" y="4114800"/>
+          <a:ext cx="722630" cy="166370"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill prst="pct10">
+          <a:fgClr>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0000FF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="12"/>
+          </a:fgClr>
+          <a:bgClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>8964</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>731594</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>166370</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="Rectangle 21" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{449C9574-5D7D-48B7-9D82-F04CE5D05641}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5784924" y="4297680"/>
+          <a:ext cx="722630" cy="166370"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill prst="pct10">
+          <a:fgClr>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0000FF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="12"/>
+          </a:fgClr>
+          <a:bgClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>179293</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>448236</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>170330</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="Rectangle 22" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71298594-C0D9-47F7-8CE2-0AFFD644C804}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5775960" y="4476973"/>
+          <a:ext cx="1179756" cy="173917"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill prst="pct10">
+          <a:fgClr>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0000FF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="12"/>
+          </a:fgClr>
+          <a:bgClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>403410</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>8965</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>17930</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>4034</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="Rectangle 23" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DCB22B8-345F-4BA1-8560-E83A138F6148}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6179370" y="4672405"/>
+          <a:ext cx="1077560" cy="177949"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill prst="pct10">
+          <a:fgClr>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0000FF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="12"/>
+          </a:fgClr>
+          <a:bgClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>8965</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>17929</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>389554</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>2690</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="Rectangle 24" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12DE2454-3901-4343-94E5-2220A3A2F603}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6516445" y="4864249"/>
+          <a:ext cx="1112109" cy="167641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill prst="pct10">
+          <a:fgClr>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0000FF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="12"/>
+          </a:fgClr>
+          <a:bgClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2391</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>7171</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>394447</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>8964</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="Rectangle 25" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD8F4D1C-EBE7-4106-A056-F26BAC924AA8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6509871" y="5036371"/>
+          <a:ext cx="1123576" cy="184673"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill prst="pct10">
+          <a:fgClr>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0000FF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="12"/>
+          </a:fgClr>
+          <a:bgClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>8965</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>385483</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>10759</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="Rectangle 26" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD9F636F-DDB7-42F7-A65F-8445E44E77EE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6507480" y="5221045"/>
+          <a:ext cx="1117003" cy="184674"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill prst="pct10">
+          <a:fgClr>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0000FF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="12"/>
+          </a:fgClr>
+          <a:bgClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>382494</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>8966</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>726141</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>170330</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="Rectangle 27" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C447FF7-57E9-4A36-90B3-33FDD25F63A0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7621494" y="5403926"/>
+          <a:ext cx="1075167" cy="161364"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill prst="pct10">
+          <a:fgClr>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0000FF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="12"/>
+          </a:fgClr>
+          <a:bgClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>372185</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>170329</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>726141</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="Rectangle 28" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D5504D6-6C51-48F6-AEDE-E6FDA948F7C7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7611185" y="5565289"/>
+          <a:ext cx="1085476" cy="180191"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill prst="pct10">
+          <a:fgClr>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0000FF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="12"/>
+          </a:fgClr>
+          <a:bgClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>372184</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>726141</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>177502</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="30" name="Rectangle 29" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{245C6239-252A-42E0-9E31-79E16DB6CFD5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7611184" y="5760720"/>
+          <a:ext cx="1085477" cy="177502"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill prst="pct10">
+          <a:fgClr>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0000FF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="12"/>
+          </a:fgClr>
+          <a:bgClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>729615</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>166370</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="Rectangle 30" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC4D54F9-FCA3-48F1-B4F5-9DC04C6A22C0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8702040" y="5943600"/>
+          <a:ext cx="729615" cy="166370"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill prst="pct10">
+          <a:fgClr>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0000FF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="12"/>
+          </a:fgClr>
+          <a:bgClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>18191</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>734060</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>157256</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="32" name="Rectangle 31" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB0E45D1-BFA0-4C95-9D94-B18CB637CE92}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8709660" y="6144671"/>
+          <a:ext cx="726440" cy="139065"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill prst="pct10">
+          <a:fgClr>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0000FF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="12"/>
+          </a:fgClr>
+          <a:bgClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>11019</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>6312</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>527909</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>158712</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="33" name="Rectangle 32" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63AFBB7C-CC1C-4E37-9CD5-966691432076}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9444579" y="6498552"/>
+          <a:ext cx="516890" cy="152400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill prst="pct10">
+          <a:fgClr>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0000FF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="12"/>
+          </a:fgClr>
+          <a:bgClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>491303</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>18340</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>718857</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>971</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="34" name="Rectangle 33" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{832E0E84-BBF8-4318-B92D-BE1809456E7C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10656383" y="7059220"/>
+          <a:ext cx="959074" cy="165511"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill prst="pct10">
+          <a:fgClr>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0000FF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="12"/>
+          </a:fgClr>
+          <a:bgClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>26894</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>23233</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>722443</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>175633</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="36" name="Rectangle 35" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86264EAD-21B3-4469-8E46-DDE5DA9E76D7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9460454" y="6698353"/>
+          <a:ext cx="1427069" cy="152400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill prst="pct10">
+          <a:fgClr>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0000FF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="12"/>
+          </a:fgClr>
+          <a:bgClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="en-US"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>726029</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>13484</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>722443</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>152549</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="37" name="Rectangle 36" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E908E89B-070A-4840-9EC9-E88BF6C37FC7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10159589" y="6871484"/>
+          <a:ext cx="727934" cy="139065"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill prst="pct10">
+          <a:fgClr>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0000FF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="12"/>
+          </a:fgClr>
+          <a:bgClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>8965</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>35859</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>380665</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>4520</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="38" name="Rectangle 37" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9818958A-77F4-473A-9A39-EAA965BCA2AE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12368605" y="7259619"/>
+          <a:ext cx="1103220" cy="151541"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill prst="pct10">
+          <a:fgClr>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0000FF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="12"/>
+          </a:fgClr>
+          <a:bgClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="en-US"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>529590</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>23906</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>212539</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>168686</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="39" name="Rectangle 38" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0FC5232-97BE-425C-8FDE-095EFA5F57D1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12889230" y="7430546"/>
+          <a:ext cx="1145989" cy="144780"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill prst="pct10">
+          <a:fgClr>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0000FF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="12"/>
+          </a:fgClr>
+          <a:bgClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>381225</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>38</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>8219</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="40" name="Rectangle 39" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{028C1D09-1F2B-462A-8FD8-7176B23AE89A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13472385" y="7589521"/>
+          <a:ext cx="1081853" cy="191098"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill prst="pct10">
+          <a:fgClr>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0000FF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="12"/>
+          </a:fgClr>
+          <a:bgClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>469826</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>20619</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>269390</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>174924</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="41" name="Rectangle 40" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07E82DBE-201E-4088-AB03-10BC9D070A08}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14292506" y="7793019"/>
+          <a:ext cx="531084" cy="154305"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill prst="pct10">
+          <a:fgClr>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0000FF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="12"/>
+          </a:fgClr>
+          <a:bgClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>460563</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>172906</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>16735</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>164427</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="42" name="Rectangle 41" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BF19BD5-5969-4032-876D-D54AFB33FBDF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15014763" y="8493946"/>
+          <a:ext cx="1750732" cy="174401"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill prst="pct10">
+          <a:fgClr>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0000FF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="12"/>
+          </a:fgClr>
+          <a:bgClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>199988</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>10459</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>725133</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>174289</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="43" name="Rectangle 42" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9550244D-DC6C-4E77-8F54-47F60C867FEE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14754188" y="7965739"/>
+          <a:ext cx="525145" cy="163830"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill prst="pct10">
+          <a:fgClr>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0000FF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="12"/>
+          </a:fgClr>
+          <a:bgClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>723676</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>24279</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>527685</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>3735</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="44" name="Rectangle 43" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3996FC91-2B09-4E15-9BE5-9555310DFDFD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15277876" y="8162439"/>
+          <a:ext cx="535529" cy="162336"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill prst="pct10">
+          <a:fgClr>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0000FF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="12"/>
+          </a:fgClr>
+          <a:bgClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>516816</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>179070</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>311935</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>158526</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="45" name="Rectangle 44" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F75F40CE-D179-4FB9-A67D-6C7ECC376C1B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13607976" y="8317230"/>
+          <a:ext cx="526639" cy="162336"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill prst="pct10">
+          <a:fgClr>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0000FF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="12"/>
+          </a:fgClr>
+          <a:bgClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>5371</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>177995</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>1785</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>161365</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="46" name="Text Box 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76173589-EE56-495B-9C31-C9E34964868B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11633491" y="3744155"/>
+          <a:ext cx="727934" cy="4921130"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFF99" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="43"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vert="vert270" wrap="square" lIns="18288" tIns="0" rIns="0" bIns="0" anchor="ctr" upright="1"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="en-US"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>405457</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>137619</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>439270</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="47" name="Line 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71D28825-3750-4EC6-BE03-05DDB4F7F475}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeShapeType="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14228137" y="3703779"/>
+          <a:ext cx="33813" cy="4983021"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="63500" cmpd="tri">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:noFill/>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="en-US"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>170329</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>8964</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>358589</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>179294</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="48" name="Isosceles Triangle 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B551809-38CB-4D1B-B487-59168D9D168B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3507889" y="10219764"/>
+          <a:ext cx="188260" cy="170330"/>
+        </a:xfrm>
+        <a:prstGeom prst="triangle">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="00B050"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>142874</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>561974</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Abgerundetes Rechteck 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="752474" y="238125"/>
+          <a:ext cx="4829175" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="de-DE" sz="1400" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Project</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="de-DE" sz="1400" b="1" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>plan-Project (10credits) in Master Course </a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="de-DE" sz="1400" b="1" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="de-DE" sz="1400" b="1" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>"Business Intelligence and Data Analytics" </a:t>
+          </a:r>
+          <a:endParaRPr lang="de-DE" sz="1400" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -5046,7 +9121,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -8873,116 +12948,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>142874</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>561974</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Abgerundetes Rechteck 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="752474" y="238125"/>
-          <a:ext cx="4829175" cy="457200"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1">
-            <a:lumMod val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent6">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent6"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent6"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="de-DE" sz="1400" b="1">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Project</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="de-DE" sz="1400" b="1" baseline="0">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>plan-Project (10credits) in Master Course </a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="de-DE" sz="1400" b="1" baseline="0">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="de-DE" sz="1400" b="1" baseline="0">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>"Business Intelligence and Data Analytics" </a:t>
-          </a:r>
-          <a:endParaRPr lang="de-DE" sz="1400" b="1">
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
@@ -9294,18 +13259,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I78"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="55" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" ht="23.4">
       <c r="B1" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="15" thickBot="1"/>
+    <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
@@ -9318,7 +13283,7 @@
       </c>
       <c r="I4" s="3"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9">
       <c r="A5" s="5" t="s">
         <v>18</v>
       </c>
@@ -9330,7 +13295,7 @@
       </c>
       <c r="I5" s="7"/>
     </row>
-    <row r="6" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="15" thickBot="1">
       <c r="A6" s="8"/>
       <c r="B6" s="9"/>
       <c r="H6" s="8" t="s">
@@ -9338,19 +13303,19 @@
       </c>
       <c r="I6" s="9"/>
     </row>
-    <row r="9" spans="1:9" ht="21" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:9" ht="21">
       <c r="B9" s="64" t="s">
         <v>0</v>
       </c>
       <c r="C9" s="64"/>
       <c r="D9" s="64"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="21" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:9" ht="21">
       <c r="A13" s="61" t="s">
         <v>1</v>
       </c>
@@ -9364,7 +13329,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="21" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:9" ht="21">
       <c r="A14" s="64" t="s">
         <v>37</v>
       </c>
@@ -9372,7 +13337,7 @@
       <c r="C14" s="64"/>
       <c r="D14" s="64"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9">
       <c r="A15">
         <v>1</v>
       </c>
@@ -9383,7 +13348,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9">
       <c r="A16">
         <f t="shared" ref="A16:A78" si="0">A15+1</f>
         <v>2</v>
@@ -9393,7 +13358,7 @@
       </c>
       <c r="C16" s="65"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -9403,7 +13368,7 @@
       </c>
       <c r="C17" s="65"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -9413,7 +13378,7 @@
       </c>
       <c r="C18" s="65"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -9423,7 +13388,7 @@
       </c>
       <c r="C19" s="65"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -9433,7 +13398,7 @@
       </c>
       <c r="C20" s="65"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -9443,7 +13408,7 @@
       </c>
       <c r="C21" s="65"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -9453,7 +13418,7 @@
       </c>
       <c r="C22" s="65"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -9463,7 +13428,7 @@
       </c>
       <c r="C23" s="65"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -9473,7 +13438,7 @@
       </c>
       <c r="C24" s="65"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -9483,7 +13448,7 @@
       </c>
       <c r="C25" s="65"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -9495,7 +13460,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -9505,7 +13470,7 @@
       </c>
       <c r="C27" s="66"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -9515,7 +13480,7 @@
       </c>
       <c r="C28" s="66"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -9525,7 +13490,7 @@
       </c>
       <c r="C29" s="66"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -9535,7 +13500,7 @@
       </c>
       <c r="C30" s="66"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -9545,7 +13510,7 @@
       </c>
       <c r="C31" s="66"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -9555,7 +13520,7 @@
       </c>
       <c r="C32" s="66"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -9565,7 +13530,7 @@
       </c>
       <c r="C33" s="66"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -9577,7 +13542,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -9587,7 +13552,7 @@
       </c>
       <c r="C35" s="65"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -9597,7 +13562,7 @@
       </c>
       <c r="C36" s="65"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -9607,7 +13572,7 @@
       </c>
       <c r="C37" s="65"/>
     </row>
-    <row r="38" spans="1:4" ht="21" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:4" ht="21">
       <c r="A38" s="64" t="s">
         <v>38</v>
       </c>
@@ -9615,7 +13580,7 @@
       <c r="C38" s="64"/>
       <c r="D38" s="64"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4">
       <c r="A39">
         <f>A37+1</f>
         <v>24</v>
@@ -9627,7 +13592,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -9637,7 +13602,7 @@
       </c>
       <c r="C40" s="66"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -9647,7 +13612,7 @@
       </c>
       <c r="C41" s="66"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -9657,7 +13622,7 @@
       </c>
       <c r="C42" s="66"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -9667,7 +13632,7 @@
       </c>
       <c r="C43" s="66"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -9677,7 +13642,7 @@
       </c>
       <c r="C44" s="66"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -9687,7 +13652,7 @@
       </c>
       <c r="C45" s="66"/>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" ht="15" customHeight="1">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -9699,7 +13664,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -9709,7 +13674,7 @@
       </c>
       <c r="C47" s="67"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -9719,7 +13684,7 @@
       </c>
       <c r="C48" s="67"/>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -9729,7 +13694,7 @@
       </c>
       <c r="C49" s="67"/>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -9741,7 +13706,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -9751,7 +13716,7 @@
       </c>
       <c r="C51" s="68"/>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -9761,7 +13726,7 @@
       </c>
       <c r="C52" s="68"/>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -9774,7 +13739,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -9784,7 +13749,7 @@
       </c>
       <c r="C54" s="67"/>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -9794,7 +13759,7 @@
       </c>
       <c r="C55" s="67"/>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -9806,7 +13771,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -9816,7 +13781,7 @@
       </c>
       <c r="C57" s="68"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3">
       <c r="A58">
         <f>A57+1</f>
         <v>43</v>
@@ -9826,7 +13791,7 @@
       </c>
       <c r="C58" s="68"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -9836,7 +13801,7 @@
       </c>
       <c r="C59" s="68"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -9848,7 +13813,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -9858,7 +13823,7 @@
       </c>
       <c r="C61" s="67"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -9868,7 +13833,7 @@
       </c>
       <c r="C62" s="67"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -9880,7 +13845,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -9890,7 +13855,7 @@
       </c>
       <c r="C64" s="68"/>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -9900,7 +13865,7 @@
       </c>
       <c r="C65" s="68"/>
     </row>
-    <row r="66" spans="1:4" ht="21" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:4" ht="21">
       <c r="A66" s="64" t="s">
         <v>39</v>
       </c>
@@ -9908,7 +13873,7 @@
       <c r="C66" s="64"/>
       <c r="D66" s="64"/>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4">
       <c r="A67">
         <f>A65+1</f>
         <v>51</v>
@@ -9917,7 +13882,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -9926,7 +13891,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4">
       <c r="A69">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -9935,7 +13900,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4">
       <c r="A70">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -9944,7 +13909,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4">
       <c r="A71">
         <f>A70+1</f>
         <v>55</v>
@@ -9953,7 +13918,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4">
       <c r="A72">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -9962,7 +13927,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4">
       <c r="A73">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -9971,7 +13936,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4">
       <c r="A74">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -9980,25 +13945,25 @@
         <v>46</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4">
       <c r="A75">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4">
       <c r="A76">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4">
       <c r="A77">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4">
       <c r="A78">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -10026,11 +13991,2014 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2DE6EA5-B6F4-47D6-AC52-769953112EBF}">
+  <dimension ref="A1:AC51"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="28.77734375" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:29">
+      <c r="A1" s="70"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="70"/>
+      <c r="O1" s="70"/>
+      <c r="P1" s="70"/>
+      <c r="Q1" s="70"/>
+      <c r="R1" s="71"/>
+      <c r="S1" s="71"/>
+      <c r="T1" s="71"/>
+      <c r="U1" s="71"/>
+      <c r="V1" s="71"/>
+      <c r="W1" s="71"/>
+      <c r="X1" s="71"/>
+      <c r="Y1" s="71"/>
+      <c r="Z1" s="71"/>
+      <c r="AA1" s="71"/>
+      <c r="AB1" s="71"/>
+      <c r="AC1" s="71"/>
+    </row>
+    <row r="2" spans="1:29">
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70"/>
+      <c r="N2" s="70"/>
+      <c r="O2" s="70"/>
+      <c r="P2" s="70"/>
+      <c r="Q2" s="70"/>
+      <c r="R2" s="71"/>
+      <c r="S2" s="71"/>
+      <c r="T2" s="71"/>
+      <c r="U2" s="71"/>
+      <c r="V2" s="71"/>
+      <c r="W2" s="71"/>
+      <c r="X2" s="71"/>
+      <c r="Y2" s="71"/>
+      <c r="Z2" s="71"/>
+      <c r="AA2" s="71"/>
+      <c r="AB2" s="71"/>
+      <c r="AC2" s="71"/>
+    </row>
+    <row r="3" spans="1:29">
+      <c r="A3" s="70"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
+      <c r="I3" s="70"/>
+      <c r="J3" s="70"/>
+      <c r="K3" s="70"/>
+      <c r="L3" s="70"/>
+      <c r="M3" s="70"/>
+      <c r="N3" s="70"/>
+      <c r="O3" s="70"/>
+      <c r="P3" s="70"/>
+      <c r="Q3" s="70"/>
+      <c r="R3" s="71"/>
+      <c r="S3" s="71"/>
+      <c r="T3" s="71"/>
+      <c r="U3" s="71"/>
+      <c r="V3" s="71"/>
+      <c r="W3" s="71"/>
+      <c r="X3" s="71"/>
+      <c r="Y3" s="71"/>
+      <c r="Z3" s="71"/>
+      <c r="AA3" s="71"/>
+      <c r="AB3" s="71"/>
+      <c r="AC3" s="71"/>
+    </row>
+    <row r="4" spans="1:29">
+      <c r="A4" s="70"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="70"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="70"/>
+      <c r="J4" s="70"/>
+      <c r="K4" s="70"/>
+      <c r="L4" s="70"/>
+      <c r="M4" s="70"/>
+      <c r="N4" s="70"/>
+      <c r="O4" s="70"/>
+      <c r="P4" s="70"/>
+      <c r="Q4" s="70"/>
+      <c r="R4" s="70"/>
+      <c r="S4" s="71"/>
+      <c r="T4" s="71"/>
+      <c r="U4" s="71"/>
+      <c r="V4" s="71"/>
+      <c r="W4" s="71"/>
+      <c r="X4" s="71"/>
+      <c r="Y4" s="71"/>
+      <c r="Z4" s="71"/>
+      <c r="AA4" s="71"/>
+      <c r="AB4" s="71"/>
+      <c r="AC4" s="71"/>
+    </row>
+    <row r="5" spans="1:29">
+      <c r="A5" s="70"/>
+      <c r="B5" s="71"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="70"/>
+      <c r="K5" s="70"/>
+      <c r="L5" s="70"/>
+      <c r="M5" s="70"/>
+      <c r="N5" s="70"/>
+      <c r="O5" s="70"/>
+      <c r="P5" s="70"/>
+      <c r="Q5" s="70"/>
+      <c r="R5" s="71"/>
+      <c r="S5" s="71"/>
+      <c r="T5" s="71"/>
+      <c r="U5" s="71"/>
+      <c r="V5" s="71"/>
+      <c r="W5" s="71"/>
+      <c r="X5" s="71"/>
+      <c r="Y5" s="71"/>
+      <c r="Z5" s="71"/>
+      <c r="AA5" s="71"/>
+      <c r="AB5" s="71"/>
+      <c r="AC5" s="71"/>
+    </row>
+    <row r="6" spans="1:29">
+      <c r="A6" s="70"/>
+      <c r="B6" s="71"/>
+      <c r="C6" s="71"/>
+      <c r="D6" s="71"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="70"/>
+      <c r="L6" s="70"/>
+      <c r="M6" s="70"/>
+      <c r="N6" s="70"/>
+      <c r="O6" s="70"/>
+      <c r="P6" s="70"/>
+      <c r="Q6" s="70"/>
+      <c r="R6" s="71"/>
+      <c r="S6" s="71"/>
+      <c r="T6" t="s">
+        <v>137</v>
+      </c>
+      <c r="U6" s="71"/>
+      <c r="V6" s="71"/>
+      <c r="W6" s="71"/>
+      <c r="X6" s="71"/>
+      <c r="Y6" s="71"/>
+      <c r="Z6" s="71"/>
+      <c r="AA6" s="71"/>
+      <c r="AB6" s="71"/>
+      <c r="AC6" s="71"/>
+    </row>
+    <row r="7" spans="1:29" ht="15.6">
+      <c r="A7" s="70"/>
+      <c r="B7" s="70"/>
+      <c r="C7" s="70"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="72"/>
+      <c r="F7" s="72"/>
+      <c r="G7" s="72"/>
+      <c r="H7" s="72"/>
+      <c r="I7" s="72"/>
+      <c r="J7" s="72"/>
+      <c r="K7" s="72"/>
+      <c r="L7" s="72"/>
+      <c r="M7" s="72"/>
+      <c r="N7" s="72"/>
+      <c r="O7" s="72"/>
+      <c r="P7" s="72"/>
+      <c r="Q7" s="72"/>
+      <c r="R7" s="71"/>
+      <c r="S7" s="71" t="s">
+        <v>54</v>
+      </c>
+      <c r="T7" s="71" t="s">
+        <v>138</v>
+      </c>
+      <c r="U7" s="71"/>
+      <c r="V7" s="71"/>
+      <c r="W7" s="71"/>
+      <c r="X7" s="71"/>
+      <c r="Y7" s="71"/>
+      <c r="Z7" s="71"/>
+      <c r="AA7" s="71"/>
+      <c r="AB7" s="71"/>
+      <c r="AC7" s="71"/>
+    </row>
+    <row r="8" spans="1:29" ht="17.399999999999999">
+      <c r="A8" s="70"/>
+      <c r="B8" s="70"/>
+      <c r="C8" s="70"/>
+      <c r="D8" s="70"/>
+      <c r="E8" s="73" t="s">
+        <v>136</v>
+      </c>
+      <c r="F8" s="73"/>
+      <c r="G8" s="73"/>
+      <c r="H8" s="73"/>
+      <c r="I8" s="73"/>
+      <c r="J8" s="73"/>
+      <c r="K8" s="73"/>
+      <c r="L8" s="73"/>
+      <c r="M8" s="73"/>
+      <c r="N8" s="73"/>
+      <c r="O8" s="73"/>
+      <c r="P8" s="73"/>
+      <c r="Q8" s="73"/>
+      <c r="R8" s="71"/>
+      <c r="S8" s="71"/>
+      <c r="T8" s="71" t="s">
+        <v>139</v>
+      </c>
+      <c r="U8" s="71"/>
+      <c r="V8" s="71"/>
+      <c r="W8" s="71"/>
+      <c r="X8" s="71"/>
+      <c r="Y8" s="71"/>
+      <c r="Z8" s="71"/>
+      <c r="AA8" s="71"/>
+      <c r="AB8" s="71"/>
+      <c r="AC8" s="71"/>
+    </row>
+    <row r="9" spans="1:29" ht="15.6">
+      <c r="A9" s="70"/>
+      <c r="B9" s="70"/>
+      <c r="C9" s="70"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="72"/>
+      <c r="F9" s="72"/>
+      <c r="G9" s="72"/>
+      <c r="H9" s="72"/>
+      <c r="I9" s="72"/>
+      <c r="J9" s="72"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="72"/>
+      <c r="M9" s="72"/>
+      <c r="N9" s="72"/>
+      <c r="O9" s="72"/>
+      <c r="P9" s="72"/>
+      <c r="Q9" s="72"/>
+      <c r="R9" s="71"/>
+      <c r="S9" s="71"/>
+      <c r="T9" s="71"/>
+      <c r="U9" s="71"/>
+      <c r="V9" s="71"/>
+      <c r="W9" s="71"/>
+      <c r="X9" s="71"/>
+      <c r="Y9" s="71"/>
+      <c r="Z9" s="71"/>
+      <c r="AA9" s="71"/>
+      <c r="AB9" s="71"/>
+      <c r="AC9" s="71"/>
+    </row>
+    <row r="10" spans="1:29" ht="15" thickBot="1">
+      <c r="A10" s="70"/>
+      <c r="B10" s="71"/>
+      <c r="C10" s="71"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="70"/>
+      <c r="K10" s="70"/>
+      <c r="L10" s="70"/>
+      <c r="M10" s="70"/>
+      <c r="N10" s="70"/>
+      <c r="O10" s="70"/>
+      <c r="P10" s="70"/>
+      <c r="Q10" s="70"/>
+      <c r="R10" s="71"/>
+      <c r="S10" s="71"/>
+      <c r="T10" s="71"/>
+      <c r="U10" s="71"/>
+      <c r="V10" s="71"/>
+      <c r="W10" s="71"/>
+      <c r="X10" s="71"/>
+      <c r="Y10" s="71"/>
+      <c r="Z10" s="71"/>
+      <c r="AA10" s="71"/>
+      <c r="AB10" s="71"/>
+      <c r="AC10" s="71"/>
+    </row>
+    <row r="11" spans="1:29" ht="15" thickTop="1">
+      <c r="A11" s="74"/>
+      <c r="B11" s="75"/>
+      <c r="C11" s="76" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" s="77">
+        <v>40</v>
+      </c>
+      <c r="E11" s="77">
+        <v>41</v>
+      </c>
+      <c r="F11" s="77">
+        <v>42</v>
+      </c>
+      <c r="G11" s="77">
+        <v>43</v>
+      </c>
+      <c r="H11" s="77">
+        <v>44</v>
+      </c>
+      <c r="I11" s="77">
+        <v>45</v>
+      </c>
+      <c r="J11" s="77">
+        <v>46</v>
+      </c>
+      <c r="K11" s="77">
+        <v>47</v>
+      </c>
+      <c r="L11" s="77">
+        <v>48</v>
+      </c>
+      <c r="M11" s="77">
+        <v>49</v>
+      </c>
+      <c r="N11" s="77">
+        <v>50</v>
+      </c>
+      <c r="O11" s="77">
+        <v>51</v>
+      </c>
+      <c r="P11" s="77">
+        <v>52</v>
+      </c>
+      <c r="Q11" s="77">
+        <v>1</v>
+      </c>
+      <c r="R11" s="77">
+        <v>2</v>
+      </c>
+      <c r="S11" s="77">
+        <v>3</v>
+      </c>
+      <c r="T11" s="78">
+        <v>4</v>
+      </c>
+      <c r="U11" s="79">
+        <v>5</v>
+      </c>
+      <c r="V11" s="79">
+        <v>6</v>
+      </c>
+      <c r="W11" s="79">
+        <v>7</v>
+      </c>
+      <c r="X11" s="71"/>
+      <c r="Y11" s="71"/>
+      <c r="Z11" s="71"/>
+      <c r="AA11" s="71"/>
+      <c r="AB11" s="71"/>
+      <c r="AC11" s="71"/>
+    </row>
+    <row r="12" spans="1:29">
+      <c r="A12" s="80"/>
+      <c r="B12" s="81"/>
+      <c r="C12" s="82" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" s="83">
+        <v>1</v>
+      </c>
+      <c r="E12" s="83">
+        <v>2</v>
+      </c>
+      <c r="F12" s="83">
+        <v>3</v>
+      </c>
+      <c r="G12" s="83">
+        <v>4</v>
+      </c>
+      <c r="H12" s="83">
+        <v>5</v>
+      </c>
+      <c r="I12" s="83">
+        <v>6</v>
+      </c>
+      <c r="J12" s="83">
+        <v>7</v>
+      </c>
+      <c r="K12" s="83">
+        <v>8</v>
+      </c>
+      <c r="L12" s="83">
+        <v>9</v>
+      </c>
+      <c r="M12" s="83">
+        <v>10</v>
+      </c>
+      <c r="N12" s="83">
+        <v>11</v>
+      </c>
+      <c r="O12" s="83">
+        <v>12</v>
+      </c>
+      <c r="P12" s="83">
+        <v>13</v>
+      </c>
+      <c r="Q12" s="83">
+        <v>14</v>
+      </c>
+      <c r="R12" s="83">
+        <v>15</v>
+      </c>
+      <c r="S12" s="83">
+        <v>16</v>
+      </c>
+      <c r="T12" s="84">
+        <v>17</v>
+      </c>
+      <c r="U12" s="85">
+        <v>18</v>
+      </c>
+      <c r="V12" s="85">
+        <v>19</v>
+      </c>
+      <c r="W12" s="85">
+        <v>20</v>
+      </c>
+      <c r="X12" s="71"/>
+      <c r="Y12" s="71"/>
+      <c r="Z12" s="71"/>
+      <c r="AA12" s="71"/>
+      <c r="AB12" s="71"/>
+      <c r="AC12" s="71"/>
+    </row>
+    <row r="13" spans="1:29" ht="15" thickBot="1">
+      <c r="A13" s="86" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" s="87" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="88" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="89"/>
+      <c r="E13" s="89"/>
+      <c r="F13" s="89"/>
+      <c r="G13" s="89"/>
+      <c r="H13" s="89"/>
+      <c r="I13" s="89"/>
+      <c r="J13" s="89"/>
+      <c r="K13" s="89"/>
+      <c r="L13" s="89"/>
+      <c r="M13" s="89"/>
+      <c r="N13" s="89"/>
+      <c r="O13" s="89"/>
+      <c r="P13" s="89"/>
+      <c r="Q13" s="89"/>
+      <c r="R13" s="89"/>
+      <c r="S13" s="89"/>
+      <c r="T13" s="90"/>
+      <c r="U13" s="91"/>
+      <c r="V13" s="91"/>
+      <c r="W13" s="91"/>
+      <c r="X13" s="71"/>
+      <c r="Y13" s="71"/>
+      <c r="Z13" s="71"/>
+      <c r="AA13" s="71"/>
+      <c r="AB13" s="71"/>
+      <c r="AC13" s="71"/>
+    </row>
+    <row r="14" spans="1:29">
+      <c r="A14" s="92">
+        <v>1</v>
+      </c>
+      <c r="B14" s="93" t="s">
+        <v>140</v>
+      </c>
+      <c r="C14" s="94">
+        <v>2</v>
+      </c>
+      <c r="D14" s="95"/>
+      <c r="E14" s="96"/>
+      <c r="F14" s="96"/>
+      <c r="G14" s="96"/>
+      <c r="H14" s="96"/>
+      <c r="I14" s="96"/>
+      <c r="J14" s="96"/>
+      <c r="K14" s="96"/>
+      <c r="L14" s="96"/>
+      <c r="M14" s="96"/>
+      <c r="N14" s="96"/>
+      <c r="O14" s="96"/>
+      <c r="P14" s="96"/>
+      <c r="Q14" s="96"/>
+      <c r="R14" s="96"/>
+      <c r="S14" s="96"/>
+      <c r="T14" s="96"/>
+      <c r="U14" s="96"/>
+      <c r="V14" s="97"/>
+      <c r="W14" s="97"/>
+      <c r="X14" s="71"/>
+      <c r="Y14" s="71"/>
+      <c r="Z14" s="71"/>
+      <c r="AA14" s="71"/>
+      <c r="AB14" s="71"/>
+      <c r="AC14" s="71"/>
+    </row>
+    <row r="15" spans="1:29">
+      <c r="A15" s="80">
+        <v>2</v>
+      </c>
+      <c r="B15" s="93" t="s">
+        <v>141</v>
+      </c>
+      <c r="C15" s="94">
+        <v>1</v>
+      </c>
+      <c r="D15" s="70"/>
+      <c r="E15" s="96"/>
+      <c r="F15" s="96"/>
+      <c r="G15" s="96"/>
+      <c r="H15" s="96"/>
+      <c r="I15" s="96"/>
+      <c r="J15" s="96"/>
+      <c r="K15" s="96"/>
+      <c r="L15" s="96"/>
+      <c r="M15" s="96"/>
+      <c r="N15" s="96"/>
+      <c r="O15" s="96"/>
+      <c r="P15" s="96"/>
+      <c r="Q15" s="96"/>
+      <c r="R15" s="96"/>
+      <c r="S15" s="96"/>
+      <c r="T15" s="96"/>
+      <c r="U15" s="96"/>
+      <c r="V15" s="97"/>
+      <c r="W15" s="97"/>
+      <c r="X15" s="71"/>
+      <c r="Y15" s="71"/>
+      <c r="Z15" s="71"/>
+      <c r="AA15" s="71"/>
+      <c r="AB15" s="71"/>
+      <c r="AC15" s="71"/>
+    </row>
+    <row r="16" spans="1:29">
+      <c r="A16" s="80">
+        <v>3</v>
+      </c>
+      <c r="B16" s="93" t="s">
+        <v>142</v>
+      </c>
+      <c r="C16" s="94">
+        <v>2</v>
+      </c>
+      <c r="D16" s="70"/>
+      <c r="E16" s="96"/>
+      <c r="F16" s="96"/>
+      <c r="G16" s="96"/>
+      <c r="H16" s="96"/>
+      <c r="I16" s="96"/>
+      <c r="J16" s="96"/>
+      <c r="K16" s="96"/>
+      <c r="L16" s="96"/>
+      <c r="M16" s="96"/>
+      <c r="N16" s="96"/>
+      <c r="O16" s="96"/>
+      <c r="P16" s="96"/>
+      <c r="Q16" s="96"/>
+      <c r="R16" s="96"/>
+      <c r="S16" s="96"/>
+      <c r="T16" s="96"/>
+      <c r="U16" s="96"/>
+      <c r="V16" s="97"/>
+      <c r="W16" s="97"/>
+      <c r="X16" s="71"/>
+      <c r="Y16" s="71"/>
+      <c r="Z16" s="71"/>
+      <c r="AA16" s="71"/>
+      <c r="AB16" s="71"/>
+      <c r="AC16" s="71"/>
+    </row>
+    <row r="17" spans="1:29">
+      <c r="A17" s="80">
+        <v>4</v>
+      </c>
+      <c r="B17" s="98" t="s">
+        <v>143</v>
+      </c>
+      <c r="C17" s="94">
+        <v>2</v>
+      </c>
+      <c r="D17" s="70"/>
+      <c r="E17" s="96"/>
+      <c r="F17" s="96"/>
+      <c r="G17" s="96"/>
+      <c r="H17" s="96"/>
+      <c r="I17" s="96"/>
+      <c r="J17" s="96"/>
+      <c r="K17" s="96"/>
+      <c r="L17" s="96"/>
+      <c r="M17" s="96"/>
+      <c r="N17" s="96"/>
+      <c r="O17" s="96"/>
+      <c r="P17" s="96"/>
+      <c r="Q17" s="96"/>
+      <c r="R17" s="96"/>
+      <c r="S17" s="96"/>
+      <c r="T17" s="96"/>
+      <c r="U17" s="96"/>
+      <c r="V17" s="97"/>
+      <c r="W17" s="97"/>
+      <c r="X17" s="71"/>
+      <c r="Y17" s="71"/>
+      <c r="Z17" s="71"/>
+      <c r="AA17" s="71"/>
+      <c r="AB17" s="71"/>
+      <c r="AC17" s="71"/>
+    </row>
+    <row r="18" spans="1:29">
+      <c r="A18" s="80">
+        <v>5</v>
+      </c>
+      <c r="B18" s="99" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="100">
+        <v>16</v>
+      </c>
+      <c r="D18" s="101"/>
+      <c r="E18" s="102"/>
+      <c r="F18" s="103"/>
+      <c r="G18" s="103"/>
+      <c r="H18" s="103"/>
+      <c r="I18" s="103"/>
+      <c r="J18" s="103"/>
+      <c r="K18" s="103"/>
+      <c r="L18" s="103"/>
+      <c r="M18" s="103"/>
+      <c r="N18" s="103"/>
+      <c r="O18" s="103"/>
+      <c r="P18" s="103"/>
+      <c r="Q18" s="103"/>
+      <c r="R18" s="103"/>
+      <c r="S18" s="103"/>
+      <c r="T18" s="103"/>
+      <c r="U18" s="103"/>
+      <c r="V18" s="97"/>
+      <c r="W18" s="97"/>
+      <c r="X18" s="71"/>
+      <c r="Y18" s="71"/>
+      <c r="Z18" s="71"/>
+      <c r="AA18" s="71"/>
+      <c r="AB18" s="71"/>
+      <c r="AC18" s="71"/>
+    </row>
+    <row r="19" spans="1:29">
+      <c r="A19" s="80">
+        <v>6</v>
+      </c>
+      <c r="B19" s="108" t="s">
+        <v>158</v>
+      </c>
+      <c r="C19" s="94">
+        <v>6</v>
+      </c>
+      <c r="D19" s="101"/>
+      <c r="E19" s="104"/>
+      <c r="F19" s="97"/>
+      <c r="G19" s="97"/>
+      <c r="H19" s="97"/>
+      <c r="I19" s="97"/>
+      <c r="J19" s="97"/>
+      <c r="K19" s="97"/>
+      <c r="L19" s="97"/>
+      <c r="M19" s="97"/>
+      <c r="N19" s="97"/>
+      <c r="O19" s="97"/>
+      <c r="P19" s="97"/>
+      <c r="Q19" s="97"/>
+      <c r="R19" s="97"/>
+      <c r="S19" s="97"/>
+      <c r="T19" s="97"/>
+      <c r="U19" s="97"/>
+      <c r="V19" s="97"/>
+      <c r="W19" s="97"/>
+      <c r="X19" s="71"/>
+      <c r="Y19" s="71"/>
+      <c r="Z19" s="71"/>
+      <c r="AA19" s="71"/>
+      <c r="AB19" s="71"/>
+      <c r="AC19" s="71"/>
+    </row>
+    <row r="20" spans="1:29">
+      <c r="A20" s="80">
+        <v>7</v>
+      </c>
+      <c r="B20" s="105" t="s">
+        <v>144</v>
+      </c>
+      <c r="C20" s="106">
+        <v>5</v>
+      </c>
+      <c r="D20" s="101"/>
+      <c r="E20" s="104"/>
+      <c r="F20" s="97"/>
+      <c r="G20" s="97"/>
+      <c r="H20" s="97"/>
+      <c r="I20" s="97"/>
+      <c r="J20" s="97"/>
+      <c r="K20" s="97"/>
+      <c r="L20" s="97"/>
+      <c r="M20" s="97"/>
+      <c r="N20" s="97"/>
+      <c r="O20" s="97"/>
+      <c r="P20" s="97"/>
+      <c r="Q20" s="97"/>
+      <c r="R20" s="97"/>
+      <c r="S20" s="97"/>
+      <c r="T20" s="97"/>
+      <c r="U20" s="97"/>
+      <c r="V20" s="97"/>
+      <c r="W20" s="97"/>
+      <c r="X20" s="71"/>
+      <c r="Y20" s="71"/>
+      <c r="Z20" s="71"/>
+      <c r="AA20" s="71"/>
+      <c r="AB20" s="71"/>
+      <c r="AC20" s="71"/>
+    </row>
+    <row r="21" spans="1:29">
+      <c r="A21" s="80">
+        <v>8</v>
+      </c>
+      <c r="B21" s="107" t="s">
+        <v>145</v>
+      </c>
+      <c r="C21" s="106">
+        <v>5</v>
+      </c>
+      <c r="D21" s="101"/>
+      <c r="E21" s="104"/>
+      <c r="F21" s="97"/>
+      <c r="G21" s="97"/>
+      <c r="H21" s="97"/>
+      <c r="I21" s="97"/>
+      <c r="J21" s="97"/>
+      <c r="K21" s="97"/>
+      <c r="L21" s="97"/>
+      <c r="M21" s="97"/>
+      <c r="N21" s="97"/>
+      <c r="O21" s="97"/>
+      <c r="P21" s="97"/>
+      <c r="Q21" s="97"/>
+      <c r="R21" s="97"/>
+      <c r="S21" s="97"/>
+      <c r="T21" s="97"/>
+      <c r="U21" s="97"/>
+      <c r="V21" s="97"/>
+      <c r="W21" s="97"/>
+      <c r="X21" s="71"/>
+      <c r="Y21" s="71"/>
+      <c r="Z21" s="71"/>
+      <c r="AA21" s="71"/>
+      <c r="AB21" s="71"/>
+      <c r="AC21" s="71"/>
+    </row>
+    <row r="22" spans="1:29">
+      <c r="A22" s="80">
+        <v>9</v>
+      </c>
+      <c r="B22" s="108" t="s">
+        <v>146</v>
+      </c>
+      <c r="C22" s="106">
+        <v>5</v>
+      </c>
+      <c r="D22" s="101"/>
+      <c r="E22" s="104"/>
+      <c r="F22" s="97"/>
+      <c r="G22" s="97"/>
+      <c r="H22" s="97"/>
+      <c r="I22" s="97"/>
+      <c r="J22" s="97"/>
+      <c r="K22" s="97"/>
+      <c r="L22" s="97"/>
+      <c r="M22" s="97"/>
+      <c r="N22" s="97"/>
+      <c r="O22" s="97"/>
+      <c r="P22" s="97"/>
+      <c r="Q22" s="97"/>
+      <c r="R22" s="97"/>
+      <c r="S22" s="97"/>
+      <c r="T22" s="97"/>
+      <c r="U22" s="97"/>
+      <c r="V22" s="97"/>
+      <c r="W22" s="97"/>
+      <c r="X22" s="71"/>
+      <c r="Y22" s="71"/>
+      <c r="Z22" s="71"/>
+      <c r="AA22" s="71"/>
+      <c r="AB22" s="71"/>
+      <c r="AC22" s="71"/>
+    </row>
+    <row r="23" spans="1:29">
+      <c r="A23" s="80">
+        <v>10</v>
+      </c>
+      <c r="B23" s="107" t="s">
+        <v>147</v>
+      </c>
+      <c r="C23" s="106">
+        <v>5</v>
+      </c>
+      <c r="D23" s="101"/>
+      <c r="E23" s="104"/>
+      <c r="F23" s="97"/>
+      <c r="G23" s="97"/>
+      <c r="H23" s="97"/>
+      <c r="I23" s="97"/>
+      <c r="J23" s="97"/>
+      <c r="K23" s="97"/>
+      <c r="L23" s="97"/>
+      <c r="M23" s="97"/>
+      <c r="N23" s="97"/>
+      <c r="O23" s="97"/>
+      <c r="P23" s="97"/>
+      <c r="Q23" s="97"/>
+      <c r="R23" s="97"/>
+      <c r="S23" s="97"/>
+      <c r="T23" s="97"/>
+      <c r="U23" s="97"/>
+      <c r="V23" s="97"/>
+      <c r="W23" s="97"/>
+      <c r="X23" s="71"/>
+      <c r="Y23" s="71"/>
+      <c r="Z23" s="71"/>
+      <c r="AA23" s="71"/>
+      <c r="AB23" s="71"/>
+      <c r="AC23" s="71"/>
+    </row>
+    <row r="24" spans="1:29">
+      <c r="A24" s="80">
+        <v>11</v>
+      </c>
+      <c r="B24" s="109" t="s">
+        <v>175</v>
+      </c>
+      <c r="C24" s="106">
+        <v>5</v>
+      </c>
+      <c r="D24" s="101"/>
+      <c r="E24" s="104"/>
+      <c r="F24" s="97"/>
+      <c r="G24" s="97"/>
+      <c r="H24" s="97"/>
+      <c r="I24" s="97"/>
+      <c r="J24" s="97"/>
+      <c r="K24" s="97"/>
+      <c r="L24" s="97"/>
+      <c r="M24" s="97"/>
+      <c r="N24" s="97"/>
+      <c r="O24" s="97"/>
+      <c r="P24" s="97"/>
+      <c r="Q24" s="97"/>
+      <c r="R24" s="97"/>
+      <c r="S24" s="97"/>
+      <c r="T24" s="97"/>
+      <c r="U24" s="97"/>
+      <c r="V24" s="97"/>
+      <c r="W24" s="97"/>
+      <c r="X24" s="71"/>
+      <c r="Y24" s="71"/>
+      <c r="Z24" s="71"/>
+      <c r="AA24" s="71"/>
+      <c r="AB24" s="71"/>
+      <c r="AC24" s="71"/>
+    </row>
+    <row r="25" spans="1:29">
+      <c r="A25" s="80">
+        <v>12</v>
+      </c>
+      <c r="B25" s="109" t="s">
+        <v>148</v>
+      </c>
+      <c r="C25" s="106">
+        <v>7</v>
+      </c>
+      <c r="D25" s="101"/>
+      <c r="E25" s="104"/>
+      <c r="F25" s="97"/>
+      <c r="G25" s="97"/>
+      <c r="H25" s="97"/>
+      <c r="I25" s="97"/>
+      <c r="J25" s="97"/>
+      <c r="K25" s="97"/>
+      <c r="L25" s="97"/>
+      <c r="M25" s="97"/>
+      <c r="N25" s="97"/>
+      <c r="O25" s="97"/>
+      <c r="P25" s="97"/>
+      <c r="Q25" s="97"/>
+      <c r="R25" s="97"/>
+      <c r="S25" s="97"/>
+      <c r="T25" s="97"/>
+      <c r="U25" s="97"/>
+      <c r="V25" s="97"/>
+      <c r="W25" s="97"/>
+      <c r="X25" s="71"/>
+      <c r="Y25" s="71"/>
+      <c r="Z25" s="71"/>
+      <c r="AA25" s="71"/>
+      <c r="AB25" s="71"/>
+      <c r="AC25" s="71"/>
+    </row>
+    <row r="26" spans="1:29">
+      <c r="A26" s="80">
+        <v>13</v>
+      </c>
+      <c r="B26" s="110" t="s">
+        <v>149</v>
+      </c>
+      <c r="C26" s="106">
+        <v>5</v>
+      </c>
+      <c r="D26" s="101"/>
+      <c r="E26" s="104"/>
+      <c r="F26" s="97"/>
+      <c r="G26" s="97"/>
+      <c r="H26" s="97"/>
+      <c r="I26" s="97"/>
+      <c r="J26" s="97"/>
+      <c r="K26" s="97"/>
+      <c r="L26" s="97"/>
+      <c r="M26" s="97"/>
+      <c r="N26" s="97"/>
+      <c r="O26" s="97"/>
+      <c r="P26" s="97"/>
+      <c r="Q26" s="97"/>
+      <c r="R26" s="97"/>
+      <c r="S26" s="97"/>
+      <c r="T26" s="97"/>
+      <c r="U26" s="97"/>
+      <c r="V26" s="97"/>
+      <c r="W26" s="97"/>
+      <c r="X26" s="71"/>
+      <c r="Y26" s="71"/>
+      <c r="Z26" s="71"/>
+      <c r="AA26" s="71"/>
+      <c r="AB26" s="71"/>
+      <c r="AC26" s="71"/>
+    </row>
+    <row r="27" spans="1:29">
+      <c r="A27" s="80">
+        <v>14</v>
+      </c>
+      <c r="B27" s="111" t="s">
+        <v>150</v>
+      </c>
+      <c r="C27" s="106">
+        <v>6</v>
+      </c>
+      <c r="D27" s="101"/>
+      <c r="E27" s="104"/>
+      <c r="F27" s="97"/>
+      <c r="G27" s="97"/>
+      <c r="H27" s="97"/>
+      <c r="I27" s="97"/>
+      <c r="J27" s="97"/>
+      <c r="K27" s="97"/>
+      <c r="L27" s="97"/>
+      <c r="M27" s="97"/>
+      <c r="N27" s="97"/>
+      <c r="O27" s="97"/>
+      <c r="P27" s="97"/>
+      <c r="Q27" s="97"/>
+      <c r="R27" s="97"/>
+      <c r="S27" s="97"/>
+      <c r="T27" s="97"/>
+      <c r="U27" s="97"/>
+      <c r="V27" s="97"/>
+      <c r="W27" s="97"/>
+      <c r="X27" s="71"/>
+      <c r="Y27" s="71"/>
+      <c r="Z27" s="71"/>
+      <c r="AA27" s="71"/>
+      <c r="AB27" s="71"/>
+      <c r="AC27" s="71"/>
+    </row>
+    <row r="28" spans="1:29">
+      <c r="A28" s="80">
+        <v>15</v>
+      </c>
+      <c r="B28" s="112" t="s">
+        <v>151</v>
+      </c>
+      <c r="C28" s="106">
+        <v>6</v>
+      </c>
+      <c r="D28" s="101"/>
+      <c r="E28" s="104"/>
+      <c r="F28" s="97"/>
+      <c r="G28" s="97"/>
+      <c r="H28" s="97"/>
+      <c r="I28" s="97"/>
+      <c r="J28" s="97"/>
+      <c r="K28" s="97"/>
+      <c r="L28" s="97"/>
+      <c r="M28" s="97"/>
+      <c r="N28" s="97"/>
+      <c r="O28" s="97"/>
+      <c r="P28" s="97"/>
+      <c r="Q28" s="97"/>
+      <c r="R28" s="97"/>
+      <c r="S28" s="97"/>
+      <c r="T28" s="97"/>
+      <c r="U28" s="97"/>
+      <c r="V28" s="97"/>
+      <c r="W28" s="97"/>
+      <c r="X28" s="71"/>
+      <c r="Y28" s="71"/>
+      <c r="Z28" s="71"/>
+      <c r="AA28" s="71"/>
+      <c r="AB28" s="71"/>
+      <c r="AC28" s="71"/>
+    </row>
+    <row r="29" spans="1:29">
+      <c r="A29" s="80">
+        <v>16</v>
+      </c>
+      <c r="B29" s="105" t="s">
+        <v>152</v>
+      </c>
+      <c r="C29" s="106">
+        <v>6</v>
+      </c>
+      <c r="D29" s="101"/>
+      <c r="E29" s="104"/>
+      <c r="F29" s="97"/>
+      <c r="G29" s="97"/>
+      <c r="H29" s="97"/>
+      <c r="I29" s="97"/>
+      <c r="J29" s="97"/>
+      <c r="K29" s="97"/>
+      <c r="L29" s="97"/>
+      <c r="M29" s="97"/>
+      <c r="N29" s="97"/>
+      <c r="O29" s="97"/>
+      <c r="P29" s="97"/>
+      <c r="Q29" s="97"/>
+      <c r="R29" s="97"/>
+      <c r="S29" s="97"/>
+      <c r="T29" s="97"/>
+      <c r="U29" s="97"/>
+      <c r="V29" s="97"/>
+      <c r="W29" s="97"/>
+      <c r="X29" s="71"/>
+      <c r="Y29" s="71"/>
+      <c r="Z29" s="71"/>
+      <c r="AA29" s="71"/>
+      <c r="AB29" s="71"/>
+      <c r="AC29" s="71"/>
+    </row>
+    <row r="30" spans="1:29">
+      <c r="A30" s="80">
+        <v>17</v>
+      </c>
+      <c r="B30" s="111" t="s">
+        <v>153</v>
+      </c>
+      <c r="C30" s="106">
+        <v>7</v>
+      </c>
+      <c r="D30" s="101"/>
+      <c r="E30" s="104"/>
+      <c r="F30" s="97"/>
+      <c r="G30" s="97"/>
+      <c r="H30" s="97"/>
+      <c r="I30" s="97"/>
+      <c r="J30" s="97"/>
+      <c r="K30" s="97"/>
+      <c r="L30" s="97"/>
+      <c r="M30" s="97"/>
+      <c r="N30" s="97"/>
+      <c r="O30" s="97"/>
+      <c r="P30" s="97"/>
+      <c r="Q30" s="97"/>
+      <c r="R30" s="97"/>
+      <c r="S30" s="97"/>
+      <c r="T30" s="97"/>
+      <c r="U30" s="97"/>
+      <c r="V30" s="97"/>
+      <c r="W30" s="97"/>
+      <c r="X30" s="71"/>
+      <c r="Y30" s="71"/>
+      <c r="Z30" s="71"/>
+      <c r="AA30" s="71"/>
+      <c r="AB30" s="71"/>
+      <c r="AC30" s="71"/>
+    </row>
+    <row r="31" spans="1:29">
+      <c r="A31" s="80">
+        <v>18</v>
+      </c>
+      <c r="B31" s="112" t="s">
+        <v>154</v>
+      </c>
+      <c r="C31" s="106">
+        <v>7</v>
+      </c>
+      <c r="D31" s="101"/>
+      <c r="E31" s="104"/>
+      <c r="F31" s="97"/>
+      <c r="G31" s="97"/>
+      <c r="H31" s="97"/>
+      <c r="I31" s="97"/>
+      <c r="J31" s="97"/>
+      <c r="K31" s="97"/>
+      <c r="L31" s="97"/>
+      <c r="M31" s="97"/>
+      <c r="N31" s="97"/>
+      <c r="O31" s="97"/>
+      <c r="P31" s="97"/>
+      <c r="Q31" s="97"/>
+      <c r="R31" s="97"/>
+      <c r="S31" s="97"/>
+      <c r="T31" s="97"/>
+      <c r="U31" s="97"/>
+      <c r="V31" s="97"/>
+      <c r="W31" s="97"/>
+      <c r="X31" s="71"/>
+      <c r="Y31" s="71"/>
+      <c r="Z31" s="71"/>
+      <c r="AA31" s="71"/>
+      <c r="AB31" s="71"/>
+      <c r="AC31" s="71"/>
+    </row>
+    <row r="32" spans="1:29">
+      <c r="A32" s="80">
+        <v>19</v>
+      </c>
+      <c r="B32" s="105" t="s">
+        <v>155</v>
+      </c>
+      <c r="C32" s="106">
+        <v>7</v>
+      </c>
+      <c r="D32" s="101"/>
+      <c r="E32" s="104"/>
+      <c r="F32" s="97"/>
+      <c r="G32" s="97"/>
+      <c r="H32" s="97"/>
+      <c r="I32" s="97"/>
+      <c r="J32" s="97"/>
+      <c r="K32" s="97"/>
+      <c r="L32" s="97"/>
+      <c r="M32" s="97"/>
+      <c r="N32" s="97"/>
+      <c r="O32" s="97"/>
+      <c r="P32" s="97"/>
+      <c r="Q32" s="97"/>
+      <c r="R32" s="97"/>
+      <c r="S32" s="97"/>
+      <c r="T32" s="97"/>
+      <c r="U32" s="97"/>
+      <c r="V32" s="97"/>
+      <c r="W32" s="97"/>
+      <c r="X32" s="71"/>
+      <c r="Y32" s="71"/>
+      <c r="Z32" s="71"/>
+      <c r="AA32" s="71"/>
+      <c r="AB32" s="71"/>
+      <c r="AC32" s="71"/>
+    </row>
+    <row r="33" spans="1:29">
+      <c r="A33" s="80">
+        <v>20</v>
+      </c>
+      <c r="B33" s="113" t="s">
+        <v>156</v>
+      </c>
+      <c r="C33" s="114">
+        <v>5</v>
+      </c>
+      <c r="D33" s="101"/>
+      <c r="E33" s="104"/>
+      <c r="F33" s="97"/>
+      <c r="G33" s="97"/>
+      <c r="H33" s="97"/>
+      <c r="I33" s="97"/>
+      <c r="J33" s="97"/>
+      <c r="K33" s="97"/>
+      <c r="L33" s="97"/>
+      <c r="M33" s="97"/>
+      <c r="N33" s="97"/>
+      <c r="O33" s="97"/>
+      <c r="P33" s="97"/>
+      <c r="Q33" s="97"/>
+      <c r="R33" s="97"/>
+      <c r="S33" s="97"/>
+      <c r="T33" s="97"/>
+      <c r="U33" s="97"/>
+      <c r="V33" s="97"/>
+      <c r="W33" s="97"/>
+      <c r="X33" s="71"/>
+      <c r="Y33" s="71"/>
+      <c r="Z33" s="71"/>
+      <c r="AA33" s="71"/>
+      <c r="AB33" s="71"/>
+      <c r="AC33" s="71"/>
+    </row>
+    <row r="34" spans="1:29">
+      <c r="A34" s="80">
+        <v>21</v>
+      </c>
+      <c r="B34" s="115" t="s">
+        <v>157</v>
+      </c>
+      <c r="C34" s="114">
+        <v>5</v>
+      </c>
+      <c r="D34" s="101"/>
+      <c r="E34" s="104"/>
+      <c r="F34" s="97"/>
+      <c r="G34" s="97"/>
+      <c r="H34" s="97"/>
+      <c r="I34" s="97"/>
+      <c r="J34" s="97"/>
+      <c r="K34" s="97"/>
+      <c r="L34" s="97"/>
+      <c r="M34" s="97"/>
+      <c r="N34" s="97"/>
+      <c r="O34" s="97"/>
+      <c r="P34" s="97"/>
+      <c r="Q34" s="97"/>
+      <c r="R34" s="97"/>
+      <c r="S34" s="97"/>
+      <c r="T34" s="97"/>
+      <c r="U34" s="97"/>
+      <c r="V34" s="97"/>
+      <c r="W34" s="97"/>
+      <c r="X34" s="71"/>
+      <c r="Y34" s="71"/>
+      <c r="Z34" s="71"/>
+      <c r="AA34" s="71"/>
+      <c r="AB34" s="71"/>
+      <c r="AC34" s="71"/>
+    </row>
+    <row r="35" spans="1:29">
+      <c r="A35" s="80">
+        <v>23</v>
+      </c>
+      <c r="B35" s="116" t="s">
+        <v>159</v>
+      </c>
+      <c r="C35" s="106">
+        <v>3</v>
+      </c>
+      <c r="D35" s="101"/>
+      <c r="E35" s="104"/>
+      <c r="F35" s="97"/>
+      <c r="G35" s="97"/>
+      <c r="H35" s="97"/>
+      <c r="I35" s="97"/>
+      <c r="J35" s="97"/>
+      <c r="K35" s="97"/>
+      <c r="L35" s="97"/>
+      <c r="M35" s="97"/>
+      <c r="N35" s="97"/>
+      <c r="O35" s="97"/>
+      <c r="P35" s="97"/>
+      <c r="Q35" s="97"/>
+      <c r="R35" s="97"/>
+      <c r="S35" s="97"/>
+      <c r="T35" s="97"/>
+      <c r="U35" s="97"/>
+      <c r="V35" s="97"/>
+      <c r="W35" s="97"/>
+      <c r="X35" s="71"/>
+      <c r="Y35" s="71"/>
+      <c r="Z35" s="71"/>
+      <c r="AA35" s="71"/>
+      <c r="AB35" s="71"/>
+      <c r="AC35" s="71"/>
+    </row>
+    <row r="36" spans="1:29">
+      <c r="A36" s="80">
+        <v>24</v>
+      </c>
+      <c r="B36" s="117" t="s">
+        <v>160</v>
+      </c>
+      <c r="C36" s="118">
+        <v>10</v>
+      </c>
+      <c r="D36" s="101"/>
+      <c r="E36" s="119"/>
+      <c r="F36" s="120"/>
+      <c r="G36" s="120"/>
+      <c r="H36" s="120"/>
+      <c r="I36" s="120"/>
+      <c r="J36" s="120"/>
+      <c r="K36" s="120"/>
+      <c r="L36" s="120"/>
+      <c r="M36" s="120"/>
+      <c r="N36" s="120"/>
+      <c r="O36" s="120"/>
+      <c r="P36" s="120"/>
+      <c r="Q36" s="120"/>
+      <c r="R36" s="120"/>
+      <c r="S36" s="120"/>
+      <c r="T36" s="97"/>
+      <c r="U36" s="97"/>
+      <c r="V36" s="97"/>
+      <c r="W36" s="97"/>
+      <c r="X36" s="71"/>
+      <c r="Y36" s="71"/>
+      <c r="Z36" s="71"/>
+      <c r="AA36" s="71"/>
+      <c r="AB36" s="71"/>
+      <c r="AC36" s="71"/>
+    </row>
+    <row r="37" spans="1:29">
+      <c r="A37" s="80">
+        <v>25</v>
+      </c>
+      <c r="B37" s="121" t="s">
+        <v>161</v>
+      </c>
+      <c r="C37" s="118">
+        <v>5</v>
+      </c>
+      <c r="D37" s="101"/>
+      <c r="E37" s="119"/>
+      <c r="F37" s="120"/>
+      <c r="G37" s="120"/>
+      <c r="H37" s="120"/>
+      <c r="I37" s="120"/>
+      <c r="J37" s="120"/>
+      <c r="K37" s="120"/>
+      <c r="L37" s="120"/>
+      <c r="M37" s="120"/>
+      <c r="N37" s="120"/>
+      <c r="O37" s="120"/>
+      <c r="P37" s="120"/>
+      <c r="Q37" s="120"/>
+      <c r="R37" s="120"/>
+      <c r="S37" s="120"/>
+      <c r="T37" s="97"/>
+      <c r="U37" s="97"/>
+      <c r="V37" s="97"/>
+      <c r="W37" s="97"/>
+      <c r="X37" s="71"/>
+      <c r="Y37" s="71"/>
+      <c r="Z37" s="71"/>
+      <c r="AA37" s="71"/>
+      <c r="AB37" s="71"/>
+      <c r="AC37" s="71"/>
+    </row>
+    <row r="38" spans="1:29">
+      <c r="A38" s="80">
+        <v>26</v>
+      </c>
+      <c r="B38" s="122" t="s">
+        <v>162</v>
+      </c>
+      <c r="C38" s="114">
+        <v>6</v>
+      </c>
+      <c r="D38" s="101"/>
+      <c r="E38" s="119"/>
+      <c r="F38" s="120"/>
+      <c r="G38" s="120"/>
+      <c r="H38" s="120"/>
+      <c r="I38" s="120"/>
+      <c r="J38" s="120"/>
+      <c r="K38" s="120"/>
+      <c r="L38" s="120"/>
+      <c r="M38" s="120"/>
+      <c r="N38" s="120"/>
+      <c r="O38" s="120"/>
+      <c r="P38" s="120"/>
+      <c r="Q38" s="120"/>
+      <c r="R38" s="120"/>
+      <c r="S38" s="120"/>
+      <c r="T38" s="97"/>
+      <c r="U38" s="97"/>
+      <c r="V38" s="97"/>
+      <c r="W38" s="97"/>
+      <c r="X38" s="71"/>
+      <c r="Y38" s="71"/>
+      <c r="Z38" s="71"/>
+      <c r="AA38" s="71"/>
+      <c r="AB38" s="71"/>
+      <c r="AC38" s="71"/>
+    </row>
+    <row r="39" spans="1:29">
+      <c r="A39" s="80">
+        <v>27</v>
+      </c>
+      <c r="B39" s="121" t="s">
+        <v>163</v>
+      </c>
+      <c r="C39" s="118">
+        <v>5</v>
+      </c>
+      <c r="D39" s="101"/>
+      <c r="E39" s="119"/>
+      <c r="F39" s="120"/>
+      <c r="G39" s="120"/>
+      <c r="H39" s="120"/>
+      <c r="I39" s="120"/>
+      <c r="J39" s="120"/>
+      <c r="K39" s="120"/>
+      <c r="L39" s="120"/>
+      <c r="M39" s="120"/>
+      <c r="N39" s="120"/>
+      <c r="O39" s="120"/>
+      <c r="P39" s="120"/>
+      <c r="Q39" s="120"/>
+      <c r="R39" s="120"/>
+      <c r="S39" s="120"/>
+      <c r="T39" s="97"/>
+      <c r="U39" s="97"/>
+      <c r="V39" s="97"/>
+      <c r="W39" s="97"/>
+      <c r="X39" s="71"/>
+      <c r="Y39" s="71"/>
+      <c r="Z39" s="71"/>
+      <c r="AA39" s="71"/>
+      <c r="AB39" s="71"/>
+      <c r="AC39" s="71"/>
+    </row>
+    <row r="40" spans="1:29">
+      <c r="A40" s="80">
+        <v>28</v>
+      </c>
+      <c r="B40" s="123" t="s">
+        <v>174</v>
+      </c>
+      <c r="C40" s="118">
+        <v>5</v>
+      </c>
+      <c r="D40" s="101"/>
+      <c r="E40" s="119"/>
+      <c r="F40" s="120"/>
+      <c r="G40" s="120"/>
+      <c r="H40" s="120"/>
+      <c r="I40" s="120"/>
+      <c r="J40" s="120"/>
+      <c r="K40" s="120"/>
+      <c r="L40" s="120"/>
+      <c r="M40" s="120"/>
+      <c r="N40" s="120"/>
+      <c r="O40" s="120"/>
+      <c r="P40" s="120"/>
+      <c r="Q40" s="120"/>
+      <c r="R40" s="120"/>
+      <c r="S40" s="120"/>
+      <c r="T40" s="97"/>
+      <c r="U40" s="97"/>
+      <c r="V40" s="97"/>
+      <c r="W40" s="97"/>
+      <c r="X40" s="71"/>
+      <c r="Y40" s="71"/>
+      <c r="Z40" s="71"/>
+      <c r="AA40" s="71"/>
+      <c r="AB40" s="71"/>
+      <c r="AC40" s="71"/>
+    </row>
+    <row r="41" spans="1:29">
+      <c r="A41" s="80">
+        <v>29</v>
+      </c>
+      <c r="B41" s="123" t="s">
+        <v>176</v>
+      </c>
+      <c r="C41" s="118">
+        <v>3</v>
+      </c>
+      <c r="D41" s="101"/>
+      <c r="E41" s="119"/>
+      <c r="F41" s="120"/>
+      <c r="G41" s="120"/>
+      <c r="H41" s="120"/>
+      <c r="I41" s="120"/>
+      <c r="J41" s="120"/>
+      <c r="K41" s="120"/>
+      <c r="L41" s="120"/>
+      <c r="M41" s="120"/>
+      <c r="N41" s="120"/>
+      <c r="O41" s="120"/>
+      <c r="P41" s="120"/>
+      <c r="Q41" s="120"/>
+      <c r="R41" s="120"/>
+      <c r="S41" s="120"/>
+      <c r="T41" s="97"/>
+      <c r="U41" s="97"/>
+      <c r="V41" s="97"/>
+      <c r="W41" s="97"/>
+      <c r="X41" s="71"/>
+      <c r="Y41" s="71"/>
+      <c r="Z41" s="71"/>
+      <c r="AA41" s="71"/>
+      <c r="AB41" s="71"/>
+      <c r="AC41" s="71"/>
+    </row>
+    <row r="42" spans="1:29">
+      <c r="A42" s="80">
+        <v>29</v>
+      </c>
+      <c r="B42" s="123" t="s">
+        <v>164</v>
+      </c>
+      <c r="C42" s="118">
+        <v>6</v>
+      </c>
+      <c r="D42" s="101"/>
+      <c r="E42" s="119"/>
+      <c r="F42" s="120"/>
+      <c r="G42" s="120"/>
+      <c r="H42" s="120"/>
+      <c r="I42" s="120"/>
+      <c r="J42" s="120"/>
+      <c r="K42" s="120"/>
+      <c r="L42" s="120"/>
+      <c r="M42" s="120"/>
+      <c r="N42" s="120"/>
+      <c r="O42" s="120"/>
+      <c r="P42" s="120"/>
+      <c r="Q42" s="120"/>
+      <c r="R42" s="120"/>
+      <c r="S42" s="120"/>
+      <c r="T42" s="97"/>
+      <c r="U42" s="97"/>
+      <c r="V42" s="97"/>
+      <c r="W42" s="97"/>
+      <c r="X42" s="71"/>
+      <c r="Y42" s="71"/>
+      <c r="Z42" s="71"/>
+      <c r="AA42" s="71"/>
+      <c r="AB42" s="71"/>
+      <c r="AC42" s="71"/>
+    </row>
+    <row r="43" spans="1:29">
+      <c r="A43" s="80">
+        <v>30</v>
+      </c>
+      <c r="B43" s="123" t="s">
+        <v>165</v>
+      </c>
+      <c r="C43" s="118">
+        <v>8</v>
+      </c>
+      <c r="D43" s="101"/>
+      <c r="E43" s="119"/>
+      <c r="F43" s="120"/>
+      <c r="G43" s="120"/>
+      <c r="H43" s="120"/>
+      <c r="I43" s="120"/>
+      <c r="J43" s="120"/>
+      <c r="K43" s="120"/>
+      <c r="L43" s="120"/>
+      <c r="M43" s="120"/>
+      <c r="N43" s="120"/>
+      <c r="O43" s="120"/>
+      <c r="P43" s="120"/>
+      <c r="Q43" s="120"/>
+      <c r="R43" s="120"/>
+      <c r="S43" s="120"/>
+      <c r="T43" s="97"/>
+      <c r="U43" s="97"/>
+      <c r="V43" s="97"/>
+      <c r="W43" s="97"/>
+      <c r="X43" s="71"/>
+      <c r="Y43" s="71"/>
+      <c r="Z43" s="71"/>
+      <c r="AA43" s="71"/>
+      <c r="AB43" s="71"/>
+      <c r="AC43" s="71"/>
+    </row>
+    <row r="44" spans="1:29">
+      <c r="A44" s="80">
+        <v>31</v>
+      </c>
+      <c r="B44" s="115" t="s">
+        <v>166</v>
+      </c>
+      <c r="C44" s="124">
+        <v>4</v>
+      </c>
+      <c r="D44" s="101"/>
+      <c r="E44" s="119"/>
+      <c r="F44" s="101"/>
+      <c r="G44" s="101"/>
+      <c r="H44" s="101"/>
+      <c r="I44" s="101"/>
+      <c r="J44" s="101"/>
+      <c r="K44" s="101"/>
+      <c r="L44" s="120"/>
+      <c r="M44" s="101"/>
+      <c r="N44" s="101"/>
+      <c r="O44" s="101"/>
+      <c r="P44" s="101"/>
+      <c r="Q44" s="101"/>
+      <c r="R44" s="101"/>
+      <c r="S44" s="101"/>
+      <c r="T44" s="97"/>
+      <c r="U44" s="97"/>
+      <c r="V44" s="97"/>
+      <c r="W44" s="97"/>
+      <c r="X44" s="71"/>
+      <c r="Y44" s="71"/>
+      <c r="Z44" s="71"/>
+      <c r="AA44" s="71"/>
+      <c r="AB44" s="71"/>
+      <c r="AC44" s="71"/>
+    </row>
+    <row r="45" spans="1:29">
+      <c r="A45" s="80">
+        <v>32</v>
+      </c>
+      <c r="B45" s="125" t="s">
+        <v>167</v>
+      </c>
+      <c r="C45" s="114">
+        <v>4</v>
+      </c>
+      <c r="D45" s="101"/>
+      <c r="E45" s="119"/>
+      <c r="F45" s="101"/>
+      <c r="G45" s="101"/>
+      <c r="H45" s="101"/>
+      <c r="I45" s="101"/>
+      <c r="J45" s="101"/>
+      <c r="K45" s="101"/>
+      <c r="L45" s="120"/>
+      <c r="M45" s="101"/>
+      <c r="N45" s="101"/>
+      <c r="O45" s="101"/>
+      <c r="P45" s="101"/>
+      <c r="Q45" s="101"/>
+      <c r="R45" s="101"/>
+      <c r="S45" s="101"/>
+      <c r="T45" s="97"/>
+      <c r="U45" s="97"/>
+      <c r="V45" s="97"/>
+      <c r="W45" s="97"/>
+      <c r="X45" s="71"/>
+      <c r="Y45" s="71"/>
+      <c r="Z45" s="71"/>
+      <c r="AA45" s="71"/>
+      <c r="AB45" s="71"/>
+      <c r="AC45" s="71"/>
+    </row>
+    <row r="46" spans="1:29">
+      <c r="A46" s="80">
+        <v>33</v>
+      </c>
+      <c r="B46" s="117" t="s">
+        <v>168</v>
+      </c>
+      <c r="C46" s="118">
+        <v>4</v>
+      </c>
+      <c r="D46" s="101"/>
+      <c r="E46" s="119"/>
+      <c r="F46" s="101"/>
+      <c r="G46" s="101"/>
+      <c r="H46" s="101"/>
+      <c r="I46" s="101"/>
+      <c r="J46" s="101"/>
+      <c r="K46" s="101"/>
+      <c r="L46" s="120"/>
+      <c r="M46" s="101"/>
+      <c r="N46" s="101"/>
+      <c r="O46" s="101"/>
+      <c r="P46" s="101"/>
+      <c r="Q46" s="101"/>
+      <c r="R46" s="101"/>
+      <c r="S46" s="101"/>
+      <c r="T46" s="97"/>
+      <c r="U46" s="97"/>
+      <c r="V46" s="97"/>
+      <c r="W46" s="97"/>
+      <c r="X46" s="71"/>
+      <c r="Y46" s="71"/>
+      <c r="Z46" s="71"/>
+      <c r="AA46" s="71"/>
+      <c r="AB46" s="71"/>
+      <c r="AC46" s="71"/>
+    </row>
+    <row r="47" spans="1:29" ht="15" thickBot="1">
+      <c r="A47" s="80">
+        <v>34</v>
+      </c>
+      <c r="B47" s="117" t="s">
+        <v>169</v>
+      </c>
+      <c r="C47" s="114">
+        <v>12</v>
+      </c>
+      <c r="D47" s="101"/>
+      <c r="E47" s="119"/>
+      <c r="F47" s="70"/>
+      <c r="G47" s="70"/>
+      <c r="H47" s="70"/>
+      <c r="I47" s="70"/>
+      <c r="J47" s="70"/>
+      <c r="K47" s="70"/>
+      <c r="L47" s="120"/>
+      <c r="M47" s="70"/>
+      <c r="N47" s="70"/>
+      <c r="O47" s="70"/>
+      <c r="P47" s="70"/>
+      <c r="Q47" s="70"/>
+      <c r="R47" s="70"/>
+      <c r="S47" s="70"/>
+      <c r="T47" s="103"/>
+      <c r="U47" s="126"/>
+      <c r="V47" s="126"/>
+      <c r="W47" s="126"/>
+      <c r="X47" s="71"/>
+      <c r="Y47" s="71"/>
+      <c r="Z47" s="71"/>
+      <c r="AA47" s="71"/>
+      <c r="AB47" s="71"/>
+      <c r="AC47" s="71"/>
+    </row>
+    <row r="48" spans="1:29" ht="54" thickTop="1">
+      <c r="A48" s="127"/>
+      <c r="B48" s="128" t="s">
+        <v>77</v>
+      </c>
+      <c r="C48" s="129"/>
+      <c r="D48" s="129"/>
+      <c r="E48" s="130"/>
+      <c r="F48" s="129"/>
+      <c r="G48" s="129"/>
+      <c r="H48" s="129"/>
+      <c r="I48" s="129"/>
+      <c r="J48" s="129"/>
+      <c r="K48" s="129"/>
+      <c r="L48" s="131"/>
+      <c r="M48" s="129"/>
+      <c r="N48" s="129"/>
+      <c r="O48" s="129"/>
+      <c r="P48" s="132" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q48" s="129"/>
+      <c r="R48" s="129"/>
+      <c r="S48" s="129"/>
+      <c r="T48" s="129"/>
+      <c r="U48" s="133"/>
+      <c r="V48" s="134"/>
+      <c r="W48" s="133" t="s">
+        <v>171</v>
+      </c>
+      <c r="X48" s="71"/>
+      <c r="Y48" s="71"/>
+      <c r="Z48" s="71"/>
+      <c r="AA48" s="71"/>
+      <c r="AB48" s="71"/>
+      <c r="AC48" s="71"/>
+    </row>
+    <row r="49" spans="1:29" ht="66">
+      <c r="A49" s="135"/>
+      <c r="B49" s="136" t="s">
+        <v>81</v>
+      </c>
+      <c r="C49" s="137"/>
+      <c r="D49" s="137"/>
+      <c r="E49" s="138"/>
+      <c r="F49" s="97"/>
+      <c r="G49" s="97"/>
+      <c r="H49" s="97"/>
+      <c r="I49" s="97"/>
+      <c r="J49" s="97"/>
+      <c r="K49" s="97"/>
+      <c r="L49" s="71"/>
+      <c r="M49" s="97"/>
+      <c r="N49" s="139"/>
+      <c r="O49" s="97"/>
+      <c r="P49" s="140"/>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="71"/>
+      <c r="S49" s="139" t="s">
+        <v>172</v>
+      </c>
+      <c r="T49" s="71"/>
+      <c r="U49" s="141"/>
+      <c r="V49" s="141"/>
+      <c r="W49" s="141" t="s">
+        <v>173</v>
+      </c>
+      <c r="X49" s="71"/>
+      <c r="Y49" s="71"/>
+      <c r="Z49" s="71"/>
+      <c r="AA49" s="71"/>
+      <c r="AB49" s="71"/>
+      <c r="AC49" s="71"/>
+    </row>
+    <row r="50" spans="1:29" ht="15" thickBot="1">
+      <c r="A50" s="142"/>
+      <c r="B50" s="143" t="s">
+        <v>84</v>
+      </c>
+      <c r="C50" s="144"/>
+      <c r="D50" s="144"/>
+      <c r="E50" s="145"/>
+      <c r="F50" s="146"/>
+      <c r="G50" s="146"/>
+      <c r="H50" s="146"/>
+      <c r="I50" s="146"/>
+      <c r="J50" s="146"/>
+      <c r="K50" s="146"/>
+      <c r="L50" s="146"/>
+      <c r="M50" s="146"/>
+      <c r="N50" s="146"/>
+      <c r="O50" s="146"/>
+      <c r="P50" s="147"/>
+      <c r="Q50" s="146"/>
+      <c r="R50" s="146"/>
+      <c r="S50" s="146"/>
+      <c r="T50" s="146"/>
+      <c r="U50" s="148"/>
+      <c r="V50" s="148"/>
+      <c r="W50" s="148"/>
+      <c r="X50" s="71"/>
+      <c r="Y50" s="71"/>
+      <c r="Z50" s="71"/>
+      <c r="AA50" s="71"/>
+      <c r="AB50" s="71"/>
+      <c r="AC50" s="71"/>
+    </row>
+    <row r="51" spans="1:29" ht="15" thickTop="1"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E8:Q8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A7:I25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="29.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="7" spans="1:9" ht="23.4">
+      <c r="B7" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15" thickBot="1"/>
+    <row r="10" spans="1:9">
+      <c r="A10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="6">
+        <v>7026116</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I11" s="7"/>
+    </row>
+    <row r="12" spans="1:9" ht="15" thickBot="1">
+      <c r="A12" s="8"/>
+      <c r="B12" s="9"/>
+      <c r="H12" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I12" s="9"/>
+    </row>
+    <row r="15" spans="1:9" ht="21">
+      <c r="B15" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" s="64"/>
+      <c r="D15" s="64"/>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>94</v>
+      </c>
+      <c r="B19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="B20" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="B21" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="B22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="B23" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="B24" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="B25" t="s">
+        <v>88</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B15:D15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R44"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18">
       <c r="A1" s="11"/>
       <c r="D1" s="11"/>
       <c r="E1" s="11"/>
@@ -10047,7 +16015,7 @@
       <c r="P1" s="11"/>
       <c r="Q1" s="11"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18">
       <c r="A2" s="11"/>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
@@ -10064,7 +16032,7 @@
       <c r="P2" s="11"/>
       <c r="Q2" s="11"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18">
       <c r="A3" s="11"/>
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
@@ -10081,7 +16049,7 @@
       <c r="P3" s="11"/>
       <c r="Q3" s="11"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18">
       <c r="A4" s="11"/>
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
@@ -10098,7 +16066,7 @@
       <c r="P4" s="11"/>
       <c r="Q4" s="11"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18">
       <c r="A5" s="11"/>
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
@@ -10115,7 +16083,7 @@
       <c r="P5" s="11"/>
       <c r="Q5" s="11"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18">
       <c r="A6" s="11"/>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
@@ -10132,7 +16100,7 @@
       <c r="P6" s="11"/>
       <c r="Q6" s="11"/>
     </row>
-    <row r="7" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" ht="15.6">
       <c r="A7" s="11"/>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -10151,7 +16119,7 @@
       <c r="P7" s="12"/>
       <c r="Q7" s="11"/>
     </row>
-    <row r="8" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="17.399999999999999">
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -10172,7 +16140,7 @@
       <c r="P8" s="69"/>
       <c r="Q8" s="11"/>
     </row>
-    <row r="9" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="15.6">
       <c r="A9" s="11"/>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -10191,7 +16159,7 @@
       <c r="P9" s="12"/>
       <c r="Q9" s="11"/>
     </row>
-    <row r="10" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" ht="15" thickBot="1">
       <c r="A10" s="11"/>
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
@@ -10208,7 +16176,7 @@
       <c r="P10" s="11"/>
       <c r="Q10" s="11"/>
     </row>
-    <row r="11" spans="1:18" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="15" thickTop="1">
       <c r="A11" s="13"/>
       <c r="B11" s="14"/>
       <c r="C11" s="14" t="s">
@@ -10255,7 +16223,7 @@
       </c>
       <c r="Q11" s="11"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18">
       <c r="A12" s="18"/>
       <c r="B12" s="19"/>
       <c r="C12" s="19" t="s">
@@ -10302,7 +16270,7 @@
       </c>
       <c r="Q12" s="11"/>
     </row>
-    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" ht="15" thickBot="1">
       <c r="A13" s="23" t="s">
         <v>27</v>
       </c>
@@ -10327,7 +16295,7 @@
       <c r="P13" s="28"/>
       <c r="Q13" s="11"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18">
       <c r="A14" s="29">
         <v>1</v>
       </c>
@@ -10353,7 +16321,7 @@
       <c r="Q14" s="35"/>
       <c r="R14" s="36"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18">
       <c r="A15" s="37">
         <f>A14+1</f>
         <v>2</v>
@@ -10380,7 +16348,7 @@
       <c r="Q15" s="35"/>
       <c r="R15" s="36"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18">
       <c r="A16" s="37">
         <f t="shared" ref="A16:A30" si="0">A15+1</f>
         <v>3</v>
@@ -10407,7 +16375,7 @@
       <c r="Q16" s="35"/>
       <c r="R16" s="36"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18">
       <c r="A17" s="37">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -10432,7 +16400,7 @@
       <c r="Q17" s="35"/>
       <c r="R17" s="36"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18">
       <c r="A18" s="37">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -10457,7 +16425,7 @@
       <c r="Q18" s="35"/>
       <c r="R18" s="36"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18">
       <c r="A19" s="37">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -10480,7 +16448,7 @@
       <c r="Q19" s="35"/>
       <c r="R19" s="36"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18">
       <c r="A20" s="37">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -10503,7 +16471,7 @@
       <c r="Q20" s="35"/>
       <c r="R20" s="36"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18">
       <c r="A21" s="37">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -10526,7 +16494,7 @@
       <c r="Q21" s="35"/>
       <c r="R21" s="36"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18">
       <c r="A22" s="37">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -10549,7 +16517,7 @@
       <c r="Q22" s="35"/>
       <c r="R22" s="36"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18">
       <c r="A23" s="37">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -10572,7 +16540,7 @@
       <c r="Q23" s="35"/>
       <c r="R23" s="36"/>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18">
       <c r="A24" s="37">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -10595,7 +16563,7 @@
       <c r="Q24" s="35"/>
       <c r="R24" s="36"/>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18">
       <c r="A25" s="37">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -10618,7 +16586,7 @@
       <c r="Q25" s="35"/>
       <c r="R25" s="36"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18">
       <c r="A26" s="37">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -10641,7 +16609,7 @@
       <c r="Q26" s="35"/>
       <c r="R26" s="36"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18">
       <c r="A27" s="37">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -10668,7 +16636,7 @@
       <c r="Q27" s="35"/>
       <c r="R27" s="36"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18">
       <c r="A28" s="37">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -10695,7 +16663,7 @@
       <c r="Q28" s="35"/>
       <c r="R28" s="36"/>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18">
       <c r="A29" s="37">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -10722,7 +16690,7 @@
       <c r="Q29" s="35"/>
       <c r="R29" s="36"/>
     </row>
-    <row r="30" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:18" ht="15" thickBot="1">
       <c r="A30" s="43">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -10749,7 +16717,7 @@
       <c r="Q30" s="35"/>
       <c r="R30" s="36"/>
     </row>
-    <row r="31" spans="1:18" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" ht="15" thickTop="1">
       <c r="A31" s="11"/>
       <c r="C31" s="49"/>
       <c r="D31" s="11"/>
@@ -10767,7 +16735,7 @@
       <c r="P31" s="11"/>
       <c r="Q31" s="11"/>
     </row>
-    <row r="32" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:18" ht="15" thickBot="1">
       <c r="A32" s="11"/>
       <c r="C32" s="49"/>
       <c r="D32" s="11"/>
@@ -10785,7 +16753,7 @@
       <c r="P32" s="11"/>
       <c r="Q32" s="11"/>
     </row>
-    <row r="33" spans="1:18" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" ht="15" thickTop="1">
       <c r="A33" s="50"/>
       <c r="B33" s="51" t="s">
         <v>56</v>
@@ -10813,7 +16781,7 @@
       <c r="Q33" s="35"/>
       <c r="R33" s="36"/>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18">
       <c r="A34" s="37"/>
       <c r="B34" s="38" t="s">
         <v>60</v>
@@ -10839,7 +16807,7 @@
       <c r="Q34" s="35"/>
       <c r="R34" s="36"/>
     </row>
-    <row r="35" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:18" ht="15" thickBot="1">
       <c r="A35" s="43"/>
       <c r="B35" s="44" t="s">
         <v>29</v>
@@ -10861,7 +16829,7 @@
       <c r="Q35" s="35"/>
       <c r="R35" s="36"/>
     </row>
-    <row r="36" spans="1:18" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" ht="15" thickTop="1">
       <c r="A36" s="11"/>
       <c r="D36" s="11"/>
       <c r="E36" s="11"/>
@@ -10878,7 +16846,7 @@
       <c r="P36" s="11"/>
       <c r="Q36" s="11"/>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18">
       <c r="A37" s="11"/>
       <c r="D37" s="11"/>
       <c r="E37" s="11"/>
@@ -10895,7 +16863,7 @@
       <c r="P37" s="11"/>
       <c r="Q37" s="11"/>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18">
       <c r="A38" s="11"/>
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
@@ -10912,7 +16880,7 @@
       <c r="P38" s="11"/>
       <c r="Q38" s="11"/>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18">
       <c r="A39" s="11"/>
       <c r="B39" s="57" t="s">
         <v>63</v>
@@ -10932,7 +16900,7 @@
       <c r="P39" s="11"/>
       <c r="Q39" s="11"/>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18">
       <c r="A40" s="11"/>
       <c r="B40" s="57" t="s">
         <v>64</v>
@@ -10954,7 +16922,7 @@
       <c r="P40" s="11"/>
       <c r="Q40" s="11"/>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18">
       <c r="A41" s="11"/>
       <c r="B41" s="57"/>
       <c r="D41" s="11"/>
@@ -10972,7 +16940,7 @@
       <c r="P41" s="11"/>
       <c r="Q41" s="11"/>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18">
       <c r="A42" s="11"/>
       <c r="D42" s="11"/>
       <c r="E42" s="11"/>
@@ -10989,7 +16957,7 @@
       <c r="P42" s="11"/>
       <c r="Q42" s="11"/>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18">
       <c r="A43" s="11"/>
       <c r="B43" s="57"/>
       <c r="D43" s="11"/>
@@ -11007,7 +16975,7 @@
       <c r="P43" s="11"/>
       <c r="Q43" s="11"/>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18">
       <c r="A44" s="11"/>
       <c r="D44" s="11"/>
       <c r="E44" s="11"/>
@@ -11033,15 +17001,15 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:P44"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16">
       <c r="A1" s="11"/>
       <c r="D1" s="11"/>
       <c r="E1" s="11"/>
@@ -11057,7 +17025,7 @@
       <c r="O1" s="11"/>
       <c r="P1" s="11"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16">
       <c r="A2" s="11"/>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
@@ -11073,7 +17041,7 @@
       <c r="O2" s="11"/>
       <c r="P2" s="11"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16">
       <c r="A3" s="11"/>
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
@@ -11089,7 +17057,7 @@
       <c r="O3" s="11"/>
       <c r="P3" s="11"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16">
       <c r="A4" s="11"/>
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
@@ -11105,7 +17073,7 @@
       <c r="O4" s="11"/>
       <c r="P4" s="11"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16">
       <c r="A5" s="11"/>
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
@@ -11121,7 +17089,7 @@
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16">
       <c r="A6" s="11"/>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
@@ -11137,7 +17105,7 @@
       <c r="O6" s="11"/>
       <c r="P6" s="11"/>
     </row>
-    <row r="7" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" ht="15.6">
       <c r="A7" s="11"/>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -11155,7 +17123,7 @@
       <c r="O7" s="12"/>
       <c r="P7" s="12"/>
     </row>
-    <row r="8" spans="1:16" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" ht="17.399999999999999">
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -11175,7 +17143,7 @@
       <c r="O8" s="69"/>
       <c r="P8" s="69"/>
     </row>
-    <row r="9" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="15.6">
       <c r="A9" s="11"/>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -11193,7 +17161,7 @@
       <c r="O9" s="12"/>
       <c r="P9" s="12"/>
     </row>
-    <row r="10" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16" ht="15" thickBot="1">
       <c r="A10" s="11"/>
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
@@ -11209,7 +17177,7 @@
       <c r="O10" s="11"/>
       <c r="P10" s="11"/>
     </row>
-    <row r="11" spans="1:16" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" ht="15" thickTop="1">
       <c r="A11" s="13"/>
       <c r="B11" s="14"/>
       <c r="C11" s="14" t="s">
@@ -11255,7 +17223,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16">
       <c r="A12" s="18"/>
       <c r="B12" s="19"/>
       <c r="C12" s="19" t="s">
@@ -11301,7 +17269,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" ht="15" thickBot="1">
       <c r="A13" s="23" t="s">
         <v>69</v>
       </c>
@@ -11325,7 +17293,7 @@
       <c r="O13" s="27"/>
       <c r="P13" s="28"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16">
       <c r="A14" s="29">
         <v>1</v>
       </c>
@@ -11349,7 +17317,7 @@
       <c r="O14" s="33"/>
       <c r="P14" s="34"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16">
       <c r="A15" s="37">
         <f>A14+1</f>
         <v>2</v>
@@ -11374,7 +17342,7 @@
       <c r="O15" s="41"/>
       <c r="P15" s="42"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16">
       <c r="A16" s="37">
         <f t="shared" ref="A16:A30" si="0">A15+1</f>
         <v>3</v>
@@ -11399,7 +17367,7 @@
       <c r="O16" s="41"/>
       <c r="P16" s="42"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16">
       <c r="A17" s="37">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -11422,7 +17390,7 @@
       <c r="O17" s="41"/>
       <c r="P17" s="42"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16">
       <c r="A18" s="37">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -11445,7 +17413,7 @@
       <c r="O18" s="41"/>
       <c r="P18" s="42"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16">
       <c r="A19" s="37">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -11466,7 +17434,7 @@
       <c r="O19" s="41"/>
       <c r="P19" s="42"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16">
       <c r="A20" s="37">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -11487,7 +17455,7 @@
       <c r="O20" s="41"/>
       <c r="P20" s="42"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16">
       <c r="A21" s="37">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -11508,7 +17476,7 @@
       <c r="O21" s="41"/>
       <c r="P21" s="42"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16">
       <c r="A22" s="37">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -11529,7 +17497,7 @@
       <c r="O22" s="41"/>
       <c r="P22" s="42"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16">
       <c r="A23" s="37">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -11550,7 +17518,7 @@
       <c r="O23" s="41"/>
       <c r="P23" s="42"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16">
       <c r="A24" s="37">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -11571,7 +17539,7 @@
       <c r="O24" s="41"/>
       <c r="P24" s="42"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16">
       <c r="A25" s="37">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -11592,7 +17560,7 @@
       <c r="O25" s="41"/>
       <c r="P25" s="42"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16">
       <c r="A26" s="37">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -11613,7 +17581,7 @@
       <c r="O26" s="41"/>
       <c r="P26" s="42"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16">
       <c r="A27" s="37">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -11638,7 +17606,7 @@
       <c r="O27" s="41"/>
       <c r="P27" s="42"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16">
       <c r="A28" s="37">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -11663,7 +17631,7 @@
       <c r="O28" s="41"/>
       <c r="P28" s="42"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16">
       <c r="A29" s="37">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -11688,7 +17656,7 @@
       <c r="O29" s="41"/>
       <c r="P29" s="42"/>
     </row>
-    <row r="30" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:16" ht="15" thickBot="1">
       <c r="A30" s="43">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -11713,7 +17681,7 @@
       <c r="O30" s="47"/>
       <c r="P30" s="48"/>
     </row>
-    <row r="31" spans="1:16" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" ht="15" thickTop="1">
       <c r="A31" s="11"/>
       <c r="C31" s="49"/>
       <c r="D31" s="11"/>
@@ -11730,7 +17698,7 @@
       <c r="O31" s="11"/>
       <c r="P31" s="11"/>
     </row>
-    <row r="32" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16" ht="15" thickBot="1">
       <c r="A32" s="11"/>
       <c r="C32" s="49"/>
       <c r="D32" s="11"/>
@@ -11747,7 +17715,7 @@
       <c r="O32" s="11"/>
       <c r="P32" s="11"/>
     </row>
-    <row r="33" spans="1:16" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" ht="15" thickTop="1">
       <c r="A33" s="50"/>
       <c r="B33" s="51" t="s">
         <v>77</v>
@@ -11773,7 +17741,7 @@
       <c r="O33" s="54"/>
       <c r="P33" s="55"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16">
       <c r="A34" s="37"/>
       <c r="B34" s="38" t="s">
         <v>81</v>
@@ -11797,7 +17765,7 @@
       </c>
       <c r="P34" s="42"/>
     </row>
-    <row r="35" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:16" ht="15" thickBot="1">
       <c r="A35" s="43"/>
       <c r="B35" s="44" t="s">
         <v>84</v>
@@ -11817,7 +17785,7 @@
       <c r="O35" s="47"/>
       <c r="P35" s="48"/>
     </row>
-    <row r="36" spans="1:16" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" ht="15" thickTop="1">
       <c r="A36" s="11"/>
       <c r="D36" s="11"/>
       <c r="E36" s="11"/>
@@ -11833,7 +17801,7 @@
       <c r="O36" s="11"/>
       <c r="P36" s="11"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16">
       <c r="A37" s="11"/>
       <c r="D37" s="11"/>
       <c r="E37" s="11"/>
@@ -11849,7 +17817,7 @@
       <c r="O37" s="11"/>
       <c r="P37" s="11"/>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16">
       <c r="A38" s="11"/>
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
@@ -11865,7 +17833,7 @@
       <c r="O38" s="11"/>
       <c r="P38" s="11"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16">
       <c r="A39" s="11"/>
       <c r="B39" s="57" t="s">
         <v>85</v>
@@ -11884,7 +17852,7 @@
       <c r="O39" s="11"/>
       <c r="P39" s="11"/>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16">
       <c r="A40" s="11"/>
       <c r="D40" s="11"/>
       <c r="E40" s="11"/>
@@ -11902,7 +17870,7 @@
       <c r="O40" s="11"/>
       <c r="P40" s="11"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16">
       <c r="A41" s="11"/>
       <c r="B41" s="57"/>
       <c r="D41" s="11"/>
@@ -11919,7 +17887,7 @@
       <c r="O41" s="11"/>
       <c r="P41" s="11"/>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16">
       <c r="A42" s="11"/>
       <c r="D42" s="11"/>
       <c r="E42" s="11"/>
@@ -11935,7 +17903,7 @@
       <c r="O42" s="11"/>
       <c r="P42" s="11"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16">
       <c r="A43" s="11"/>
       <c r="D43" s="11"/>
       <c r="E43" s="11"/>
@@ -11951,7 +17919,7 @@
       <c r="O43" s="11"/>
       <c r="P43" s="11"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16">
       <c r="A44" s="11"/>
       <c r="D44" s="11"/>
       <c r="E44" s="11"/>
@@ -11974,120 +17942,4 @@
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A7:I25"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="29.5546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="7" spans="1:9" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="B7" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="G10" s="4"/>
-      <c r="H10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I10" s="3"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="6">
-        <v>7026116</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I11" s="7"/>
-    </row>
-    <row r="12" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="8"/>
-      <c r="B12" s="9"/>
-      <c r="H12" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I12" s="9"/>
-    </row>
-    <row r="15" spans="1:9" ht="21" x14ac:dyDescent="0.4">
-      <c r="B15" s="64" t="s">
-        <v>87</v>
-      </c>
-      <c r="C15" s="64"/>
-      <c r="D15" s="64"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>94</v>
-      </c>
-      <c r="B19" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B20" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B21" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B22" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B23" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B24" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B25" t="s">
-        <v>88</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B15:D15"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
 </file>
--- a/ProjectManagement/Checklist.xlsx
+++ b/ProjectManagement/Checklist.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28227"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{297DE719-9F34-4012-A557-27E115298C10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82144DE2-E924-458C-91BE-F6B3C44B2CA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Checklist" sheetId="1" r:id="rId1"/>
@@ -1755,32 +1755,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2007,6 +1986,27 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5183,6 +5183,241 @@
           <a:endParaRPr lang="en-IN" sz="1100"/>
         </a:p>
       </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>8962</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>62303</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>20665</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>167898</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="50" name="Rectangle 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5194E216-30DF-4684-B4CF-47EEDE2D442D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="4542216" y="3456432"/>
+          <a:ext cx="621303" cy="105595"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="008000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="17"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>332154</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>77784</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>401624</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>162239</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="51" name="Rectangle 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F352768-30EA-4843-AF0F-5B899D49E341}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="4867248" y="3638126"/>
+          <a:ext cx="679504" cy="84455"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="008000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="17"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>604493</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>74182</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>95498</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>158637</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="52" name="Rectangle 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11D9E07F-3057-454E-8414-9C4613A7DB52}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="5136702" y="3828474"/>
+          <a:ext cx="708613" cy="84455"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="008000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="17"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>10159</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>75999</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>603884</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>160454</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="53" name="Rectangle 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F795F97-F99C-45D1-94EB-C3E534548A0A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="5763259" y="4007919"/>
+          <a:ext cx="593725" cy="84455"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="008000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="17"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>20730</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>73221</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>607854</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>157676</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="54" name="Rectangle 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{347CDCAA-3991-4290-B2BF-9C9775F76B27}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="5773433" y="4365424"/>
+          <a:ext cx="587124" cy="84455"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="008000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="17"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -13304,11 +13539,11 @@
       <c r="I6" s="9"/>
     </row>
     <row r="9" spans="1:9" ht="21">
-      <c r="B9" s="64" t="s">
+      <c r="B9" s="142" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="64"/>
-      <c r="D9" s="64"/>
+      <c r="C9" s="142"/>
+      <c r="D9" s="142"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
@@ -13330,12 +13565,12 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="21">
-      <c r="A14" s="64" t="s">
+      <c r="A14" s="142" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="64"/>
-      <c r="C14" s="64"/>
-      <c r="D14" s="64"/>
+      <c r="B14" s="142"/>
+      <c r="C14" s="142"/>
+      <c r="D14" s="142"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15">
@@ -13344,7 +13579,7 @@
       <c r="B15" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="65" t="s">
+      <c r="C15" s="143" t="s">
         <v>125</v>
       </c>
     </row>
@@ -13356,7 +13591,7 @@
       <c r="B16" s="62" t="s">
         <v>90</v>
       </c>
-      <c r="C16" s="65"/>
+      <c r="C16" s="143"/>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
@@ -13366,7 +13601,7 @@
       <c r="B17" s="62" t="s">
         <v>91</v>
       </c>
-      <c r="C17" s="65"/>
+      <c r="C17" s="143"/>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
@@ -13376,7 +13611,7 @@
       <c r="B18" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="65"/>
+      <c r="C18" s="143"/>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
@@ -13386,7 +13621,7 @@
       <c r="B19" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="65"/>
+      <c r="C19" s="143"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
@@ -13396,7 +13631,7 @@
       <c r="B20" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="65"/>
+      <c r="C20" s="143"/>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
@@ -13406,7 +13641,7 @@
       <c r="B21" s="62" t="s">
         <v>92</v>
       </c>
-      <c r="C21" s="65"/>
+      <c r="C21" s="143"/>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
@@ -13416,7 +13651,7 @@
       <c r="B22" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="65"/>
+      <c r="C22" s="143"/>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
@@ -13426,7 +13661,7 @@
       <c r="B23" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="65"/>
+      <c r="C23" s="143"/>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
@@ -13436,7 +13671,7 @@
       <c r="B24" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="C24" s="65"/>
+      <c r="C24" s="143"/>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
@@ -13446,7 +13681,7 @@
       <c r="B25" s="62" t="s">
         <v>103</v>
       </c>
-      <c r="C25" s="65"/>
+      <c r="C25" s="143"/>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
@@ -13456,7 +13691,7 @@
       <c r="B26" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="66" t="s">
+      <c r="C26" s="144" t="s">
         <v>126</v>
       </c>
     </row>
@@ -13468,7 +13703,7 @@
       <c r="B27" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="66"/>
+      <c r="C27" s="144"/>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
@@ -13478,7 +13713,7 @@
       <c r="B28" t="s">
         <v>98</v>
       </c>
-      <c r="C28" s="66"/>
+      <c r="C28" s="144"/>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
@@ -13488,7 +13723,7 @@
       <c r="B29" t="s">
         <v>99</v>
       </c>
-      <c r="C29" s="66"/>
+      <c r="C29" s="144"/>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
@@ -13498,7 +13733,7 @@
       <c r="B30" t="s">
         <v>93</v>
       </c>
-      <c r="C30" s="66"/>
+      <c r="C30" s="144"/>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
@@ -13508,7 +13743,7 @@
       <c r="B31" t="s">
         <v>100</v>
       </c>
-      <c r="C31" s="66"/>
+      <c r="C31" s="144"/>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
@@ -13518,7 +13753,7 @@
       <c r="B32" t="s">
         <v>101</v>
       </c>
-      <c r="C32" s="66"/>
+      <c r="C32" s="144"/>
     </row>
     <row r="33" spans="1:4">
       <c r="A33">
@@ -13528,7 +13763,7 @@
       <c r="B33" t="s">
         <v>23</v>
       </c>
-      <c r="C33" s="66"/>
+      <c r="C33" s="144"/>
     </row>
     <row r="34" spans="1:4">
       <c r="A34">
@@ -13538,7 +13773,7 @@
       <c r="B34" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="C34" s="65" t="s">
+      <c r="C34" s="143" t="s">
         <v>127</v>
       </c>
     </row>
@@ -13550,7 +13785,7 @@
       <c r="B35" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="65"/>
+      <c r="C35" s="143"/>
     </row>
     <row r="36" spans="1:4">
       <c r="A36">
@@ -13560,7 +13795,7 @@
       <c r="B36" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="C36" s="65"/>
+      <c r="C36" s="143"/>
     </row>
     <row r="37" spans="1:4">
       <c r="A37">
@@ -13570,15 +13805,15 @@
       <c r="B37" s="62" t="s">
         <v>102</v>
       </c>
-      <c r="C37" s="65"/>
+      <c r="C37" s="143"/>
     </row>
     <row r="38" spans="1:4" ht="21">
-      <c r="A38" s="64" t="s">
+      <c r="A38" s="142" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="64"/>
-      <c r="C38" s="64"/>
-      <c r="D38" s="64"/>
+      <c r="B38" s="142"/>
+      <c r="C38" s="142"/>
+      <c r="D38" s="142"/>
     </row>
     <row r="39" spans="1:4">
       <c r="A39">
@@ -13588,7 +13823,7 @@
       <c r="B39" t="s">
         <v>30</v>
       </c>
-      <c r="C39" s="66" t="s">
+      <c r="C39" s="144" t="s">
         <v>128</v>
       </c>
     </row>
@@ -13600,7 +13835,7 @@
       <c r="B40" t="s">
         <v>32</v>
       </c>
-      <c r="C40" s="66"/>
+      <c r="C40" s="144"/>
     </row>
     <row r="41" spans="1:4">
       <c r="A41">
@@ -13610,7 +13845,7 @@
       <c r="B41" t="s">
         <v>33</v>
       </c>
-      <c r="C41" s="66"/>
+      <c r="C41" s="144"/>
     </row>
     <row r="42" spans="1:4">
       <c r="A42">
@@ -13620,7 +13855,7 @@
       <c r="B42" t="s">
         <v>42</v>
       </c>
-      <c r="C42" s="66"/>
+      <c r="C42" s="144"/>
     </row>
     <row r="43" spans="1:4">
       <c r="A43">
@@ -13630,7 +13865,7 @@
       <c r="B43" t="s">
         <v>44</v>
       </c>
-      <c r="C43" s="66"/>
+      <c r="C43" s="144"/>
     </row>
     <row r="44" spans="1:4">
       <c r="A44">
@@ -13640,7 +13875,7 @@
       <c r="B44" t="s">
         <v>119</v>
       </c>
-      <c r="C44" s="66"/>
+      <c r="C44" s="144"/>
     </row>
     <row r="45" spans="1:4">
       <c r="A45">
@@ -13650,7 +13885,7 @@
       <c r="B45" t="s">
         <v>118</v>
       </c>
-      <c r="C45" s="66"/>
+      <c r="C45" s="144"/>
     </row>
     <row r="46" spans="1:4" ht="15" customHeight="1">
       <c r="A46">
@@ -13660,7 +13895,7 @@
       <c r="B46" s="62" t="s">
         <v>104</v>
       </c>
-      <c r="C46" s="67" t="s">
+      <c r="C46" s="145" t="s">
         <v>129</v>
       </c>
     </row>
@@ -13672,7 +13907,7 @@
       <c r="B47" s="62" t="s">
         <v>105</v>
       </c>
-      <c r="C47" s="67"/>
+      <c r="C47" s="145"/>
     </row>
     <row r="48" spans="1:4">
       <c r="A48">
@@ -13682,7 +13917,7 @@
       <c r="B48" s="62" t="s">
         <v>106</v>
       </c>
-      <c r="C48" s="67"/>
+      <c r="C48" s="145"/>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
@@ -13692,7 +13927,7 @@
       <c r="B49" s="62" t="s">
         <v>107</v>
       </c>
-      <c r="C49" s="67"/>
+      <c r="C49" s="145"/>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
@@ -13702,7 +13937,7 @@
       <c r="B50" t="s">
         <v>108</v>
       </c>
-      <c r="C50" s="68" t="s">
+      <c r="C50" s="146" t="s">
         <v>130</v>
       </c>
     </row>
@@ -13714,7 +13949,7 @@
       <c r="B51" t="s">
         <v>109</v>
       </c>
-      <c r="C51" s="68"/>
+      <c r="C51" s="146"/>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
@@ -13724,7 +13959,7 @@
       <c r="B52" t="s">
         <v>120</v>
       </c>
-      <c r="C52" s="68"/>
+      <c r="C52" s="146"/>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
@@ -13735,7 +13970,7 @@
         <f>[1]Report!$A$207</f>
         <v>Homework "Literature"</v>
       </c>
-      <c r="C53" s="67" t="s">
+      <c r="C53" s="145" t="s">
         <v>131</v>
       </c>
     </row>
@@ -13747,7 +13982,7 @@
       <c r="B54" s="62" t="s">
         <v>110</v>
       </c>
-      <c r="C54" s="67"/>
+      <c r="C54" s="145"/>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
@@ -13757,7 +13992,7 @@
       <c r="B55" s="62" t="s">
         <v>114</v>
       </c>
-      <c r="C55" s="67"/>
+      <c r="C55" s="145"/>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
@@ -13767,7 +14002,7 @@
       <c r="B56" t="s">
         <v>113</v>
       </c>
-      <c r="C56" s="68" t="s">
+      <c r="C56" s="146" t="s">
         <v>132</v>
       </c>
     </row>
@@ -13779,7 +14014,7 @@
       <c r="B57" t="s">
         <v>115</v>
       </c>
-      <c r="C57" s="68"/>
+      <c r="C57" s="146"/>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
@@ -13789,7 +14024,7 @@
       <c r="B58" t="s">
         <v>111</v>
       </c>
-      <c r="C58" s="68"/>
+      <c r="C58" s="146"/>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
@@ -13799,7 +14034,7 @@
       <c r="B59" t="s">
         <v>112</v>
       </c>
-      <c r="C59" s="68"/>
+      <c r="C59" s="146"/>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
@@ -13809,7 +14044,7 @@
       <c r="B60" s="62" t="s">
         <v>116</v>
       </c>
-      <c r="C60" s="67" t="s">
+      <c r="C60" s="145" t="s">
         <v>133</v>
       </c>
     </row>
@@ -13821,7 +14056,7 @@
       <c r="B61" s="62" t="s">
         <v>117</v>
       </c>
-      <c r="C61" s="67"/>
+      <c r="C61" s="145"/>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
@@ -13831,7 +14066,7 @@
       <c r="B62" s="62" t="s">
         <v>122</v>
       </c>
-      <c r="C62" s="67"/>
+      <c r="C62" s="145"/>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
@@ -13841,7 +14076,7 @@
       <c r="B63" t="s">
         <v>121</v>
       </c>
-      <c r="C63" s="68" t="s">
+      <c r="C63" s="146" t="s">
         <v>134</v>
       </c>
     </row>
@@ -13853,7 +14088,7 @@
       <c r="B64" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="C64" s="68"/>
+      <c r="C64" s="146"/>
     </row>
     <row r="65" spans="1:4">
       <c r="A65">
@@ -13863,15 +14098,15 @@
       <c r="B65" s="63" t="s">
         <v>124</v>
       </c>
-      <c r="C65" s="68"/>
+      <c r="C65" s="146"/>
     </row>
     <row r="66" spans="1:4" ht="21">
-      <c r="A66" s="64" t="s">
+      <c r="A66" s="142" t="s">
         <v>39</v>
       </c>
-      <c r="B66" s="64"/>
-      <c r="C66" s="64"/>
-      <c r="D66" s="64"/>
+      <c r="B66" s="142"/>
+      <c r="C66" s="142"/>
+      <c r="D66" s="142"/>
     </row>
     <row r="67" spans="1:4">
       <c r="A67">
@@ -14000,1872 +14235,1872 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
-      <c r="A1" s="70"/>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="70"/>
-      <c r="K1" s="70"/>
-      <c r="L1" s="70"/>
-      <c r="M1" s="70"/>
-      <c r="N1" s="70"/>
-      <c r="O1" s="70"/>
-      <c r="P1" s="70"/>
-      <c r="Q1" s="70"/>
-      <c r="R1" s="71"/>
-      <c r="S1" s="71"/>
-      <c r="T1" s="71"/>
-      <c r="U1" s="71"/>
-      <c r="V1" s="71"/>
-      <c r="W1" s="71"/>
-      <c r="X1" s="71"/>
-      <c r="Y1" s="71"/>
-      <c r="Z1" s="71"/>
-      <c r="AA1" s="71"/>
-      <c r="AB1" s="71"/>
-      <c r="AC1" s="71"/>
+      <c r="A1" s="64"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
+      <c r="N1" s="64"/>
+      <c r="O1" s="64"/>
+      <c r="P1" s="64"/>
+      <c r="Q1" s="64"/>
+      <c r="R1" s="65"/>
+      <c r="S1" s="65"/>
+      <c r="T1" s="65"/>
+      <c r="U1" s="65"/>
+      <c r="V1" s="65"/>
+      <c r="W1" s="65"/>
+      <c r="X1" s="65"/>
+      <c r="Y1" s="65"/>
+      <c r="Z1" s="65"/>
+      <c r="AA1" s="65"/>
+      <c r="AB1" s="65"/>
+      <c r="AC1" s="65"/>
     </row>
     <row r="2" spans="1:29">
-      <c r="A2" s="70"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="70"/>
-      <c r="M2" s="70"/>
-      <c r="N2" s="70"/>
-      <c r="O2" s="70"/>
-      <c r="P2" s="70"/>
-      <c r="Q2" s="70"/>
-      <c r="R2" s="71"/>
-      <c r="S2" s="71"/>
-      <c r="T2" s="71"/>
-      <c r="U2" s="71"/>
-      <c r="V2" s="71"/>
-      <c r="W2" s="71"/>
-      <c r="X2" s="71"/>
-      <c r="Y2" s="71"/>
-      <c r="Z2" s="71"/>
-      <c r="AA2" s="71"/>
-      <c r="AB2" s="71"/>
-      <c r="AC2" s="71"/>
+      <c r="A2" s="64"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="64"/>
+      <c r="M2" s="64"/>
+      <c r="N2" s="64"/>
+      <c r="O2" s="64"/>
+      <c r="P2" s="64"/>
+      <c r="Q2" s="64"/>
+      <c r="R2" s="65"/>
+      <c r="S2" s="65"/>
+      <c r="T2" s="65"/>
+      <c r="U2" s="65"/>
+      <c r="V2" s="65"/>
+      <c r="W2" s="65"/>
+      <c r="X2" s="65"/>
+      <c r="Y2" s="65"/>
+      <c r="Z2" s="65"/>
+      <c r="AA2" s="65"/>
+      <c r="AB2" s="65"/>
+      <c r="AC2" s="65"/>
     </row>
     <row r="3" spans="1:29">
-      <c r="A3" s="70"/>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
-      <c r="I3" s="70"/>
-      <c r="J3" s="70"/>
-      <c r="K3" s="70"/>
-      <c r="L3" s="70"/>
-      <c r="M3" s="70"/>
-      <c r="N3" s="70"/>
-      <c r="O3" s="70"/>
-      <c r="P3" s="70"/>
-      <c r="Q3" s="70"/>
-      <c r="R3" s="71"/>
-      <c r="S3" s="71"/>
-      <c r="T3" s="71"/>
-      <c r="U3" s="71"/>
-      <c r="V3" s="71"/>
-      <c r="W3" s="71"/>
-      <c r="X3" s="71"/>
-      <c r="Y3" s="71"/>
-      <c r="Z3" s="71"/>
-      <c r="AA3" s="71"/>
-      <c r="AB3" s="71"/>
-      <c r="AC3" s="71"/>
+      <c r="A3" s="64"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="64"/>
+      <c r="L3" s="64"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="65"/>
+      <c r="W3" s="65"/>
+      <c r="X3" s="65"/>
+      <c r="Y3" s="65"/>
+      <c r="Z3" s="65"/>
+      <c r="AA3" s="65"/>
+      <c r="AB3" s="65"/>
+      <c r="AC3" s="65"/>
     </row>
     <row r="4" spans="1:29">
-      <c r="A4" s="70"/>
-      <c r="B4" s="70"/>
-      <c r="C4" s="70"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="70"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="70"/>
-      <c r="J4" s="70"/>
-      <c r="K4" s="70"/>
-      <c r="L4" s="70"/>
-      <c r="M4" s="70"/>
-      <c r="N4" s="70"/>
-      <c r="O4" s="70"/>
-      <c r="P4" s="70"/>
-      <c r="Q4" s="70"/>
-      <c r="R4" s="70"/>
-      <c r="S4" s="71"/>
-      <c r="T4" s="71"/>
-      <c r="U4" s="71"/>
-      <c r="V4" s="71"/>
-      <c r="W4" s="71"/>
-      <c r="X4" s="71"/>
-      <c r="Y4" s="71"/>
-      <c r="Z4" s="71"/>
-      <c r="AA4" s="71"/>
-      <c r="AB4" s="71"/>
-      <c r="AC4" s="71"/>
+      <c r="A4" s="64"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
+      <c r="K4" s="64"/>
+      <c r="L4" s="64"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="65"/>
+      <c r="W4" s="65"/>
+      <c r="X4" s="65"/>
+      <c r="Y4" s="65"/>
+      <c r="Z4" s="65"/>
+      <c r="AA4" s="65"/>
+      <c r="AB4" s="65"/>
+      <c r="AC4" s="65"/>
     </row>
     <row r="5" spans="1:29">
-      <c r="A5" s="70"/>
-      <c r="B5" s="71"/>
-      <c r="C5" s="71"/>
-      <c r="D5" s="71"/>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
-      <c r="I5" s="70"/>
-      <c r="J5" s="70"/>
-      <c r="K5" s="70"/>
-      <c r="L5" s="70"/>
-      <c r="M5" s="70"/>
-      <c r="N5" s="70"/>
-      <c r="O5" s="70"/>
-      <c r="P5" s="70"/>
-      <c r="Q5" s="70"/>
-      <c r="R5" s="71"/>
-      <c r="S5" s="71"/>
-      <c r="T5" s="71"/>
-      <c r="U5" s="71"/>
-      <c r="V5" s="71"/>
-      <c r="W5" s="71"/>
-      <c r="X5" s="71"/>
-      <c r="Y5" s="71"/>
-      <c r="Z5" s="71"/>
-      <c r="AA5" s="71"/>
-      <c r="AB5" s="71"/>
-      <c r="AC5" s="71"/>
+      <c r="A5" s="64"/>
+      <c r="B5" s="65"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="64"/>
+      <c r="K5" s="64"/>
+      <c r="L5" s="64"/>
+      <c r="M5" s="64"/>
+      <c r="N5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="64"/>
+      <c r="Q5" s="64"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="65"/>
+      <c r="Y5" s="65"/>
+      <c r="Z5" s="65"/>
+      <c r="AA5" s="65"/>
+      <c r="AB5" s="65"/>
+      <c r="AC5" s="65"/>
     </row>
     <row r="6" spans="1:29">
-      <c r="A6" s="70"/>
-      <c r="B6" s="71"/>
-      <c r="C6" s="71"/>
-      <c r="D6" s="71"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="70"/>
-      <c r="L6" s="70"/>
-      <c r="M6" s="70"/>
-      <c r="N6" s="70"/>
-      <c r="O6" s="70"/>
-      <c r="P6" s="70"/>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="71"/>
-      <c r="S6" s="71"/>
+      <c r="A6" s="64"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="64"/>
+      <c r="L6" s="64"/>
+      <c r="M6" s="64"/>
+      <c r="N6" s="64"/>
+      <c r="O6" s="64"/>
+      <c r="P6" s="64"/>
+      <c r="Q6" s="64"/>
+      <c r="R6" s="65"/>
+      <c r="S6" s="65"/>
       <c r="T6" t="s">
         <v>137</v>
       </c>
-      <c r="U6" s="71"/>
-      <c r="V6" s="71"/>
-      <c r="W6" s="71"/>
-      <c r="X6" s="71"/>
-      <c r="Y6" s="71"/>
-      <c r="Z6" s="71"/>
-      <c r="AA6" s="71"/>
-      <c r="AB6" s="71"/>
-      <c r="AC6" s="71"/>
+      <c r="U6" s="65"/>
+      <c r="V6" s="65"/>
+      <c r="W6" s="65"/>
+      <c r="X6" s="65"/>
+      <c r="Y6" s="65"/>
+      <c r="Z6" s="65"/>
+      <c r="AA6" s="65"/>
+      <c r="AB6" s="65"/>
+      <c r="AC6" s="65"/>
     </row>
     <row r="7" spans="1:29" ht="15.6">
-      <c r="A7" s="70"/>
-      <c r="B7" s="70"/>
-      <c r="C7" s="70"/>
-      <c r="D7" s="70"/>
-      <c r="E7" s="72"/>
-      <c r="F7" s="72"/>
-      <c r="G7" s="72"/>
-      <c r="H7" s="72"/>
-      <c r="I7" s="72"/>
-      <c r="J7" s="72"/>
-      <c r="K7" s="72"/>
-      <c r="L7" s="72"/>
-      <c r="M7" s="72"/>
-      <c r="N7" s="72"/>
-      <c r="O7" s="72"/>
-      <c r="P7" s="72"/>
-      <c r="Q7" s="72"/>
-      <c r="R7" s="71"/>
-      <c r="S7" s="71" t="s">
+      <c r="A7" s="64"/>
+      <c r="B7" s="64"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="66"/>
+      <c r="J7" s="66"/>
+      <c r="K7" s="66"/>
+      <c r="L7" s="66"/>
+      <c r="M7" s="66"/>
+      <c r="N7" s="66"/>
+      <c r="O7" s="66"/>
+      <c r="P7" s="66"/>
+      <c r="Q7" s="66"/>
+      <c r="R7" s="65"/>
+      <c r="S7" s="65" t="s">
         <v>54</v>
       </c>
-      <c r="T7" s="71" t="s">
+      <c r="T7" s="65" t="s">
         <v>138</v>
       </c>
-      <c r="U7" s="71"/>
-      <c r="V7" s="71"/>
-      <c r="W7" s="71"/>
-      <c r="X7" s="71"/>
-      <c r="Y7" s="71"/>
-      <c r="Z7" s="71"/>
-      <c r="AA7" s="71"/>
-      <c r="AB7" s="71"/>
-      <c r="AC7" s="71"/>
+      <c r="U7" s="65"/>
+      <c r="V7" s="65"/>
+      <c r="W7" s="65"/>
+      <c r="X7" s="65"/>
+      <c r="Y7" s="65"/>
+      <c r="Z7" s="65"/>
+      <c r="AA7" s="65"/>
+      <c r="AB7" s="65"/>
+      <c r="AC7" s="65"/>
     </row>
     <row r="8" spans="1:29" ht="17.399999999999999">
-      <c r="A8" s="70"/>
-      <c r="B8" s="70"/>
-      <c r="C8" s="70"/>
-      <c r="D8" s="70"/>
-      <c r="E8" s="73" t="s">
+      <c r="A8" s="64"/>
+      <c r="B8" s="64"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="147" t="s">
         <v>136</v>
       </c>
-      <c r="F8" s="73"/>
-      <c r="G8" s="73"/>
-      <c r="H8" s="73"/>
-      <c r="I8" s="73"/>
-      <c r="J8" s="73"/>
-      <c r="K8" s="73"/>
-      <c r="L8" s="73"/>
-      <c r="M8" s="73"/>
-      <c r="N8" s="73"/>
-      <c r="O8" s="73"/>
-      <c r="P8" s="73"/>
-      <c r="Q8" s="73"/>
-      <c r="R8" s="71"/>
-      <c r="S8" s="71"/>
-      <c r="T8" s="71" t="s">
+      <c r="F8" s="147"/>
+      <c r="G8" s="147"/>
+      <c r="H8" s="147"/>
+      <c r="I8" s="147"/>
+      <c r="J8" s="147"/>
+      <c r="K8" s="147"/>
+      <c r="L8" s="147"/>
+      <c r="M8" s="147"/>
+      <c r="N8" s="147"/>
+      <c r="O8" s="147"/>
+      <c r="P8" s="147"/>
+      <c r="Q8" s="147"/>
+      <c r="R8" s="65"/>
+      <c r="S8" s="65"/>
+      <c r="T8" s="65" t="s">
         <v>139</v>
       </c>
-      <c r="U8" s="71"/>
-      <c r="V8" s="71"/>
-      <c r="W8" s="71"/>
-      <c r="X8" s="71"/>
-      <c r="Y8" s="71"/>
-      <c r="Z8" s="71"/>
-      <c r="AA8" s="71"/>
-      <c r="AB8" s="71"/>
-      <c r="AC8" s="71"/>
+      <c r="U8" s="65"/>
+      <c r="V8" s="65"/>
+      <c r="W8" s="65"/>
+      <c r="X8" s="65"/>
+      <c r="Y8" s="65"/>
+      <c r="Z8" s="65"/>
+      <c r="AA8" s="65"/>
+      <c r="AB8" s="65"/>
+      <c r="AC8" s="65"/>
     </row>
     <row r="9" spans="1:29" ht="15.6">
-      <c r="A9" s="70"/>
-      <c r="B9" s="70"/>
-      <c r="C9" s="70"/>
-      <c r="D9" s="70"/>
-      <c r="E9" s="72"/>
-      <c r="F9" s="72"/>
-      <c r="G9" s="72"/>
-      <c r="H9" s="72"/>
-      <c r="I9" s="72"/>
-      <c r="J9" s="72"/>
-      <c r="K9" s="72"/>
-      <c r="L9" s="72"/>
-      <c r="M9" s="72"/>
-      <c r="N9" s="72"/>
-      <c r="O9" s="72"/>
-      <c r="P9" s="72"/>
-      <c r="Q9" s="72"/>
-      <c r="R9" s="71"/>
-      <c r="S9" s="71"/>
-      <c r="T9" s="71"/>
-      <c r="U9" s="71"/>
-      <c r="V9" s="71"/>
-      <c r="W9" s="71"/>
-      <c r="X9" s="71"/>
-      <c r="Y9" s="71"/>
-      <c r="Z9" s="71"/>
-      <c r="AA9" s="71"/>
-      <c r="AB9" s="71"/>
-      <c r="AC9" s="71"/>
+      <c r="A9" s="64"/>
+      <c r="B9" s="64"/>
+      <c r="C9" s="64"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
+      <c r="H9" s="66"/>
+      <c r="I9" s="66"/>
+      <c r="J9" s="66"/>
+      <c r="K9" s="66"/>
+      <c r="L9" s="66"/>
+      <c r="M9" s="66"/>
+      <c r="N9" s="66"/>
+      <c r="O9" s="66"/>
+      <c r="P9" s="66"/>
+      <c r="Q9" s="66"/>
+      <c r="R9" s="65"/>
+      <c r="S9" s="65"/>
+      <c r="T9" s="65"/>
+      <c r="U9" s="65"/>
+      <c r="V9" s="65"/>
+      <c r="W9" s="65"/>
+      <c r="X9" s="65"/>
+      <c r="Y9" s="65"/>
+      <c r="Z9" s="65"/>
+      <c r="AA9" s="65"/>
+      <c r="AB9" s="65"/>
+      <c r="AC9" s="65"/>
     </row>
     <row r="10" spans="1:29" ht="15" thickBot="1">
-      <c r="A10" s="70"/>
-      <c r="B10" s="71"/>
-      <c r="C10" s="71"/>
-      <c r="D10" s="71"/>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="70"/>
-      <c r="H10" s="70"/>
-      <c r="I10" s="70"/>
-      <c r="J10" s="70"/>
-      <c r="K10" s="70"/>
-      <c r="L10" s="70"/>
-      <c r="M10" s="70"/>
-      <c r="N10" s="70"/>
-      <c r="O10" s="70"/>
-      <c r="P10" s="70"/>
-      <c r="Q10" s="70"/>
-      <c r="R10" s="71"/>
-      <c r="S10" s="71"/>
-      <c r="T10" s="71"/>
-      <c r="U10" s="71"/>
-      <c r="V10" s="71"/>
-      <c r="W10" s="71"/>
-      <c r="X10" s="71"/>
-      <c r="Y10" s="71"/>
-      <c r="Z10" s="71"/>
-      <c r="AA10" s="71"/>
-      <c r="AB10" s="71"/>
-      <c r="AC10" s="71"/>
+      <c r="A10" s="64"/>
+      <c r="B10" s="65"/>
+      <c r="C10" s="65"/>
+      <c r="D10" s="65"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="64"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="64"/>
+      <c r="J10" s="64"/>
+      <c r="K10" s="64"/>
+      <c r="L10" s="64"/>
+      <c r="M10" s="64"/>
+      <c r="N10" s="64"/>
+      <c r="O10" s="64"/>
+      <c r="P10" s="64"/>
+      <c r="Q10" s="64"/>
+      <c r="R10" s="65"/>
+      <c r="S10" s="65"/>
+      <c r="T10" s="65"/>
+      <c r="U10" s="65"/>
+      <c r="V10" s="65"/>
+      <c r="W10" s="65"/>
+      <c r="X10" s="65"/>
+      <c r="Y10" s="65"/>
+      <c r="Z10" s="65"/>
+      <c r="AA10" s="65"/>
+      <c r="AB10" s="65"/>
+      <c r="AC10" s="65"/>
     </row>
     <row r="11" spans="1:29" ht="15" thickTop="1">
-      <c r="A11" s="74"/>
-      <c r="B11" s="75"/>
-      <c r="C11" s="76" t="s">
+      <c r="A11" s="67"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="D11" s="77">
+      <c r="D11" s="70">
         <v>40</v>
       </c>
-      <c r="E11" s="77">
+      <c r="E11" s="70">
         <v>41</v>
       </c>
-      <c r="F11" s="77">
+      <c r="F11" s="70">
         <v>42</v>
       </c>
-      <c r="G11" s="77">
+      <c r="G11" s="70">
         <v>43</v>
       </c>
-      <c r="H11" s="77">
+      <c r="H11" s="70">
         <v>44</v>
       </c>
-      <c r="I11" s="77">
+      <c r="I11" s="70">
         <v>45</v>
       </c>
-      <c r="J11" s="77">
+      <c r="J11" s="70">
         <v>46</v>
       </c>
-      <c r="K11" s="77">
+      <c r="K11" s="70">
         <v>47</v>
       </c>
-      <c r="L11" s="77">
+      <c r="L11" s="70">
         <v>48</v>
       </c>
-      <c r="M11" s="77">
+      <c r="M11" s="70">
         <v>49</v>
       </c>
-      <c r="N11" s="77">
+      <c r="N11" s="70">
         <v>50</v>
       </c>
-      <c r="O11" s="77">
+      <c r="O11" s="70">
         <v>51</v>
       </c>
-      <c r="P11" s="77">
+      <c r="P11" s="70">
         <v>52</v>
       </c>
-      <c r="Q11" s="77">
+      <c r="Q11" s="70">
         <v>1</v>
       </c>
-      <c r="R11" s="77">
+      <c r="R11" s="70">
         <v>2</v>
       </c>
-      <c r="S11" s="77">
+      <c r="S11" s="70">
         <v>3</v>
       </c>
-      <c r="T11" s="78">
+      <c r="T11" s="71">
         <v>4</v>
       </c>
-      <c r="U11" s="79">
+      <c r="U11" s="72">
         <v>5</v>
       </c>
-      <c r="V11" s="79">
+      <c r="V11" s="72">
         <v>6</v>
       </c>
-      <c r="W11" s="79">
+      <c r="W11" s="72">
         <v>7</v>
       </c>
-      <c r="X11" s="71"/>
-      <c r="Y11" s="71"/>
-      <c r="Z11" s="71"/>
-      <c r="AA11" s="71"/>
-      <c r="AB11" s="71"/>
-      <c r="AC11" s="71"/>
+      <c r="X11" s="65"/>
+      <c r="Y11" s="65"/>
+      <c r="Z11" s="65"/>
+      <c r="AA11" s="65"/>
+      <c r="AB11" s="65"/>
+      <c r="AC11" s="65"/>
     </row>
     <row r="12" spans="1:29">
-      <c r="A12" s="80"/>
-      <c r="B12" s="81"/>
-      <c r="C12" s="82" t="s">
+      <c r="A12" s="73"/>
+      <c r="B12" s="74"/>
+      <c r="C12" s="75" t="s">
         <v>68</v>
       </c>
-      <c r="D12" s="83">
+      <c r="D12" s="76">
         <v>1</v>
       </c>
-      <c r="E12" s="83">
+      <c r="E12" s="76">
         <v>2</v>
       </c>
-      <c r="F12" s="83">
+      <c r="F12" s="76">
         <v>3</v>
       </c>
-      <c r="G12" s="83">
+      <c r="G12" s="76">
         <v>4</v>
       </c>
-      <c r="H12" s="83">
+      <c r="H12" s="76">
         <v>5</v>
       </c>
-      <c r="I12" s="83">
+      <c r="I12" s="76">
         <v>6</v>
       </c>
-      <c r="J12" s="83">
+      <c r="J12" s="76">
         <v>7</v>
       </c>
-      <c r="K12" s="83">
+      <c r="K12" s="76">
         <v>8</v>
       </c>
-      <c r="L12" s="83">
+      <c r="L12" s="76">
         <v>9</v>
       </c>
-      <c r="M12" s="83">
+      <c r="M12" s="76">
         <v>10</v>
       </c>
-      <c r="N12" s="83">
+      <c r="N12" s="76">
         <v>11</v>
       </c>
-      <c r="O12" s="83">
+      <c r="O12" s="76">
         <v>12</v>
       </c>
-      <c r="P12" s="83">
+      <c r="P12" s="76">
         <v>13</v>
       </c>
-      <c r="Q12" s="83">
+      <c r="Q12" s="76">
         <v>14</v>
       </c>
-      <c r="R12" s="83">
+      <c r="R12" s="76">
         <v>15</v>
       </c>
-      <c r="S12" s="83">
+      <c r="S12" s="76">
         <v>16</v>
       </c>
-      <c r="T12" s="84">
+      <c r="T12" s="77">
         <v>17</v>
       </c>
-      <c r="U12" s="85">
+      <c r="U12" s="78">
         <v>18</v>
       </c>
-      <c r="V12" s="85">
+      <c r="V12" s="78">
         <v>19</v>
       </c>
-      <c r="W12" s="85">
+      <c r="W12" s="78">
         <v>20</v>
       </c>
-      <c r="X12" s="71"/>
-      <c r="Y12" s="71"/>
-      <c r="Z12" s="71"/>
-      <c r="AA12" s="71"/>
-      <c r="AB12" s="71"/>
-      <c r="AC12" s="71"/>
+      <c r="X12" s="65"/>
+      <c r="Y12" s="65"/>
+      <c r="Z12" s="65"/>
+      <c r="AA12" s="65"/>
+      <c r="AB12" s="65"/>
+      <c r="AC12" s="65"/>
     </row>
     <row r="13" spans="1:29" ht="15" thickBot="1">
-      <c r="A13" s="86" t="s">
+      <c r="A13" s="79" t="s">
         <v>69</v>
       </c>
-      <c r="B13" s="87" t="s">
+      <c r="B13" s="80" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="88" t="s">
+      <c r="C13" s="81" t="s">
         <v>71</v>
       </c>
-      <c r="D13" s="89"/>
-      <c r="E13" s="89"/>
-      <c r="F13" s="89"/>
-      <c r="G13" s="89"/>
-      <c r="H13" s="89"/>
-      <c r="I13" s="89"/>
-      <c r="J13" s="89"/>
-      <c r="K13" s="89"/>
-      <c r="L13" s="89"/>
-      <c r="M13" s="89"/>
-      <c r="N13" s="89"/>
-      <c r="O13" s="89"/>
-      <c r="P13" s="89"/>
-      <c r="Q13" s="89"/>
-      <c r="R13" s="89"/>
-      <c r="S13" s="89"/>
-      <c r="T13" s="90"/>
-      <c r="U13" s="91"/>
-      <c r="V13" s="91"/>
-      <c r="W13" s="91"/>
-      <c r="X13" s="71"/>
-      <c r="Y13" s="71"/>
-      <c r="Z13" s="71"/>
-      <c r="AA13" s="71"/>
-      <c r="AB13" s="71"/>
-      <c r="AC13" s="71"/>
+      <c r="D13" s="82"/>
+      <c r="E13" s="82"/>
+      <c r="F13" s="82"/>
+      <c r="G13" s="82"/>
+      <c r="H13" s="82"/>
+      <c r="I13" s="82"/>
+      <c r="J13" s="82"/>
+      <c r="K13" s="82"/>
+      <c r="L13" s="82"/>
+      <c r="M13" s="82"/>
+      <c r="N13" s="82"/>
+      <c r="O13" s="82"/>
+      <c r="P13" s="82"/>
+      <c r="Q13" s="82"/>
+      <c r="R13" s="82"/>
+      <c r="S13" s="82"/>
+      <c r="T13" s="83"/>
+      <c r="U13" s="84"/>
+      <c r="V13" s="84"/>
+      <c r="W13" s="84"/>
+      <c r="X13" s="65"/>
+      <c r="Y13" s="65"/>
+      <c r="Z13" s="65"/>
+      <c r="AA13" s="65"/>
+      <c r="AB13" s="65"/>
+      <c r="AC13" s="65"/>
     </row>
     <row r="14" spans="1:29">
-      <c r="A14" s="92">
+      <c r="A14" s="85">
         <v>1</v>
       </c>
-      <c r="B14" s="93" t="s">
+      <c r="B14" s="86" t="s">
         <v>140</v>
       </c>
-      <c r="C14" s="94">
+      <c r="C14" s="87">
         <v>2</v>
       </c>
-      <c r="D14" s="95"/>
-      <c r="E14" s="96"/>
-      <c r="F14" s="96"/>
-      <c r="G14" s="96"/>
-      <c r="H14" s="96"/>
-      <c r="I14" s="96"/>
-      <c r="J14" s="96"/>
-      <c r="K14" s="96"/>
-      <c r="L14" s="96"/>
-      <c r="M14" s="96"/>
-      <c r="N14" s="96"/>
-      <c r="O14" s="96"/>
-      <c r="P14" s="96"/>
-      <c r="Q14" s="96"/>
-      <c r="R14" s="96"/>
-      <c r="S14" s="96"/>
-      <c r="T14" s="96"/>
-      <c r="U14" s="96"/>
-      <c r="V14" s="97"/>
-      <c r="W14" s="97"/>
-      <c r="X14" s="71"/>
-      <c r="Y14" s="71"/>
-      <c r="Z14" s="71"/>
-      <c r="AA14" s="71"/>
-      <c r="AB14" s="71"/>
-      <c r="AC14" s="71"/>
+      <c r="D14" s="88"/>
+      <c r="E14" s="89"/>
+      <c r="F14" s="89"/>
+      <c r="G14" s="89"/>
+      <c r="H14" s="89"/>
+      <c r="I14" s="89"/>
+      <c r="J14" s="89"/>
+      <c r="K14" s="89"/>
+      <c r="L14" s="89"/>
+      <c r="M14" s="89"/>
+      <c r="N14" s="89"/>
+      <c r="O14" s="89"/>
+      <c r="P14" s="89"/>
+      <c r="Q14" s="89"/>
+      <c r="R14" s="89"/>
+      <c r="S14" s="89"/>
+      <c r="T14" s="89"/>
+      <c r="U14" s="89"/>
+      <c r="V14" s="90"/>
+      <c r="W14" s="90"/>
+      <c r="X14" s="65"/>
+      <c r="Y14" s="65"/>
+      <c r="Z14" s="65"/>
+      <c r="AA14" s="65"/>
+      <c r="AB14" s="65"/>
+      <c r="AC14" s="65"/>
     </row>
     <row r="15" spans="1:29">
-      <c r="A15" s="80">
+      <c r="A15" s="73">
         <v>2</v>
       </c>
-      <c r="B15" s="93" t="s">
+      <c r="B15" s="86" t="s">
         <v>141</v>
       </c>
-      <c r="C15" s="94">
+      <c r="C15" s="87">
         <v>1</v>
       </c>
-      <c r="D15" s="70"/>
-      <c r="E15" s="96"/>
-      <c r="F15" s="96"/>
-      <c r="G15" s="96"/>
-      <c r="H15" s="96"/>
-      <c r="I15" s="96"/>
-      <c r="J15" s="96"/>
-      <c r="K15" s="96"/>
-      <c r="L15" s="96"/>
-      <c r="M15" s="96"/>
-      <c r="N15" s="96"/>
-      <c r="O15" s="96"/>
-      <c r="P15" s="96"/>
-      <c r="Q15" s="96"/>
-      <c r="R15" s="96"/>
-      <c r="S15" s="96"/>
-      <c r="T15" s="96"/>
-      <c r="U15" s="96"/>
-      <c r="V15" s="97"/>
-      <c r="W15" s="97"/>
-      <c r="X15" s="71"/>
-      <c r="Y15" s="71"/>
-      <c r="Z15" s="71"/>
-      <c r="AA15" s="71"/>
-      <c r="AB15" s="71"/>
-      <c r="AC15" s="71"/>
+      <c r="D15" s="64"/>
+      <c r="E15" s="89"/>
+      <c r="F15" s="89"/>
+      <c r="G15" s="89"/>
+      <c r="H15" s="89"/>
+      <c r="I15" s="89"/>
+      <c r="J15" s="89"/>
+      <c r="K15" s="89"/>
+      <c r="L15" s="89"/>
+      <c r="M15" s="89"/>
+      <c r="N15" s="89"/>
+      <c r="O15" s="89"/>
+      <c r="P15" s="89"/>
+      <c r="Q15" s="89"/>
+      <c r="R15" s="89"/>
+      <c r="S15" s="89"/>
+      <c r="T15" s="89"/>
+      <c r="U15" s="89"/>
+      <c r="V15" s="90"/>
+      <c r="W15" s="90"/>
+      <c r="X15" s="65"/>
+      <c r="Y15" s="65"/>
+      <c r="Z15" s="65"/>
+      <c r="AA15" s="65"/>
+      <c r="AB15" s="65"/>
+      <c r="AC15" s="65"/>
     </row>
     <row r="16" spans="1:29">
-      <c r="A16" s="80">
+      <c r="A16" s="73">
         <v>3</v>
       </c>
-      <c r="B16" s="93" t="s">
+      <c r="B16" s="86" t="s">
         <v>142</v>
       </c>
-      <c r="C16" s="94">
+      <c r="C16" s="87">
         <v>2</v>
       </c>
-      <c r="D16" s="70"/>
-      <c r="E16" s="96"/>
-      <c r="F16" s="96"/>
-      <c r="G16" s="96"/>
-      <c r="H16" s="96"/>
-      <c r="I16" s="96"/>
-      <c r="J16" s="96"/>
-      <c r="K16" s="96"/>
-      <c r="L16" s="96"/>
-      <c r="M16" s="96"/>
-      <c r="N16" s="96"/>
-      <c r="O16" s="96"/>
-      <c r="P16" s="96"/>
-      <c r="Q16" s="96"/>
-      <c r="R16" s="96"/>
-      <c r="S16" s="96"/>
-      <c r="T16" s="96"/>
-      <c r="U16" s="96"/>
-      <c r="V16" s="97"/>
-      <c r="W16" s="97"/>
-      <c r="X16" s="71"/>
-      <c r="Y16" s="71"/>
-      <c r="Z16" s="71"/>
-      <c r="AA16" s="71"/>
-      <c r="AB16" s="71"/>
-      <c r="AC16" s="71"/>
+      <c r="D16" s="64"/>
+      <c r="E16" s="89"/>
+      <c r="F16" s="89"/>
+      <c r="G16" s="89"/>
+      <c r="H16" s="89"/>
+      <c r="I16" s="89"/>
+      <c r="J16" s="89"/>
+      <c r="K16" s="89"/>
+      <c r="L16" s="89"/>
+      <c r="M16" s="89"/>
+      <c r="N16" s="89"/>
+      <c r="O16" s="89"/>
+      <c r="P16" s="89"/>
+      <c r="Q16" s="89"/>
+      <c r="R16" s="89"/>
+      <c r="S16" s="89"/>
+      <c r="T16" s="89"/>
+      <c r="U16" s="89"/>
+      <c r="V16" s="90"/>
+      <c r="W16" s="90"/>
+      <c r="X16" s="65"/>
+      <c r="Y16" s="65"/>
+      <c r="Z16" s="65"/>
+      <c r="AA16" s="65"/>
+      <c r="AB16" s="65"/>
+      <c r="AC16" s="65"/>
     </row>
     <row r="17" spans="1:29">
-      <c r="A17" s="80">
+      <c r="A17" s="73">
         <v>4</v>
       </c>
-      <c r="B17" s="98" t="s">
+      <c r="B17" s="91" t="s">
         <v>143</v>
       </c>
-      <c r="C17" s="94">
+      <c r="C17" s="87">
         <v>2</v>
       </c>
-      <c r="D17" s="70"/>
-      <c r="E17" s="96"/>
-      <c r="F17" s="96"/>
-      <c r="G17" s="96"/>
-      <c r="H17" s="96"/>
-      <c r="I17" s="96"/>
-      <c r="J17" s="96"/>
-      <c r="K17" s="96"/>
-      <c r="L17" s="96"/>
-      <c r="M17" s="96"/>
-      <c r="N17" s="96"/>
-      <c r="O17" s="96"/>
-      <c r="P17" s="96"/>
-      <c r="Q17" s="96"/>
-      <c r="R17" s="96"/>
-      <c r="S17" s="96"/>
-      <c r="T17" s="96"/>
-      <c r="U17" s="96"/>
-      <c r="V17" s="97"/>
-      <c r="W17" s="97"/>
-      <c r="X17" s="71"/>
-      <c r="Y17" s="71"/>
-      <c r="Z17" s="71"/>
-      <c r="AA17" s="71"/>
-      <c r="AB17" s="71"/>
-      <c r="AC17" s="71"/>
+      <c r="D17" s="64"/>
+      <c r="E17" s="89"/>
+      <c r="F17" s="89"/>
+      <c r="G17" s="89"/>
+      <c r="H17" s="89"/>
+      <c r="I17" s="89"/>
+      <c r="J17" s="89"/>
+      <c r="K17" s="89"/>
+      <c r="L17" s="89"/>
+      <c r="M17" s="89"/>
+      <c r="N17" s="89"/>
+      <c r="O17" s="89"/>
+      <c r="P17" s="89"/>
+      <c r="Q17" s="89"/>
+      <c r="R17" s="89"/>
+      <c r="S17" s="89"/>
+      <c r="T17" s="89"/>
+      <c r="U17" s="89"/>
+      <c r="V17" s="90"/>
+      <c r="W17" s="90"/>
+      <c r="X17" s="65"/>
+      <c r="Y17" s="65"/>
+      <c r="Z17" s="65"/>
+      <c r="AA17" s="65"/>
+      <c r="AB17" s="65"/>
+      <c r="AC17" s="65"/>
     </row>
     <row r="18" spans="1:29">
-      <c r="A18" s="80">
+      <c r="A18" s="73">
         <v>5</v>
       </c>
-      <c r="B18" s="99" t="s">
+      <c r="B18" s="92" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="100">
+      <c r="C18" s="93">
         <v>16</v>
       </c>
-      <c r="D18" s="101"/>
-      <c r="E18" s="102"/>
-      <c r="F18" s="103"/>
-      <c r="G18" s="103"/>
-      <c r="H18" s="103"/>
-      <c r="I18" s="103"/>
-      <c r="J18" s="103"/>
-      <c r="K18" s="103"/>
-      <c r="L18" s="103"/>
-      <c r="M18" s="103"/>
-      <c r="N18" s="103"/>
-      <c r="O18" s="103"/>
-      <c r="P18" s="103"/>
-      <c r="Q18" s="103"/>
-      <c r="R18" s="103"/>
-      <c r="S18" s="103"/>
-      <c r="T18" s="103"/>
-      <c r="U18" s="103"/>
-      <c r="V18" s="97"/>
-      <c r="W18" s="97"/>
-      <c r="X18" s="71"/>
-      <c r="Y18" s="71"/>
-      <c r="Z18" s="71"/>
-      <c r="AA18" s="71"/>
-      <c r="AB18" s="71"/>
-      <c r="AC18" s="71"/>
+      <c r="D18" s="94"/>
+      <c r="E18" s="95"/>
+      <c r="F18" s="96"/>
+      <c r="G18" s="96"/>
+      <c r="H18" s="96"/>
+      <c r="I18" s="96"/>
+      <c r="J18" s="96"/>
+      <c r="K18" s="96"/>
+      <c r="L18" s="96"/>
+      <c r="M18" s="96"/>
+      <c r="N18" s="96"/>
+      <c r="O18" s="96"/>
+      <c r="P18" s="96"/>
+      <c r="Q18" s="96"/>
+      <c r="R18" s="96"/>
+      <c r="S18" s="96"/>
+      <c r="T18" s="96"/>
+      <c r="U18" s="96"/>
+      <c r="V18" s="90"/>
+      <c r="W18" s="90"/>
+      <c r="X18" s="65"/>
+      <c r="Y18" s="65"/>
+      <c r="Z18" s="65"/>
+      <c r="AA18" s="65"/>
+      <c r="AB18" s="65"/>
+      <c r="AC18" s="65"/>
     </row>
     <row r="19" spans="1:29">
-      <c r="A19" s="80">
+      <c r="A19" s="73">
         <v>6</v>
       </c>
-      <c r="B19" s="108" t="s">
+      <c r="B19" s="101" t="s">
         <v>158</v>
       </c>
-      <c r="C19" s="94">
+      <c r="C19" s="87">
         <v>6</v>
       </c>
-      <c r="D19" s="101"/>
-      <c r="E19" s="104"/>
-      <c r="F19" s="97"/>
-      <c r="G19" s="97"/>
-      <c r="H19" s="97"/>
-      <c r="I19" s="97"/>
-      <c r="J19" s="97"/>
-      <c r="K19" s="97"/>
-      <c r="L19" s="97"/>
-      <c r="M19" s="97"/>
-      <c r="N19" s="97"/>
-      <c r="O19" s="97"/>
-      <c r="P19" s="97"/>
-      <c r="Q19" s="97"/>
-      <c r="R19" s="97"/>
-      <c r="S19" s="97"/>
-      <c r="T19" s="97"/>
-      <c r="U19" s="97"/>
-      <c r="V19" s="97"/>
-      <c r="W19" s="97"/>
-      <c r="X19" s="71"/>
-      <c r="Y19" s="71"/>
-      <c r="Z19" s="71"/>
-      <c r="AA19" s="71"/>
-      <c r="AB19" s="71"/>
-      <c r="AC19" s="71"/>
+      <c r="D19" s="94"/>
+      <c r="E19" s="97"/>
+      <c r="F19" s="90"/>
+      <c r="G19" s="90"/>
+      <c r="H19" s="90"/>
+      <c r="I19" s="90"/>
+      <c r="J19" s="90"/>
+      <c r="K19" s="90"/>
+      <c r="L19" s="90"/>
+      <c r="M19" s="90"/>
+      <c r="N19" s="90"/>
+      <c r="O19" s="90"/>
+      <c r="P19" s="90"/>
+      <c r="Q19" s="90"/>
+      <c r="R19" s="90"/>
+      <c r="S19" s="90"/>
+      <c r="T19" s="90"/>
+      <c r="U19" s="90"/>
+      <c r="V19" s="90"/>
+      <c r="W19" s="90"/>
+      <c r="X19" s="65"/>
+      <c r="Y19" s="65"/>
+      <c r="Z19" s="65"/>
+      <c r="AA19" s="65"/>
+      <c r="AB19" s="65"/>
+      <c r="AC19" s="65"/>
     </row>
     <row r="20" spans="1:29">
-      <c r="A20" s="80">
+      <c r="A20" s="73">
         <v>7</v>
       </c>
-      <c r="B20" s="105" t="s">
+      <c r="B20" s="98" t="s">
         <v>144</v>
       </c>
-      <c r="C20" s="106">
+      <c r="C20" s="99">
         <v>5</v>
       </c>
-      <c r="D20" s="101"/>
-      <c r="E20" s="104"/>
-      <c r="F20" s="97"/>
-      <c r="G20" s="97"/>
-      <c r="H20" s="97"/>
-      <c r="I20" s="97"/>
-      <c r="J20" s="97"/>
-      <c r="K20" s="97"/>
-      <c r="L20" s="97"/>
-      <c r="M20" s="97"/>
-      <c r="N20" s="97"/>
-      <c r="O20" s="97"/>
-      <c r="P20" s="97"/>
-      <c r="Q20" s="97"/>
-      <c r="R20" s="97"/>
-      <c r="S20" s="97"/>
-      <c r="T20" s="97"/>
-      <c r="U20" s="97"/>
-      <c r="V20" s="97"/>
-      <c r="W20" s="97"/>
-      <c r="X20" s="71"/>
-      <c r="Y20" s="71"/>
-      <c r="Z20" s="71"/>
-      <c r="AA20" s="71"/>
-      <c r="AB20" s="71"/>
-      <c r="AC20" s="71"/>
+      <c r="D20" s="94"/>
+      <c r="E20" s="97"/>
+      <c r="F20" s="90"/>
+      <c r="G20" s="90"/>
+      <c r="H20" s="90"/>
+      <c r="I20" s="90"/>
+      <c r="J20" s="90"/>
+      <c r="K20" s="90"/>
+      <c r="L20" s="90"/>
+      <c r="M20" s="90"/>
+      <c r="N20" s="90"/>
+      <c r="O20" s="90"/>
+      <c r="P20" s="90"/>
+      <c r="Q20" s="90"/>
+      <c r="R20" s="90"/>
+      <c r="S20" s="90"/>
+      <c r="T20" s="90"/>
+      <c r="U20" s="90"/>
+      <c r="V20" s="90"/>
+      <c r="W20" s="90"/>
+      <c r="X20" s="65"/>
+      <c r="Y20" s="65"/>
+      <c r="Z20" s="65"/>
+      <c r="AA20" s="65"/>
+      <c r="AB20" s="65"/>
+      <c r="AC20" s="65"/>
     </row>
     <row r="21" spans="1:29">
-      <c r="A21" s="80">
+      <c r="A21" s="73">
         <v>8</v>
       </c>
-      <c r="B21" s="107" t="s">
+      <c r="B21" s="100" t="s">
         <v>145</v>
       </c>
-      <c r="C21" s="106">
+      <c r="C21" s="99">
         <v>5</v>
       </c>
-      <c r="D21" s="101"/>
-      <c r="E21" s="104"/>
-      <c r="F21" s="97"/>
-      <c r="G21" s="97"/>
-      <c r="H21" s="97"/>
-      <c r="I21" s="97"/>
-      <c r="J21" s="97"/>
-      <c r="K21" s="97"/>
-      <c r="L21" s="97"/>
-      <c r="M21" s="97"/>
-      <c r="N21" s="97"/>
-      <c r="O21" s="97"/>
-      <c r="P21" s="97"/>
-      <c r="Q21" s="97"/>
-      <c r="R21" s="97"/>
-      <c r="S21" s="97"/>
-      <c r="T21" s="97"/>
-      <c r="U21" s="97"/>
-      <c r="V21" s="97"/>
-      <c r="W21" s="97"/>
-      <c r="X21" s="71"/>
-      <c r="Y21" s="71"/>
-      <c r="Z21" s="71"/>
-      <c r="AA21" s="71"/>
-      <c r="AB21" s="71"/>
-      <c r="AC21" s="71"/>
+      <c r="D21" s="94"/>
+      <c r="E21" s="97"/>
+      <c r="F21" s="90"/>
+      <c r="G21" s="90"/>
+      <c r="H21" s="90"/>
+      <c r="I21" s="90"/>
+      <c r="J21" s="90"/>
+      <c r="K21" s="90"/>
+      <c r="L21" s="90"/>
+      <c r="M21" s="90"/>
+      <c r="N21" s="90"/>
+      <c r="O21" s="90"/>
+      <c r="P21" s="90"/>
+      <c r="Q21" s="90"/>
+      <c r="R21" s="90"/>
+      <c r="S21" s="90"/>
+      <c r="T21" s="90"/>
+      <c r="U21" s="90"/>
+      <c r="V21" s="90"/>
+      <c r="W21" s="90"/>
+      <c r="X21" s="65"/>
+      <c r="Y21" s="65"/>
+      <c r="Z21" s="65"/>
+      <c r="AA21" s="65"/>
+      <c r="AB21" s="65"/>
+      <c r="AC21" s="65"/>
     </row>
     <row r="22" spans="1:29">
-      <c r="A22" s="80">
+      <c r="A22" s="73">
         <v>9</v>
       </c>
-      <c r="B22" s="108" t="s">
+      <c r="B22" s="105" t="s">
         <v>146</v>
       </c>
-      <c r="C22" s="106">
+      <c r="C22" s="99">
         <v>5</v>
       </c>
-      <c r="D22" s="101"/>
-      <c r="E22" s="104"/>
-      <c r="F22" s="97"/>
-      <c r="G22" s="97"/>
-      <c r="H22" s="97"/>
-      <c r="I22" s="97"/>
-      <c r="J22" s="97"/>
-      <c r="K22" s="97"/>
-      <c r="L22" s="97"/>
-      <c r="M22" s="97"/>
-      <c r="N22" s="97"/>
-      <c r="O22" s="97"/>
-      <c r="P22" s="97"/>
-      <c r="Q22" s="97"/>
-      <c r="R22" s="97"/>
-      <c r="S22" s="97"/>
-      <c r="T22" s="97"/>
-      <c r="U22" s="97"/>
-      <c r="V22" s="97"/>
-      <c r="W22" s="97"/>
-      <c r="X22" s="71"/>
-      <c r="Y22" s="71"/>
-      <c r="Z22" s="71"/>
-      <c r="AA22" s="71"/>
-      <c r="AB22" s="71"/>
-      <c r="AC22" s="71"/>
+      <c r="D22" s="94"/>
+      <c r="E22" s="97"/>
+      <c r="F22" s="90"/>
+      <c r="G22" s="90"/>
+      <c r="H22" s="90"/>
+      <c r="I22" s="90"/>
+      <c r="J22" s="90"/>
+      <c r="K22" s="90"/>
+      <c r="L22" s="90"/>
+      <c r="M22" s="90"/>
+      <c r="N22" s="90"/>
+      <c r="O22" s="90"/>
+      <c r="P22" s="90"/>
+      <c r="Q22" s="90"/>
+      <c r="R22" s="90"/>
+      <c r="S22" s="90"/>
+      <c r="T22" s="90"/>
+      <c r="U22" s="90"/>
+      <c r="V22" s="90"/>
+      <c r="W22" s="90"/>
+      <c r="X22" s="65"/>
+      <c r="Y22" s="65"/>
+      <c r="Z22" s="65"/>
+      <c r="AA22" s="65"/>
+      <c r="AB22" s="65"/>
+      <c r="AC22" s="65"/>
     </row>
     <row r="23" spans="1:29">
-      <c r="A23" s="80">
+      <c r="A23" s="73">
         <v>10</v>
       </c>
-      <c r="B23" s="107" t="s">
+      <c r="B23" s="100" t="s">
         <v>147</v>
       </c>
-      <c r="C23" s="106">
+      <c r="C23" s="99">
         <v>5</v>
       </c>
-      <c r="D23" s="101"/>
-      <c r="E23" s="104"/>
-      <c r="F23" s="97"/>
-      <c r="G23" s="97"/>
-      <c r="H23" s="97"/>
-      <c r="I23" s="97"/>
-      <c r="J23" s="97"/>
-      <c r="K23" s="97"/>
-      <c r="L23" s="97"/>
-      <c r="M23" s="97"/>
-      <c r="N23" s="97"/>
-      <c r="O23" s="97"/>
-      <c r="P23" s="97"/>
-      <c r="Q23" s="97"/>
-      <c r="R23" s="97"/>
-      <c r="S23" s="97"/>
-      <c r="T23" s="97"/>
-      <c r="U23" s="97"/>
-      <c r="V23" s="97"/>
-      <c r="W23" s="97"/>
-      <c r="X23" s="71"/>
-      <c r="Y23" s="71"/>
-      <c r="Z23" s="71"/>
-      <c r="AA23" s="71"/>
-      <c r="AB23" s="71"/>
-      <c r="AC23" s="71"/>
+      <c r="D23" s="94"/>
+      <c r="E23" s="97"/>
+      <c r="F23" s="90"/>
+      <c r="G23" s="90"/>
+      <c r="H23" s="90"/>
+      <c r="I23" s="90"/>
+      <c r="J23" s="90"/>
+      <c r="K23" s="90"/>
+      <c r="L23" s="90"/>
+      <c r="M23" s="90"/>
+      <c r="N23" s="90"/>
+      <c r="O23" s="90"/>
+      <c r="P23" s="90"/>
+      <c r="Q23" s="90"/>
+      <c r="R23" s="90"/>
+      <c r="S23" s="90"/>
+      <c r="T23" s="90"/>
+      <c r="U23" s="90"/>
+      <c r="V23" s="90"/>
+      <c r="W23" s="90"/>
+      <c r="X23" s="65"/>
+      <c r="Y23" s="65"/>
+      <c r="Z23" s="65"/>
+      <c r="AA23" s="65"/>
+      <c r="AB23" s="65"/>
+      <c r="AC23" s="65"/>
     </row>
     <row r="24" spans="1:29">
-      <c r="A24" s="80">
+      <c r="A24" s="73">
         <v>11</v>
       </c>
-      <c r="B24" s="109" t="s">
+      <c r="B24" s="102" t="s">
         <v>175</v>
       </c>
-      <c r="C24" s="106">
+      <c r="C24" s="99">
         <v>5</v>
       </c>
-      <c r="D24" s="101"/>
-      <c r="E24" s="104"/>
-      <c r="F24" s="97"/>
-      <c r="G24" s="97"/>
-      <c r="H24" s="97"/>
-      <c r="I24" s="97"/>
-      <c r="J24" s="97"/>
-      <c r="K24" s="97"/>
-      <c r="L24" s="97"/>
-      <c r="M24" s="97"/>
-      <c r="N24" s="97"/>
-      <c r="O24" s="97"/>
-      <c r="P24" s="97"/>
-      <c r="Q24" s="97"/>
-      <c r="R24" s="97"/>
-      <c r="S24" s="97"/>
-      <c r="T24" s="97"/>
-      <c r="U24" s="97"/>
-      <c r="V24" s="97"/>
-      <c r="W24" s="97"/>
-      <c r="X24" s="71"/>
-      <c r="Y24" s="71"/>
-      <c r="Z24" s="71"/>
-      <c r="AA24" s="71"/>
-      <c r="AB24" s="71"/>
-      <c r="AC24" s="71"/>
+      <c r="D24" s="94"/>
+      <c r="E24" s="97"/>
+      <c r="F24" s="90"/>
+      <c r="G24" s="90"/>
+      <c r="H24" s="90"/>
+      <c r="I24" s="90"/>
+      <c r="J24" s="90"/>
+      <c r="K24" s="90"/>
+      <c r="L24" s="90"/>
+      <c r="M24" s="90"/>
+      <c r="N24" s="90"/>
+      <c r="O24" s="90"/>
+      <c r="P24" s="90"/>
+      <c r="Q24" s="90"/>
+      <c r="R24" s="90"/>
+      <c r="S24" s="90"/>
+      <c r="T24" s="90"/>
+      <c r="U24" s="90"/>
+      <c r="V24" s="90"/>
+      <c r="W24" s="90"/>
+      <c r="X24" s="65"/>
+      <c r="Y24" s="65"/>
+      <c r="Z24" s="65"/>
+      <c r="AA24" s="65"/>
+      <c r="AB24" s="65"/>
+      <c r="AC24" s="65"/>
     </row>
     <row r="25" spans="1:29">
-      <c r="A25" s="80">
+      <c r="A25" s="73">
         <v>12</v>
       </c>
-      <c r="B25" s="109" t="s">
+      <c r="B25" s="102" t="s">
         <v>148</v>
       </c>
-      <c r="C25" s="106">
+      <c r="C25" s="99">
         <v>7</v>
       </c>
-      <c r="D25" s="101"/>
-      <c r="E25" s="104"/>
-      <c r="F25" s="97"/>
-      <c r="G25" s="97"/>
-      <c r="H25" s="97"/>
-      <c r="I25" s="97"/>
-      <c r="J25" s="97"/>
-      <c r="K25" s="97"/>
-      <c r="L25" s="97"/>
-      <c r="M25" s="97"/>
-      <c r="N25" s="97"/>
-      <c r="O25" s="97"/>
-      <c r="P25" s="97"/>
-      <c r="Q25" s="97"/>
-      <c r="R25" s="97"/>
-      <c r="S25" s="97"/>
-      <c r="T25" s="97"/>
-      <c r="U25" s="97"/>
-      <c r="V25" s="97"/>
-      <c r="W25" s="97"/>
-      <c r="X25" s="71"/>
-      <c r="Y25" s="71"/>
-      <c r="Z25" s="71"/>
-      <c r="AA25" s="71"/>
-      <c r="AB25" s="71"/>
-      <c r="AC25" s="71"/>
+      <c r="D25" s="94"/>
+      <c r="E25" s="97"/>
+      <c r="F25" s="90"/>
+      <c r="G25" s="90"/>
+      <c r="H25" s="90"/>
+      <c r="I25" s="90"/>
+      <c r="J25" s="90"/>
+      <c r="K25" s="90"/>
+      <c r="L25" s="90"/>
+      <c r="M25" s="90"/>
+      <c r="N25" s="90"/>
+      <c r="O25" s="90"/>
+      <c r="P25" s="90"/>
+      <c r="Q25" s="90"/>
+      <c r="R25" s="90"/>
+      <c r="S25" s="90"/>
+      <c r="T25" s="90"/>
+      <c r="U25" s="90"/>
+      <c r="V25" s="90"/>
+      <c r="W25" s="90"/>
+      <c r="X25" s="65"/>
+      <c r="Y25" s="65"/>
+      <c r="Z25" s="65"/>
+      <c r="AA25" s="65"/>
+      <c r="AB25" s="65"/>
+      <c r="AC25" s="65"/>
     </row>
     <row r="26" spans="1:29">
-      <c r="A26" s="80">
+      <c r="A26" s="73">
         <v>13</v>
       </c>
-      <c r="B26" s="110" t="s">
+      <c r="B26" s="103" t="s">
         <v>149</v>
       </c>
-      <c r="C26" s="106">
+      <c r="C26" s="99">
         <v>5</v>
       </c>
-      <c r="D26" s="101"/>
-      <c r="E26" s="104"/>
-      <c r="F26" s="97"/>
-      <c r="G26" s="97"/>
-      <c r="H26" s="97"/>
-      <c r="I26" s="97"/>
-      <c r="J26" s="97"/>
-      <c r="K26" s="97"/>
-      <c r="L26" s="97"/>
-      <c r="M26" s="97"/>
-      <c r="N26" s="97"/>
-      <c r="O26" s="97"/>
-      <c r="P26" s="97"/>
-      <c r="Q26" s="97"/>
-      <c r="R26" s="97"/>
-      <c r="S26" s="97"/>
-      <c r="T26" s="97"/>
-      <c r="U26" s="97"/>
-      <c r="V26" s="97"/>
-      <c r="W26" s="97"/>
-      <c r="X26" s="71"/>
-      <c r="Y26" s="71"/>
-      <c r="Z26" s="71"/>
-      <c r="AA26" s="71"/>
-      <c r="AB26" s="71"/>
-      <c r="AC26" s="71"/>
+      <c r="D26" s="94"/>
+      <c r="E26" s="97"/>
+      <c r="F26" s="90"/>
+      <c r="G26" s="90"/>
+      <c r="H26" s="90"/>
+      <c r="I26" s="90"/>
+      <c r="J26" s="90"/>
+      <c r="K26" s="90"/>
+      <c r="L26" s="90"/>
+      <c r="M26" s="90"/>
+      <c r="N26" s="90"/>
+      <c r="O26" s="90"/>
+      <c r="P26" s="90"/>
+      <c r="Q26" s="90"/>
+      <c r="R26" s="90"/>
+      <c r="S26" s="90"/>
+      <c r="T26" s="90"/>
+      <c r="U26" s="90"/>
+      <c r="V26" s="90"/>
+      <c r="W26" s="90"/>
+      <c r="X26" s="65"/>
+      <c r="Y26" s="65"/>
+      <c r="Z26" s="65"/>
+      <c r="AA26" s="65"/>
+      <c r="AB26" s="65"/>
+      <c r="AC26" s="65"/>
     </row>
     <row r="27" spans="1:29">
-      <c r="A27" s="80">
+      <c r="A27" s="73">
         <v>14</v>
       </c>
-      <c r="B27" s="111" t="s">
+      <c r="B27" s="104" t="s">
         <v>150</v>
       </c>
-      <c r="C27" s="106">
+      <c r="C27" s="99">
         <v>6</v>
       </c>
-      <c r="D27" s="101"/>
-      <c r="E27" s="104"/>
-      <c r="F27" s="97"/>
-      <c r="G27" s="97"/>
-      <c r="H27" s="97"/>
-      <c r="I27" s="97"/>
-      <c r="J27" s="97"/>
-      <c r="K27" s="97"/>
-      <c r="L27" s="97"/>
-      <c r="M27" s="97"/>
-      <c r="N27" s="97"/>
-      <c r="O27" s="97"/>
-      <c r="P27" s="97"/>
-      <c r="Q27" s="97"/>
-      <c r="R27" s="97"/>
-      <c r="S27" s="97"/>
-      <c r="T27" s="97"/>
-      <c r="U27" s="97"/>
-      <c r="V27" s="97"/>
-      <c r="W27" s="97"/>
-      <c r="X27" s="71"/>
-      <c r="Y27" s="71"/>
-      <c r="Z27" s="71"/>
-      <c r="AA27" s="71"/>
-      <c r="AB27" s="71"/>
-      <c r="AC27" s="71"/>
+      <c r="D27" s="94"/>
+      <c r="E27" s="97"/>
+      <c r="F27" s="90"/>
+      <c r="G27" s="90"/>
+      <c r="H27" s="90"/>
+      <c r="I27" s="90"/>
+      <c r="J27" s="90"/>
+      <c r="K27" s="90"/>
+      <c r="L27" s="90"/>
+      <c r="M27" s="90"/>
+      <c r="N27" s="90"/>
+      <c r="O27" s="90"/>
+      <c r="P27" s="90"/>
+      <c r="Q27" s="90"/>
+      <c r="R27" s="90"/>
+      <c r="S27" s="90"/>
+      <c r="T27" s="90"/>
+      <c r="U27" s="90"/>
+      <c r="V27" s="90"/>
+      <c r="W27" s="90"/>
+      <c r="X27" s="65"/>
+      <c r="Y27" s="65"/>
+      <c r="Z27" s="65"/>
+      <c r="AA27" s="65"/>
+      <c r="AB27" s="65"/>
+      <c r="AC27" s="65"/>
     </row>
     <row r="28" spans="1:29">
-      <c r="A28" s="80">
+      <c r="A28" s="73">
         <v>15</v>
       </c>
-      <c r="B28" s="112" t="s">
+      <c r="B28" s="105" t="s">
         <v>151</v>
       </c>
-      <c r="C28" s="106">
+      <c r="C28" s="99">
         <v>6</v>
       </c>
-      <c r="D28" s="101"/>
-      <c r="E28" s="104"/>
-      <c r="F28" s="97"/>
-      <c r="G28" s="97"/>
-      <c r="H28" s="97"/>
-      <c r="I28" s="97"/>
-      <c r="J28" s="97"/>
-      <c r="K28" s="97"/>
-      <c r="L28" s="97"/>
-      <c r="M28" s="97"/>
-      <c r="N28" s="97"/>
-      <c r="O28" s="97"/>
-      <c r="P28" s="97"/>
-      <c r="Q28" s="97"/>
-      <c r="R28" s="97"/>
-      <c r="S28" s="97"/>
-      <c r="T28" s="97"/>
-      <c r="U28" s="97"/>
-      <c r="V28" s="97"/>
-      <c r="W28" s="97"/>
-      <c r="X28" s="71"/>
-      <c r="Y28" s="71"/>
-      <c r="Z28" s="71"/>
-      <c r="AA28" s="71"/>
-      <c r="AB28" s="71"/>
-      <c r="AC28" s="71"/>
+      <c r="D28" s="94"/>
+      <c r="E28" s="97"/>
+      <c r="F28" s="90"/>
+      <c r="G28" s="90"/>
+      <c r="H28" s="90"/>
+      <c r="I28" s="90"/>
+      <c r="J28" s="90"/>
+      <c r="K28" s="90"/>
+      <c r="L28" s="90"/>
+      <c r="M28" s="90"/>
+      <c r="N28" s="90"/>
+      <c r="O28" s="90"/>
+      <c r="P28" s="90"/>
+      <c r="Q28" s="90"/>
+      <c r="R28" s="90"/>
+      <c r="S28" s="90"/>
+      <c r="T28" s="90"/>
+      <c r="U28" s="90"/>
+      <c r="V28" s="90"/>
+      <c r="W28" s="90"/>
+      <c r="X28" s="65"/>
+      <c r="Y28" s="65"/>
+      <c r="Z28" s="65"/>
+      <c r="AA28" s="65"/>
+      <c r="AB28" s="65"/>
+      <c r="AC28" s="65"/>
     </row>
     <row r="29" spans="1:29">
-      <c r="A29" s="80">
+      <c r="A29" s="73">
         <v>16</v>
       </c>
-      <c r="B29" s="105" t="s">
+      <c r="B29" s="98" t="s">
         <v>152</v>
       </c>
-      <c r="C29" s="106">
+      <c r="C29" s="99">
         <v>6</v>
       </c>
-      <c r="D29" s="101"/>
-      <c r="E29" s="104"/>
-      <c r="F29" s="97"/>
-      <c r="G29" s="97"/>
-      <c r="H29" s="97"/>
-      <c r="I29" s="97"/>
-      <c r="J29" s="97"/>
-      <c r="K29" s="97"/>
-      <c r="L29" s="97"/>
-      <c r="M29" s="97"/>
-      <c r="N29" s="97"/>
-      <c r="O29" s="97"/>
-      <c r="P29" s="97"/>
-      <c r="Q29" s="97"/>
-      <c r="R29" s="97"/>
-      <c r="S29" s="97"/>
-      <c r="T29" s="97"/>
-      <c r="U29" s="97"/>
-      <c r="V29" s="97"/>
-      <c r="W29" s="97"/>
-      <c r="X29" s="71"/>
-      <c r="Y29" s="71"/>
-      <c r="Z29" s="71"/>
-      <c r="AA29" s="71"/>
-      <c r="AB29" s="71"/>
-      <c r="AC29" s="71"/>
+      <c r="D29" s="94"/>
+      <c r="E29" s="97"/>
+      <c r="F29" s="90"/>
+      <c r="G29" s="90"/>
+      <c r="H29" s="90"/>
+      <c r="I29" s="90"/>
+      <c r="J29" s="90"/>
+      <c r="K29" s="90"/>
+      <c r="L29" s="90"/>
+      <c r="M29" s="90"/>
+      <c r="N29" s="90"/>
+      <c r="O29" s="90"/>
+      <c r="P29" s="90"/>
+      <c r="Q29" s="90"/>
+      <c r="R29" s="90"/>
+      <c r="S29" s="90"/>
+      <c r="T29" s="90"/>
+      <c r="U29" s="90"/>
+      <c r="V29" s="90"/>
+      <c r="W29" s="90"/>
+      <c r="X29" s="65"/>
+      <c r="Y29" s="65"/>
+      <c r="Z29" s="65"/>
+      <c r="AA29" s="65"/>
+      <c r="AB29" s="65"/>
+      <c r="AC29" s="65"/>
     </row>
     <row r="30" spans="1:29">
-      <c r="A30" s="80">
+      <c r="A30" s="73">
         <v>17</v>
       </c>
-      <c r="B30" s="111" t="s">
+      <c r="B30" s="104" t="s">
         <v>153</v>
       </c>
-      <c r="C30" s="106">
+      <c r="C30" s="99">
         <v>7</v>
       </c>
-      <c r="D30" s="101"/>
-      <c r="E30" s="104"/>
-      <c r="F30" s="97"/>
-      <c r="G30" s="97"/>
-      <c r="H30" s="97"/>
-      <c r="I30" s="97"/>
-      <c r="J30" s="97"/>
-      <c r="K30" s="97"/>
-      <c r="L30" s="97"/>
-      <c r="M30" s="97"/>
-      <c r="N30" s="97"/>
-      <c r="O30" s="97"/>
-      <c r="P30" s="97"/>
-      <c r="Q30" s="97"/>
-      <c r="R30" s="97"/>
-      <c r="S30" s="97"/>
-      <c r="T30" s="97"/>
-      <c r="U30" s="97"/>
-      <c r="V30" s="97"/>
-      <c r="W30" s="97"/>
-      <c r="X30" s="71"/>
-      <c r="Y30" s="71"/>
-      <c r="Z30" s="71"/>
-      <c r="AA30" s="71"/>
-      <c r="AB30" s="71"/>
-      <c r="AC30" s="71"/>
+      <c r="D30" s="94"/>
+      <c r="E30" s="97"/>
+      <c r="F30" s="90"/>
+      <c r="G30" s="90"/>
+      <c r="H30" s="90"/>
+      <c r="I30" s="90"/>
+      <c r="J30" s="90"/>
+      <c r="K30" s="90"/>
+      <c r="L30" s="90"/>
+      <c r="M30" s="90"/>
+      <c r="N30" s="90"/>
+      <c r="O30" s="90"/>
+      <c r="P30" s="90"/>
+      <c r="Q30" s="90"/>
+      <c r="R30" s="90"/>
+      <c r="S30" s="90"/>
+      <c r="T30" s="90"/>
+      <c r="U30" s="90"/>
+      <c r="V30" s="90"/>
+      <c r="W30" s="90"/>
+      <c r="X30" s="65"/>
+      <c r="Y30" s="65"/>
+      <c r="Z30" s="65"/>
+      <c r="AA30" s="65"/>
+      <c r="AB30" s="65"/>
+      <c r="AC30" s="65"/>
     </row>
     <row r="31" spans="1:29">
-      <c r="A31" s="80">
+      <c r="A31" s="73">
         <v>18</v>
       </c>
-      <c r="B31" s="112" t="s">
+      <c r="B31" s="105" t="s">
         <v>154</v>
       </c>
-      <c r="C31" s="106">
+      <c r="C31" s="99">
         <v>7</v>
       </c>
-      <c r="D31" s="101"/>
-      <c r="E31" s="104"/>
-      <c r="F31" s="97"/>
-      <c r="G31" s="97"/>
-      <c r="H31" s="97"/>
-      <c r="I31" s="97"/>
-      <c r="J31" s="97"/>
-      <c r="K31" s="97"/>
-      <c r="L31" s="97"/>
-      <c r="M31" s="97"/>
-      <c r="N31" s="97"/>
-      <c r="O31" s="97"/>
-      <c r="P31" s="97"/>
-      <c r="Q31" s="97"/>
-      <c r="R31" s="97"/>
-      <c r="S31" s="97"/>
-      <c r="T31" s="97"/>
-      <c r="U31" s="97"/>
-      <c r="V31" s="97"/>
-      <c r="W31" s="97"/>
-      <c r="X31" s="71"/>
-      <c r="Y31" s="71"/>
-      <c r="Z31" s="71"/>
-      <c r="AA31" s="71"/>
-      <c r="AB31" s="71"/>
-      <c r="AC31" s="71"/>
+      <c r="D31" s="94"/>
+      <c r="E31" s="97"/>
+      <c r="F31" s="90"/>
+      <c r="G31" s="90"/>
+      <c r="H31" s="90"/>
+      <c r="I31" s="90"/>
+      <c r="J31" s="90"/>
+      <c r="K31" s="90"/>
+      <c r="L31" s="90"/>
+      <c r="M31" s="90"/>
+      <c r="N31" s="90"/>
+      <c r="O31" s="90"/>
+      <c r="P31" s="90"/>
+      <c r="Q31" s="90"/>
+      <c r="R31" s="90"/>
+      <c r="S31" s="90"/>
+      <c r="T31" s="90"/>
+      <c r="U31" s="90"/>
+      <c r="V31" s="90"/>
+      <c r="W31" s="90"/>
+      <c r="X31" s="65"/>
+      <c r="Y31" s="65"/>
+      <c r="Z31" s="65"/>
+      <c r="AA31" s="65"/>
+      <c r="AB31" s="65"/>
+      <c r="AC31" s="65"/>
     </row>
     <row r="32" spans="1:29">
-      <c r="A32" s="80">
+      <c r="A32" s="73">
         <v>19</v>
       </c>
-      <c r="B32" s="105" t="s">
+      <c r="B32" s="98" t="s">
         <v>155</v>
       </c>
-      <c r="C32" s="106">
+      <c r="C32" s="99">
         <v>7</v>
       </c>
-      <c r="D32" s="101"/>
-      <c r="E32" s="104"/>
-      <c r="F32" s="97"/>
-      <c r="G32" s="97"/>
-      <c r="H32" s="97"/>
-      <c r="I32" s="97"/>
-      <c r="J32" s="97"/>
-      <c r="K32" s="97"/>
-      <c r="L32" s="97"/>
-      <c r="M32" s="97"/>
-      <c r="N32" s="97"/>
-      <c r="O32" s="97"/>
-      <c r="P32" s="97"/>
-      <c r="Q32" s="97"/>
-      <c r="R32" s="97"/>
-      <c r="S32" s="97"/>
-      <c r="T32" s="97"/>
-      <c r="U32" s="97"/>
-      <c r="V32" s="97"/>
-      <c r="W32" s="97"/>
-      <c r="X32" s="71"/>
-      <c r="Y32" s="71"/>
-      <c r="Z32" s="71"/>
-      <c r="AA32" s="71"/>
-      <c r="AB32" s="71"/>
-      <c r="AC32" s="71"/>
+      <c r="D32" s="94"/>
+      <c r="E32" s="97"/>
+      <c r="F32" s="90"/>
+      <c r="G32" s="90"/>
+      <c r="H32" s="90"/>
+      <c r="I32" s="90"/>
+      <c r="J32" s="90"/>
+      <c r="K32" s="90"/>
+      <c r="L32" s="90"/>
+      <c r="M32" s="90"/>
+      <c r="N32" s="90"/>
+      <c r="O32" s="90"/>
+      <c r="P32" s="90"/>
+      <c r="Q32" s="90"/>
+      <c r="R32" s="90"/>
+      <c r="S32" s="90"/>
+      <c r="T32" s="90"/>
+      <c r="U32" s="90"/>
+      <c r="V32" s="90"/>
+      <c r="W32" s="90"/>
+      <c r="X32" s="65"/>
+      <c r="Y32" s="65"/>
+      <c r="Z32" s="65"/>
+      <c r="AA32" s="65"/>
+      <c r="AB32" s="65"/>
+      <c r="AC32" s="65"/>
     </row>
     <row r="33" spans="1:29">
-      <c r="A33" s="80">
+      <c r="A33" s="73">
         <v>20</v>
       </c>
-      <c r="B33" s="113" t="s">
+      <c r="B33" s="106" t="s">
         <v>156</v>
       </c>
-      <c r="C33" s="114">
+      <c r="C33" s="107">
         <v>5</v>
       </c>
-      <c r="D33" s="101"/>
-      <c r="E33" s="104"/>
-      <c r="F33" s="97"/>
-      <c r="G33" s="97"/>
-      <c r="H33" s="97"/>
-      <c r="I33" s="97"/>
-      <c r="J33" s="97"/>
-      <c r="K33" s="97"/>
-      <c r="L33" s="97"/>
-      <c r="M33" s="97"/>
-      <c r="N33" s="97"/>
-      <c r="O33" s="97"/>
-      <c r="P33" s="97"/>
-      <c r="Q33" s="97"/>
-      <c r="R33" s="97"/>
-      <c r="S33" s="97"/>
-      <c r="T33" s="97"/>
-      <c r="U33" s="97"/>
-      <c r="V33" s="97"/>
-      <c r="W33" s="97"/>
-      <c r="X33" s="71"/>
-      <c r="Y33" s="71"/>
-      <c r="Z33" s="71"/>
-      <c r="AA33" s="71"/>
-      <c r="AB33" s="71"/>
-      <c r="AC33" s="71"/>
+      <c r="D33" s="94"/>
+      <c r="E33" s="97"/>
+      <c r="F33" s="90"/>
+      <c r="G33" s="90"/>
+      <c r="H33" s="90"/>
+      <c r="I33" s="90"/>
+      <c r="J33" s="90"/>
+      <c r="K33" s="90"/>
+      <c r="L33" s="90"/>
+      <c r="M33" s="90"/>
+      <c r="N33" s="90"/>
+      <c r="O33" s="90"/>
+      <c r="P33" s="90"/>
+      <c r="Q33" s="90"/>
+      <c r="R33" s="90"/>
+      <c r="S33" s="90"/>
+      <c r="T33" s="90"/>
+      <c r="U33" s="90"/>
+      <c r="V33" s="90"/>
+      <c r="W33" s="90"/>
+      <c r="X33" s="65"/>
+      <c r="Y33" s="65"/>
+      <c r="Z33" s="65"/>
+      <c r="AA33" s="65"/>
+      <c r="AB33" s="65"/>
+      <c r="AC33" s="65"/>
     </row>
     <row r="34" spans="1:29">
-      <c r="A34" s="80">
+      <c r="A34" s="73">
         <v>21</v>
       </c>
-      <c r="B34" s="115" t="s">
+      <c r="B34" s="108" t="s">
         <v>157</v>
       </c>
-      <c r="C34" s="114">
+      <c r="C34" s="107">
         <v>5</v>
       </c>
-      <c r="D34" s="101"/>
-      <c r="E34" s="104"/>
-      <c r="F34" s="97"/>
-      <c r="G34" s="97"/>
-      <c r="H34" s="97"/>
-      <c r="I34" s="97"/>
-      <c r="J34" s="97"/>
-      <c r="K34" s="97"/>
-      <c r="L34" s="97"/>
-      <c r="M34" s="97"/>
-      <c r="N34" s="97"/>
-      <c r="O34" s="97"/>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="97"/>
-      <c r="S34" s="97"/>
-      <c r="T34" s="97"/>
-      <c r="U34" s="97"/>
-      <c r="V34" s="97"/>
-      <c r="W34" s="97"/>
-      <c r="X34" s="71"/>
-      <c r="Y34" s="71"/>
-      <c r="Z34" s="71"/>
-      <c r="AA34" s="71"/>
-      <c r="AB34" s="71"/>
-      <c r="AC34" s="71"/>
+      <c r="D34" s="94"/>
+      <c r="E34" s="97"/>
+      <c r="F34" s="90"/>
+      <c r="G34" s="90"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="90"/>
+      <c r="J34" s="90"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="90"/>
+      <c r="M34" s="90"/>
+      <c r="N34" s="90"/>
+      <c r="O34" s="90"/>
+      <c r="P34" s="90"/>
+      <c r="Q34" s="90"/>
+      <c r="R34" s="90"/>
+      <c r="S34" s="90"/>
+      <c r="T34" s="90"/>
+      <c r="U34" s="90"/>
+      <c r="V34" s="90"/>
+      <c r="W34" s="90"/>
+      <c r="X34" s="65"/>
+      <c r="Y34" s="65"/>
+      <c r="Z34" s="65"/>
+      <c r="AA34" s="65"/>
+      <c r="AB34" s="65"/>
+      <c r="AC34" s="65"/>
     </row>
     <row r="35" spans="1:29">
-      <c r="A35" s="80">
+      <c r="A35" s="73">
         <v>23</v>
       </c>
-      <c r="B35" s="116" t="s">
+      <c r="B35" s="109" t="s">
         <v>159</v>
       </c>
-      <c r="C35" s="106">
+      <c r="C35" s="99">
         <v>3</v>
       </c>
-      <c r="D35" s="101"/>
-      <c r="E35" s="104"/>
-      <c r="F35" s="97"/>
-      <c r="G35" s="97"/>
-      <c r="H35" s="97"/>
-      <c r="I35" s="97"/>
-      <c r="J35" s="97"/>
-      <c r="K35" s="97"/>
-      <c r="L35" s="97"/>
-      <c r="M35" s="97"/>
-      <c r="N35" s="97"/>
-      <c r="O35" s="97"/>
-      <c r="P35" s="97"/>
-      <c r="Q35" s="97"/>
-      <c r="R35" s="97"/>
-      <c r="S35" s="97"/>
-      <c r="T35" s="97"/>
-      <c r="U35" s="97"/>
-      <c r="V35" s="97"/>
-      <c r="W35" s="97"/>
-      <c r="X35" s="71"/>
-      <c r="Y35" s="71"/>
-      <c r="Z35" s="71"/>
-      <c r="AA35" s="71"/>
-      <c r="AB35" s="71"/>
-      <c r="AC35" s="71"/>
+      <c r="D35" s="94"/>
+      <c r="E35" s="97"/>
+      <c r="F35" s="90"/>
+      <c r="G35" s="90"/>
+      <c r="H35" s="90"/>
+      <c r="I35" s="90"/>
+      <c r="J35" s="90"/>
+      <c r="K35" s="90"/>
+      <c r="L35" s="90"/>
+      <c r="M35" s="90"/>
+      <c r="N35" s="90"/>
+      <c r="O35" s="90"/>
+      <c r="P35" s="90"/>
+      <c r="Q35" s="90"/>
+      <c r="R35" s="90"/>
+      <c r="S35" s="90"/>
+      <c r="T35" s="90"/>
+      <c r="U35" s="90"/>
+      <c r="V35" s="90"/>
+      <c r="W35" s="90"/>
+      <c r="X35" s="65"/>
+      <c r="Y35" s="65"/>
+      <c r="Z35" s="65"/>
+      <c r="AA35" s="65"/>
+      <c r="AB35" s="65"/>
+      <c r="AC35" s="65"/>
     </row>
     <row r="36" spans="1:29">
-      <c r="A36" s="80">
+      <c r="A36" s="73">
         <v>24</v>
       </c>
-      <c r="B36" s="117" t="s">
+      <c r="B36" s="110" t="s">
         <v>160</v>
       </c>
-      <c r="C36" s="118">
+      <c r="C36" s="111">
         <v>10</v>
       </c>
-      <c r="D36" s="101"/>
-      <c r="E36" s="119"/>
-      <c r="F36" s="120"/>
-      <c r="G36" s="120"/>
-      <c r="H36" s="120"/>
-      <c r="I36" s="120"/>
-      <c r="J36" s="120"/>
-      <c r="K36" s="120"/>
-      <c r="L36" s="120"/>
-      <c r="M36" s="120"/>
-      <c r="N36" s="120"/>
-      <c r="O36" s="120"/>
-      <c r="P36" s="120"/>
-      <c r="Q36" s="120"/>
-      <c r="R36" s="120"/>
-      <c r="S36" s="120"/>
-      <c r="T36" s="97"/>
-      <c r="U36" s="97"/>
-      <c r="V36" s="97"/>
-      <c r="W36" s="97"/>
-      <c r="X36" s="71"/>
-      <c r="Y36" s="71"/>
-      <c r="Z36" s="71"/>
-      <c r="AA36" s="71"/>
-      <c r="AB36" s="71"/>
-      <c r="AC36" s="71"/>
+      <c r="D36" s="94"/>
+      <c r="E36" s="112"/>
+      <c r="F36" s="113"/>
+      <c r="G36" s="113"/>
+      <c r="H36" s="113"/>
+      <c r="I36" s="113"/>
+      <c r="J36" s="113"/>
+      <c r="K36" s="113"/>
+      <c r="L36" s="113"/>
+      <c r="M36" s="113"/>
+      <c r="N36" s="113"/>
+      <c r="O36" s="113"/>
+      <c r="P36" s="113"/>
+      <c r="Q36" s="113"/>
+      <c r="R36" s="113"/>
+      <c r="S36" s="113"/>
+      <c r="T36" s="90"/>
+      <c r="U36" s="90"/>
+      <c r="V36" s="90"/>
+      <c r="W36" s="90"/>
+      <c r="X36" s="65"/>
+      <c r="Y36" s="65"/>
+      <c r="Z36" s="65"/>
+      <c r="AA36" s="65"/>
+      <c r="AB36" s="65"/>
+      <c r="AC36" s="65"/>
     </row>
     <row r="37" spans="1:29">
-      <c r="A37" s="80">
+      <c r="A37" s="73">
         <v>25</v>
       </c>
-      <c r="B37" s="121" t="s">
+      <c r="B37" s="114" t="s">
         <v>161</v>
       </c>
-      <c r="C37" s="118">
+      <c r="C37" s="111">
         <v>5</v>
       </c>
-      <c r="D37" s="101"/>
-      <c r="E37" s="119"/>
-      <c r="F37" s="120"/>
-      <c r="G37" s="120"/>
-      <c r="H37" s="120"/>
-      <c r="I37" s="120"/>
-      <c r="J37" s="120"/>
-      <c r="K37" s="120"/>
-      <c r="L37" s="120"/>
-      <c r="M37" s="120"/>
-      <c r="N37" s="120"/>
-      <c r="O37" s="120"/>
-      <c r="P37" s="120"/>
-      <c r="Q37" s="120"/>
-      <c r="R37" s="120"/>
-      <c r="S37" s="120"/>
-      <c r="T37" s="97"/>
-      <c r="U37" s="97"/>
-      <c r="V37" s="97"/>
-      <c r="W37" s="97"/>
-      <c r="X37" s="71"/>
-      <c r="Y37" s="71"/>
-      <c r="Z37" s="71"/>
-      <c r="AA37" s="71"/>
-      <c r="AB37" s="71"/>
-      <c r="AC37" s="71"/>
+      <c r="D37" s="94"/>
+      <c r="E37" s="112"/>
+      <c r="F37" s="113"/>
+      <c r="G37" s="113"/>
+      <c r="H37" s="113"/>
+      <c r="I37" s="113"/>
+      <c r="J37" s="113"/>
+      <c r="K37" s="113"/>
+      <c r="L37" s="113"/>
+      <c r="M37" s="113"/>
+      <c r="N37" s="113"/>
+      <c r="O37" s="113"/>
+      <c r="P37" s="113"/>
+      <c r="Q37" s="113"/>
+      <c r="R37" s="113"/>
+      <c r="S37" s="113"/>
+      <c r="T37" s="90"/>
+      <c r="U37" s="90"/>
+      <c r="V37" s="90"/>
+      <c r="W37" s="90"/>
+      <c r="X37" s="65"/>
+      <c r="Y37" s="65"/>
+      <c r="Z37" s="65"/>
+      <c r="AA37" s="65"/>
+      <c r="AB37" s="65"/>
+      <c r="AC37" s="65"/>
     </row>
     <row r="38" spans="1:29">
-      <c r="A38" s="80">
+      <c r="A38" s="73">
         <v>26</v>
       </c>
-      <c r="B38" s="122" t="s">
+      <c r="B38" s="115" t="s">
         <v>162</v>
       </c>
-      <c r="C38" s="114">
+      <c r="C38" s="107">
         <v>6</v>
       </c>
-      <c r="D38" s="101"/>
-      <c r="E38" s="119"/>
-      <c r="F38" s="120"/>
-      <c r="G38" s="120"/>
-      <c r="H38" s="120"/>
-      <c r="I38" s="120"/>
-      <c r="J38" s="120"/>
-      <c r="K38" s="120"/>
-      <c r="L38" s="120"/>
-      <c r="M38" s="120"/>
-      <c r="N38" s="120"/>
-      <c r="O38" s="120"/>
-      <c r="P38" s="120"/>
-      <c r="Q38" s="120"/>
-      <c r="R38" s="120"/>
-      <c r="S38" s="120"/>
-      <c r="T38" s="97"/>
-      <c r="U38" s="97"/>
-      <c r="V38" s="97"/>
-      <c r="W38" s="97"/>
-      <c r="X38" s="71"/>
-      <c r="Y38" s="71"/>
-      <c r="Z38" s="71"/>
-      <c r="AA38" s="71"/>
-      <c r="AB38" s="71"/>
-      <c r="AC38" s="71"/>
+      <c r="D38" s="94"/>
+      <c r="E38" s="112"/>
+      <c r="F38" s="113"/>
+      <c r="G38" s="113"/>
+      <c r="H38" s="113"/>
+      <c r="I38" s="113"/>
+      <c r="J38" s="113"/>
+      <c r="K38" s="113"/>
+      <c r="L38" s="113"/>
+      <c r="M38" s="113"/>
+      <c r="N38" s="113"/>
+      <c r="O38" s="113"/>
+      <c r="P38" s="113"/>
+      <c r="Q38" s="113"/>
+      <c r="R38" s="113"/>
+      <c r="S38" s="113"/>
+      <c r="T38" s="90"/>
+      <c r="U38" s="90"/>
+      <c r="V38" s="90"/>
+      <c r="W38" s="90"/>
+      <c r="X38" s="65"/>
+      <c r="Y38" s="65"/>
+      <c r="Z38" s="65"/>
+      <c r="AA38" s="65"/>
+      <c r="AB38" s="65"/>
+      <c r="AC38" s="65"/>
     </row>
     <row r="39" spans="1:29">
-      <c r="A39" s="80">
+      <c r="A39" s="73">
         <v>27</v>
       </c>
-      <c r="B39" s="121" t="s">
+      <c r="B39" s="114" t="s">
         <v>163</v>
       </c>
-      <c r="C39" s="118">
+      <c r="C39" s="111">
         <v>5</v>
       </c>
-      <c r="D39" s="101"/>
-      <c r="E39" s="119"/>
-      <c r="F39" s="120"/>
-      <c r="G39" s="120"/>
-      <c r="H39" s="120"/>
-      <c r="I39" s="120"/>
-      <c r="J39" s="120"/>
-      <c r="K39" s="120"/>
-      <c r="L39" s="120"/>
-      <c r="M39" s="120"/>
-      <c r="N39" s="120"/>
-      <c r="O39" s="120"/>
-      <c r="P39" s="120"/>
-      <c r="Q39" s="120"/>
-      <c r="R39" s="120"/>
-      <c r="S39" s="120"/>
-      <c r="T39" s="97"/>
-      <c r="U39" s="97"/>
-      <c r="V39" s="97"/>
-      <c r="W39" s="97"/>
-      <c r="X39" s="71"/>
-      <c r="Y39" s="71"/>
-      <c r="Z39" s="71"/>
-      <c r="AA39" s="71"/>
-      <c r="AB39" s="71"/>
-      <c r="AC39" s="71"/>
+      <c r="D39" s="94"/>
+      <c r="E39" s="112"/>
+      <c r="F39" s="113"/>
+      <c r="G39" s="113"/>
+      <c r="H39" s="113"/>
+      <c r="I39" s="113"/>
+      <c r="J39" s="113"/>
+      <c r="K39" s="113"/>
+      <c r="L39" s="113"/>
+      <c r="M39" s="113"/>
+      <c r="N39" s="113"/>
+      <c r="O39" s="113"/>
+      <c r="P39" s="113"/>
+      <c r="Q39" s="113"/>
+      <c r="R39" s="113"/>
+      <c r="S39" s="113"/>
+      <c r="T39" s="90"/>
+      <c r="U39" s="90"/>
+      <c r="V39" s="90"/>
+      <c r="W39" s="90"/>
+      <c r="X39" s="65"/>
+      <c r="Y39" s="65"/>
+      <c r="Z39" s="65"/>
+      <c r="AA39" s="65"/>
+      <c r="AB39" s="65"/>
+      <c r="AC39" s="65"/>
     </row>
     <row r="40" spans="1:29">
-      <c r="A40" s="80">
+      <c r="A40" s="73">
         <v>28</v>
       </c>
-      <c r="B40" s="123" t="s">
+      <c r="B40" s="116" t="s">
         <v>174</v>
       </c>
-      <c r="C40" s="118">
+      <c r="C40" s="111">
         <v>5</v>
       </c>
-      <c r="D40" s="101"/>
-      <c r="E40" s="119"/>
-      <c r="F40" s="120"/>
-      <c r="G40" s="120"/>
-      <c r="H40" s="120"/>
-      <c r="I40" s="120"/>
-      <c r="J40" s="120"/>
-      <c r="K40" s="120"/>
-      <c r="L40" s="120"/>
-      <c r="M40" s="120"/>
-      <c r="N40" s="120"/>
-      <c r="O40" s="120"/>
-      <c r="P40" s="120"/>
-      <c r="Q40" s="120"/>
-      <c r="R40" s="120"/>
-      <c r="S40" s="120"/>
-      <c r="T40" s="97"/>
-      <c r="U40" s="97"/>
-      <c r="V40" s="97"/>
-      <c r="W40" s="97"/>
-      <c r="X40" s="71"/>
-      <c r="Y40" s="71"/>
-      <c r="Z40" s="71"/>
-      <c r="AA40" s="71"/>
-      <c r="AB40" s="71"/>
-      <c r="AC40" s="71"/>
+      <c r="D40" s="94"/>
+      <c r="E40" s="112"/>
+      <c r="F40" s="113"/>
+      <c r="G40" s="113"/>
+      <c r="H40" s="113"/>
+      <c r="I40" s="113"/>
+      <c r="J40" s="113"/>
+      <c r="K40" s="113"/>
+      <c r="L40" s="113"/>
+      <c r="M40" s="113"/>
+      <c r="N40" s="113"/>
+      <c r="O40" s="113"/>
+      <c r="P40" s="113"/>
+      <c r="Q40" s="113"/>
+      <c r="R40" s="113"/>
+      <c r="S40" s="113"/>
+      <c r="T40" s="90"/>
+      <c r="U40" s="90"/>
+      <c r="V40" s="90"/>
+      <c r="W40" s="90"/>
+      <c r="X40" s="65"/>
+      <c r="Y40" s="65"/>
+      <c r="Z40" s="65"/>
+      <c r="AA40" s="65"/>
+      <c r="AB40" s="65"/>
+      <c r="AC40" s="65"/>
     </row>
     <row r="41" spans="1:29">
-      <c r="A41" s="80">
+      <c r="A41" s="73">
         <v>29</v>
       </c>
-      <c r="B41" s="123" t="s">
+      <c r="B41" s="116" t="s">
         <v>176</v>
       </c>
-      <c r="C41" s="118">
+      <c r="C41" s="111">
         <v>3</v>
       </c>
-      <c r="D41" s="101"/>
-      <c r="E41" s="119"/>
-      <c r="F41" s="120"/>
-      <c r="G41" s="120"/>
-      <c r="H41" s="120"/>
-      <c r="I41" s="120"/>
-      <c r="J41" s="120"/>
-      <c r="K41" s="120"/>
-      <c r="L41" s="120"/>
-      <c r="M41" s="120"/>
-      <c r="N41" s="120"/>
-      <c r="O41" s="120"/>
-      <c r="P41" s="120"/>
-      <c r="Q41" s="120"/>
-      <c r="R41" s="120"/>
-      <c r="S41" s="120"/>
-      <c r="T41" s="97"/>
-      <c r="U41" s="97"/>
-      <c r="V41" s="97"/>
-      <c r="W41" s="97"/>
-      <c r="X41" s="71"/>
-      <c r="Y41" s="71"/>
-      <c r="Z41" s="71"/>
-      <c r="AA41" s="71"/>
-      <c r="AB41" s="71"/>
-      <c r="AC41" s="71"/>
+      <c r="D41" s="94"/>
+      <c r="E41" s="112"/>
+      <c r="F41" s="113"/>
+      <c r="G41" s="113"/>
+      <c r="H41" s="113"/>
+      <c r="I41" s="113"/>
+      <c r="J41" s="113"/>
+      <c r="K41" s="113"/>
+      <c r="L41" s="113"/>
+      <c r="M41" s="113"/>
+      <c r="N41" s="113"/>
+      <c r="O41" s="113"/>
+      <c r="P41" s="113"/>
+      <c r="Q41" s="113"/>
+      <c r="R41" s="113"/>
+      <c r="S41" s="113"/>
+      <c r="T41" s="90"/>
+      <c r="U41" s="90"/>
+      <c r="V41" s="90"/>
+      <c r="W41" s="90"/>
+      <c r="X41" s="65"/>
+      <c r="Y41" s="65"/>
+      <c r="Z41" s="65"/>
+      <c r="AA41" s="65"/>
+      <c r="AB41" s="65"/>
+      <c r="AC41" s="65"/>
     </row>
     <row r="42" spans="1:29">
-      <c r="A42" s="80">
+      <c r="A42" s="73">
         <v>29</v>
       </c>
-      <c r="B42" s="123" t="s">
+      <c r="B42" s="116" t="s">
         <v>164</v>
       </c>
-      <c r="C42" s="118">
+      <c r="C42" s="111">
         <v>6</v>
       </c>
-      <c r="D42" s="101"/>
-      <c r="E42" s="119"/>
-      <c r="F42" s="120"/>
-      <c r="G42" s="120"/>
-      <c r="H42" s="120"/>
-      <c r="I42" s="120"/>
-      <c r="J42" s="120"/>
-      <c r="K42" s="120"/>
-      <c r="L42" s="120"/>
-      <c r="M42" s="120"/>
-      <c r="N42" s="120"/>
-      <c r="O42" s="120"/>
-      <c r="P42" s="120"/>
-      <c r="Q42" s="120"/>
-      <c r="R42" s="120"/>
-      <c r="S42" s="120"/>
-      <c r="T42" s="97"/>
-      <c r="U42" s="97"/>
-      <c r="V42" s="97"/>
-      <c r="W42" s="97"/>
-      <c r="X42" s="71"/>
-      <c r="Y42" s="71"/>
-      <c r="Z42" s="71"/>
-      <c r="AA42" s="71"/>
-      <c r="AB42" s="71"/>
-      <c r="AC42" s="71"/>
+      <c r="D42" s="94"/>
+      <c r="E42" s="112"/>
+      <c r="F42" s="113"/>
+      <c r="G42" s="113"/>
+      <c r="H42" s="113"/>
+      <c r="I42" s="113"/>
+      <c r="J42" s="113"/>
+      <c r="K42" s="113"/>
+      <c r="L42" s="113"/>
+      <c r="M42" s="113"/>
+      <c r="N42" s="113"/>
+      <c r="O42" s="113"/>
+      <c r="P42" s="113"/>
+      <c r="Q42" s="113"/>
+      <c r="R42" s="113"/>
+      <c r="S42" s="113"/>
+      <c r="T42" s="90"/>
+      <c r="U42" s="90"/>
+      <c r="V42" s="90"/>
+      <c r="W42" s="90"/>
+      <c r="X42" s="65"/>
+      <c r="Y42" s="65"/>
+      <c r="Z42" s="65"/>
+      <c r="AA42" s="65"/>
+      <c r="AB42" s="65"/>
+      <c r="AC42" s="65"/>
     </row>
     <row r="43" spans="1:29">
-      <c r="A43" s="80">
+      <c r="A43" s="73">
         <v>30</v>
       </c>
-      <c r="B43" s="123" t="s">
+      <c r="B43" s="116" t="s">
         <v>165</v>
       </c>
-      <c r="C43" s="118">
+      <c r="C43" s="111">
         <v>8</v>
       </c>
-      <c r="D43" s="101"/>
-      <c r="E43" s="119"/>
-      <c r="F43" s="120"/>
-      <c r="G43" s="120"/>
-      <c r="H43" s="120"/>
-      <c r="I43" s="120"/>
-      <c r="J43" s="120"/>
-      <c r="K43" s="120"/>
-      <c r="L43" s="120"/>
-      <c r="M43" s="120"/>
-      <c r="N43" s="120"/>
-      <c r="O43" s="120"/>
-      <c r="P43" s="120"/>
-      <c r="Q43" s="120"/>
-      <c r="R43" s="120"/>
-      <c r="S43" s="120"/>
-      <c r="T43" s="97"/>
-      <c r="U43" s="97"/>
-      <c r="V43" s="97"/>
-      <c r="W43" s="97"/>
-      <c r="X43" s="71"/>
-      <c r="Y43" s="71"/>
-      <c r="Z43" s="71"/>
-      <c r="AA43" s="71"/>
-      <c r="AB43" s="71"/>
-      <c r="AC43" s="71"/>
+      <c r="D43" s="94"/>
+      <c r="E43" s="112"/>
+      <c r="F43" s="113"/>
+      <c r="G43" s="113"/>
+      <c r="H43" s="113"/>
+      <c r="I43" s="113"/>
+      <c r="J43" s="113"/>
+      <c r="K43" s="113"/>
+      <c r="L43" s="113"/>
+      <c r="M43" s="113"/>
+      <c r="N43" s="113"/>
+      <c r="O43" s="113"/>
+      <c r="P43" s="113"/>
+      <c r="Q43" s="113"/>
+      <c r="R43" s="113"/>
+      <c r="S43" s="113"/>
+      <c r="T43" s="90"/>
+      <c r="U43" s="90"/>
+      <c r="V43" s="90"/>
+      <c r="W43" s="90"/>
+      <c r="X43" s="65"/>
+      <c r="Y43" s="65"/>
+      <c r="Z43" s="65"/>
+      <c r="AA43" s="65"/>
+      <c r="AB43" s="65"/>
+      <c r="AC43" s="65"/>
     </row>
     <row r="44" spans="1:29">
-      <c r="A44" s="80">
+      <c r="A44" s="73">
         <v>31</v>
       </c>
-      <c r="B44" s="115" t="s">
+      <c r="B44" s="108" t="s">
         <v>166</v>
       </c>
-      <c r="C44" s="124">
+      <c r="C44" s="117">
         <v>4</v>
       </c>
-      <c r="D44" s="101"/>
-      <c r="E44" s="119"/>
-      <c r="F44" s="101"/>
-      <c r="G44" s="101"/>
-      <c r="H44" s="101"/>
-      <c r="I44" s="101"/>
-      <c r="J44" s="101"/>
-      <c r="K44" s="101"/>
-      <c r="L44" s="120"/>
-      <c r="M44" s="101"/>
-      <c r="N44" s="101"/>
-      <c r="O44" s="101"/>
-      <c r="P44" s="101"/>
-      <c r="Q44" s="101"/>
-      <c r="R44" s="101"/>
-      <c r="S44" s="101"/>
-      <c r="T44" s="97"/>
-      <c r="U44" s="97"/>
-      <c r="V44" s="97"/>
-      <c r="W44" s="97"/>
-      <c r="X44" s="71"/>
-      <c r="Y44" s="71"/>
-      <c r="Z44" s="71"/>
-      <c r="AA44" s="71"/>
-      <c r="AB44" s="71"/>
-      <c r="AC44" s="71"/>
+      <c r="D44" s="94"/>
+      <c r="E44" s="112"/>
+      <c r="F44" s="94"/>
+      <c r="G44" s="94"/>
+      <c r="H44" s="94"/>
+      <c r="I44" s="94"/>
+      <c r="J44" s="94"/>
+      <c r="K44" s="94"/>
+      <c r="L44" s="113"/>
+      <c r="M44" s="94"/>
+      <c r="N44" s="94"/>
+      <c r="O44" s="94"/>
+      <c r="P44" s="94"/>
+      <c r="Q44" s="94"/>
+      <c r="R44" s="94"/>
+      <c r="S44" s="94"/>
+      <c r="T44" s="90"/>
+      <c r="U44" s="90"/>
+      <c r="V44" s="90"/>
+      <c r="W44" s="90"/>
+      <c r="X44" s="65"/>
+      <c r="Y44" s="65"/>
+      <c r="Z44" s="65"/>
+      <c r="AA44" s="65"/>
+      <c r="AB44" s="65"/>
+      <c r="AC44" s="65"/>
     </row>
     <row r="45" spans="1:29">
-      <c r="A45" s="80">
+      <c r="A45" s="73">
         <v>32</v>
       </c>
-      <c r="B45" s="125" t="s">
+      <c r="B45" s="118" t="s">
         <v>167</v>
       </c>
-      <c r="C45" s="114">
+      <c r="C45" s="107">
         <v>4</v>
       </c>
-      <c r="D45" s="101"/>
-      <c r="E45" s="119"/>
-      <c r="F45" s="101"/>
-      <c r="G45" s="101"/>
-      <c r="H45" s="101"/>
-      <c r="I45" s="101"/>
-      <c r="J45" s="101"/>
-      <c r="K45" s="101"/>
-      <c r="L45" s="120"/>
-      <c r="M45" s="101"/>
-      <c r="N45" s="101"/>
-      <c r="O45" s="101"/>
-      <c r="P45" s="101"/>
-      <c r="Q45" s="101"/>
-      <c r="R45" s="101"/>
-      <c r="S45" s="101"/>
-      <c r="T45" s="97"/>
-      <c r="U45" s="97"/>
-      <c r="V45" s="97"/>
-      <c r="W45" s="97"/>
-      <c r="X45" s="71"/>
-      <c r="Y45" s="71"/>
-      <c r="Z45" s="71"/>
-      <c r="AA45" s="71"/>
-      <c r="AB45" s="71"/>
-      <c r="AC45" s="71"/>
+      <c r="D45" s="94"/>
+      <c r="E45" s="112"/>
+      <c r="F45" s="94"/>
+      <c r="G45" s="94"/>
+      <c r="H45" s="94"/>
+      <c r="I45" s="94"/>
+      <c r="J45" s="94"/>
+      <c r="K45" s="94"/>
+      <c r="L45" s="113"/>
+      <c r="M45" s="94"/>
+      <c r="N45" s="94"/>
+      <c r="O45" s="94"/>
+      <c r="P45" s="94"/>
+      <c r="Q45" s="94"/>
+      <c r="R45" s="94"/>
+      <c r="S45" s="94"/>
+      <c r="T45" s="90"/>
+      <c r="U45" s="90"/>
+      <c r="V45" s="90"/>
+      <c r="W45" s="90"/>
+      <c r="X45" s="65"/>
+      <c r="Y45" s="65"/>
+      <c r="Z45" s="65"/>
+      <c r="AA45" s="65"/>
+      <c r="AB45" s="65"/>
+      <c r="AC45" s="65"/>
     </row>
     <row r="46" spans="1:29">
-      <c r="A46" s="80">
+      <c r="A46" s="73">
         <v>33</v>
       </c>
-      <c r="B46" s="117" t="s">
+      <c r="B46" s="110" t="s">
         <v>168</v>
       </c>
-      <c r="C46" s="118">
+      <c r="C46" s="111">
         <v>4</v>
       </c>
-      <c r="D46" s="101"/>
-      <c r="E46" s="119"/>
-      <c r="F46" s="101"/>
-      <c r="G46" s="101"/>
-      <c r="H46" s="101"/>
-      <c r="I46" s="101"/>
-      <c r="J46" s="101"/>
-      <c r="K46" s="101"/>
-      <c r="L46" s="120"/>
-      <c r="M46" s="101"/>
-      <c r="N46" s="101"/>
-      <c r="O46" s="101"/>
-      <c r="P46" s="101"/>
-      <c r="Q46" s="101"/>
-      <c r="R46" s="101"/>
-      <c r="S46" s="101"/>
-      <c r="T46" s="97"/>
-      <c r="U46" s="97"/>
-      <c r="V46" s="97"/>
-      <c r="W46" s="97"/>
-      <c r="X46" s="71"/>
-      <c r="Y46" s="71"/>
-      <c r="Z46" s="71"/>
-      <c r="AA46" s="71"/>
-      <c r="AB46" s="71"/>
-      <c r="AC46" s="71"/>
+      <c r="D46" s="94"/>
+      <c r="E46" s="112"/>
+      <c r="F46" s="94"/>
+      <c r="G46" s="94"/>
+      <c r="H46" s="94"/>
+      <c r="I46" s="94"/>
+      <c r="J46" s="94"/>
+      <c r="K46" s="94"/>
+      <c r="L46" s="113"/>
+      <c r="M46" s="94"/>
+      <c r="N46" s="94"/>
+      <c r="O46" s="94"/>
+      <c r="P46" s="94"/>
+      <c r="Q46" s="94"/>
+      <c r="R46" s="94"/>
+      <c r="S46" s="94"/>
+      <c r="T46" s="90"/>
+      <c r="U46" s="90"/>
+      <c r="V46" s="90"/>
+      <c r="W46" s="90"/>
+      <c r="X46" s="65"/>
+      <c r="Y46" s="65"/>
+      <c r="Z46" s="65"/>
+      <c r="AA46" s="65"/>
+      <c r="AB46" s="65"/>
+      <c r="AC46" s="65"/>
     </row>
     <row r="47" spans="1:29" ht="15" thickBot="1">
-      <c r="A47" s="80">
+      <c r="A47" s="73">
         <v>34</v>
       </c>
-      <c r="B47" s="117" t="s">
+      <c r="B47" s="110" t="s">
         <v>169</v>
       </c>
-      <c r="C47" s="114">
+      <c r="C47" s="107">
         <v>12</v>
       </c>
-      <c r="D47" s="101"/>
-      <c r="E47" s="119"/>
-      <c r="F47" s="70"/>
-      <c r="G47" s="70"/>
-      <c r="H47" s="70"/>
-      <c r="I47" s="70"/>
-      <c r="J47" s="70"/>
-      <c r="K47" s="70"/>
-      <c r="L47" s="120"/>
-      <c r="M47" s="70"/>
-      <c r="N47" s="70"/>
-      <c r="O47" s="70"/>
-      <c r="P47" s="70"/>
-      <c r="Q47" s="70"/>
-      <c r="R47" s="70"/>
-      <c r="S47" s="70"/>
-      <c r="T47" s="103"/>
-      <c r="U47" s="126"/>
-      <c r="V47" s="126"/>
-      <c r="W47" s="126"/>
-      <c r="X47" s="71"/>
-      <c r="Y47" s="71"/>
-      <c r="Z47" s="71"/>
-      <c r="AA47" s="71"/>
-      <c r="AB47" s="71"/>
-      <c r="AC47" s="71"/>
+      <c r="D47" s="94"/>
+      <c r="E47" s="112"/>
+      <c r="F47" s="64"/>
+      <c r="G47" s="64"/>
+      <c r="H47" s="64"/>
+      <c r="I47" s="64"/>
+      <c r="J47" s="64"/>
+      <c r="K47" s="64"/>
+      <c r="L47" s="113"/>
+      <c r="M47" s="64"/>
+      <c r="N47" s="64"/>
+      <c r="O47" s="64"/>
+      <c r="P47" s="64"/>
+      <c r="Q47" s="64"/>
+      <c r="R47" s="64"/>
+      <c r="S47" s="64"/>
+      <c r="T47" s="96"/>
+      <c r="U47" s="119"/>
+      <c r="V47" s="119"/>
+      <c r="W47" s="119"/>
+      <c r="X47" s="65"/>
+      <c r="Y47" s="65"/>
+      <c r="Z47" s="65"/>
+      <c r="AA47" s="65"/>
+      <c r="AB47" s="65"/>
+      <c r="AC47" s="65"/>
     </row>
     <row r="48" spans="1:29" ht="54" thickTop="1">
-      <c r="A48" s="127"/>
-      <c r="B48" s="128" t="s">
+      <c r="A48" s="120"/>
+      <c r="B48" s="121" t="s">
         <v>77</v>
       </c>
-      <c r="C48" s="129"/>
-      <c r="D48" s="129"/>
-      <c r="E48" s="130"/>
-      <c r="F48" s="129"/>
-      <c r="G48" s="129"/>
-      <c r="H48" s="129"/>
-      <c r="I48" s="129"/>
-      <c r="J48" s="129"/>
-      <c r="K48" s="129"/>
-      <c r="L48" s="131"/>
-      <c r="M48" s="129"/>
-      <c r="N48" s="129"/>
-      <c r="O48" s="129"/>
-      <c r="P48" s="132" t="s">
+      <c r="C48" s="122"/>
+      <c r="D48" s="122"/>
+      <c r="E48" s="123"/>
+      <c r="F48" s="122"/>
+      <c r="G48" s="122"/>
+      <c r="H48" s="122"/>
+      <c r="I48" s="122"/>
+      <c r="J48" s="122"/>
+      <c r="K48" s="122"/>
+      <c r="L48" s="124"/>
+      <c r="M48" s="122"/>
+      <c r="N48" s="122"/>
+      <c r="O48" s="122"/>
+      <c r="P48" s="125" t="s">
         <v>170</v>
       </c>
-      <c r="Q48" s="129"/>
-      <c r="R48" s="129"/>
-      <c r="S48" s="129"/>
-      <c r="T48" s="129"/>
-      <c r="U48" s="133"/>
-      <c r="V48" s="134"/>
-      <c r="W48" s="133" t="s">
+      <c r="Q48" s="122"/>
+      <c r="R48" s="122"/>
+      <c r="S48" s="122"/>
+      <c r="T48" s="122"/>
+      <c r="U48" s="126"/>
+      <c r="V48" s="127"/>
+      <c r="W48" s="126" t="s">
         <v>171</v>
       </c>
-      <c r="X48" s="71"/>
-      <c r="Y48" s="71"/>
-      <c r="Z48" s="71"/>
-      <c r="AA48" s="71"/>
-      <c r="AB48" s="71"/>
-      <c r="AC48" s="71"/>
+      <c r="X48" s="65"/>
+      <c r="Y48" s="65"/>
+      <c r="Z48" s="65"/>
+      <c r="AA48" s="65"/>
+      <c r="AB48" s="65"/>
+      <c r="AC48" s="65"/>
     </row>
     <row r="49" spans="1:29" ht="66">
-      <c r="A49" s="135"/>
-      <c r="B49" s="136" t="s">
+      <c r="A49" s="128"/>
+      <c r="B49" s="129" t="s">
         <v>81</v>
       </c>
-      <c r="C49" s="137"/>
-      <c r="D49" s="137"/>
-      <c r="E49" s="138"/>
-      <c r="F49" s="97"/>
-      <c r="G49" s="97"/>
-      <c r="H49" s="97"/>
-      <c r="I49" s="97"/>
-      <c r="J49" s="97"/>
-      <c r="K49" s="97"/>
-      <c r="L49" s="71"/>
-      <c r="M49" s="97"/>
-      <c r="N49" s="139"/>
-      <c r="O49" s="97"/>
-      <c r="P49" s="140"/>
-      <c r="Q49" s="71"/>
-      <c r="R49" s="71"/>
-      <c r="S49" s="139" t="s">
+      <c r="C49" s="130"/>
+      <c r="D49" s="130"/>
+      <c r="E49" s="131"/>
+      <c r="F49" s="90"/>
+      <c r="G49" s="90"/>
+      <c r="H49" s="90"/>
+      <c r="I49" s="90"/>
+      <c r="J49" s="90"/>
+      <c r="K49" s="90"/>
+      <c r="L49" s="65"/>
+      <c r="M49" s="90"/>
+      <c r="N49" s="132"/>
+      <c r="O49" s="90"/>
+      <c r="P49" s="133"/>
+      <c r="Q49" s="65"/>
+      <c r="R49" s="65"/>
+      <c r="S49" s="132" t="s">
         <v>172</v>
       </c>
-      <c r="T49" s="71"/>
-      <c r="U49" s="141"/>
-      <c r="V49" s="141"/>
-      <c r="W49" s="141" t="s">
+      <c r="T49" s="65"/>
+      <c r="U49" s="134"/>
+      <c r="V49" s="134"/>
+      <c r="W49" s="134" t="s">
         <v>173</v>
       </c>
-      <c r="X49" s="71"/>
-      <c r="Y49" s="71"/>
-      <c r="Z49" s="71"/>
-      <c r="AA49" s="71"/>
-      <c r="AB49" s="71"/>
-      <c r="AC49" s="71"/>
+      <c r="X49" s="65"/>
+      <c r="Y49" s="65"/>
+      <c r="Z49" s="65"/>
+      <c r="AA49" s="65"/>
+      <c r="AB49" s="65"/>
+      <c r="AC49" s="65"/>
     </row>
     <row r="50" spans="1:29" ht="15" thickBot="1">
-      <c r="A50" s="142"/>
-      <c r="B50" s="143" t="s">
+      <c r="A50" s="135"/>
+      <c r="B50" s="136" t="s">
         <v>84</v>
       </c>
-      <c r="C50" s="144"/>
-      <c r="D50" s="144"/>
-      <c r="E50" s="145"/>
-      <c r="F50" s="146"/>
-      <c r="G50" s="146"/>
-      <c r="H50" s="146"/>
-      <c r="I50" s="146"/>
-      <c r="J50" s="146"/>
-      <c r="K50" s="146"/>
-      <c r="L50" s="146"/>
-      <c r="M50" s="146"/>
-      <c r="N50" s="146"/>
-      <c r="O50" s="146"/>
-      <c r="P50" s="147"/>
-      <c r="Q50" s="146"/>
-      <c r="R50" s="146"/>
-      <c r="S50" s="146"/>
-      <c r="T50" s="146"/>
-      <c r="U50" s="148"/>
-      <c r="V50" s="148"/>
-      <c r="W50" s="148"/>
-      <c r="X50" s="71"/>
-      <c r="Y50" s="71"/>
-      <c r="Z50" s="71"/>
-      <c r="AA50" s="71"/>
-      <c r="AB50" s="71"/>
-      <c r="AC50" s="71"/>
+      <c r="C50" s="137"/>
+      <c r="D50" s="137"/>
+      <c r="E50" s="138"/>
+      <c r="F50" s="139"/>
+      <c r="G50" s="139"/>
+      <c r="H50" s="139"/>
+      <c r="I50" s="139"/>
+      <c r="J50" s="139"/>
+      <c r="K50" s="139"/>
+      <c r="L50" s="139"/>
+      <c r="M50" s="139"/>
+      <c r="N50" s="139"/>
+      <c r="O50" s="139"/>
+      <c r="P50" s="140"/>
+      <c r="Q50" s="139"/>
+      <c r="R50" s="139"/>
+      <c r="S50" s="139"/>
+      <c r="T50" s="139"/>
+      <c r="U50" s="141"/>
+      <c r="V50" s="141"/>
+      <c r="W50" s="141"/>
+      <c r="X50" s="65"/>
+      <c r="Y50" s="65"/>
+      <c r="Z50" s="65"/>
+      <c r="AA50" s="65"/>
+      <c r="AB50" s="65"/>
+      <c r="AC50" s="65"/>
     </row>
     <row r="51" spans="1:29" ht="15" thickTop="1"/>
   </sheetData>
@@ -15925,11 +16160,11 @@
       <c r="I12" s="9"/>
     </row>
     <row r="15" spans="1:9" ht="21">
-      <c r="B15" s="64" t="s">
+      <c r="B15" s="142" t="s">
         <v>87</v>
       </c>
-      <c r="C15" s="64"/>
-      <c r="D15" s="64"/>
+      <c r="C15" s="142"/>
+      <c r="D15" s="142"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="10" t="s">
@@ -16123,21 +16358,21 @@
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="69" t="s">
+      <c r="D8" s="148" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69"/>
-      <c r="J8" s="69"/>
-      <c r="K8" s="69"/>
-      <c r="L8" s="69"/>
-      <c r="M8" s="69"/>
-      <c r="N8" s="69"/>
-      <c r="O8" s="69"/>
-      <c r="P8" s="69"/>
+      <c r="E8" s="148"/>
+      <c r="F8" s="148"/>
+      <c r="G8" s="148"/>
+      <c r="H8" s="148"/>
+      <c r="I8" s="148"/>
+      <c r="J8" s="148"/>
+      <c r="K8" s="148"/>
+      <c r="L8" s="148"/>
+      <c r="M8" s="148"/>
+      <c r="N8" s="148"/>
+      <c r="O8" s="148"/>
+      <c r="P8" s="148"/>
       <c r="Q8" s="11"/>
     </row>
     <row r="9" spans="1:18" ht="15.6">
@@ -17127,21 +17362,21 @@
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="69" t="s">
+      <c r="D8" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69"/>
-      <c r="J8" s="69"/>
-      <c r="K8" s="69"/>
-      <c r="L8" s="69"/>
-      <c r="M8" s="69"/>
-      <c r="N8" s="69"/>
-      <c r="O8" s="69"/>
-      <c r="P8" s="69"/>
+      <c r="E8" s="148"/>
+      <c r="F8" s="148"/>
+      <c r="G8" s="148"/>
+      <c r="H8" s="148"/>
+      <c r="I8" s="148"/>
+      <c r="J8" s="148"/>
+      <c r="K8" s="148"/>
+      <c r="L8" s="148"/>
+      <c r="M8" s="148"/>
+      <c r="N8" s="148"/>
+      <c r="O8" s="148"/>
+      <c r="P8" s="148"/>
     </row>
     <row r="9" spans="1:16" ht="15.6">
       <c r="A9" s="11"/>

--- a/ProjectManagement/Checklist.xlsx
+++ b/ProjectManagement/Checklist.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10112"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B585C7A-5B5C-144A-98D7-26BA12C84679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="165" windowWidth="14805" windowHeight="7950"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="51200" windowHeight="25260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Checklist" sheetId="1" r:id="rId1"/>
@@ -15,7 +16,20 @@
   <externalReferences>
     <externalReference r:id="rId5"/>
   </externalReferences>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -436,7 +450,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1015,7 +1029,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1180,17 +1194,13 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" textRotation="180"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
@@ -1198,12 +1208,15 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="180"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -1235,7 +1248,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="Rectangle 26" descr="10%"/>
+        <xdr:cNvPr id="2" name="Rectangle 26" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1283,7 +1302,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Text Box 11"/>
+        <xdr:cNvPr id="3" name="Text Box 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1333,7 +1358,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="Text Box 12"/>
+        <xdr:cNvPr id="4" name="Text Box 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1404,7 +1435,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="Line 1"/>
+        <xdr:cNvPr id="5" name="Line 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeShapeType="1"/>
         </xdr:cNvSpPr>
@@ -1452,7 +1489,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="Line 2"/>
+        <xdr:cNvPr id="6" name="Line 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeShapeType="1"/>
         </xdr:cNvSpPr>
@@ -1500,7 +1543,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="AutoShape 3"/>
+        <xdr:cNvPr id="7" name="AutoShape 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1545,7 +1594,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="AutoShape 4"/>
+        <xdr:cNvPr id="8" name="AutoShape 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1590,7 +1645,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="AutoShape 5"/>
+        <xdr:cNvPr id="9" name="AutoShape 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1635,7 +1696,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="AutoShape 6"/>
+        <xdr:cNvPr id="10" name="AutoShape 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1680,7 +1747,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="AutoShape 7"/>
+        <xdr:cNvPr id="11" name="AutoShape 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1725,7 +1798,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="Text Box 9"/>
+        <xdr:cNvPr id="12" name="Text Box 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1775,7 +1854,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="Text Box 10"/>
+        <xdr:cNvPr id="13" name="Text Box 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1825,7 +1910,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="14" name="Text Box 13"/>
+        <xdr:cNvPr id="14" name="Text Box 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1896,7 +1987,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="15" name="Rectangle 14" descr="10%"/>
+        <xdr:cNvPr id="15" name="Rectangle 14" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1944,7 +2041,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="16" name="Rectangle 15" descr="10%"/>
+        <xdr:cNvPr id="16" name="Rectangle 15" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000010000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1992,22 +2095,34 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="17" name="Group 21"/>
+        <xdr:cNvPr id="17" name="Group 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000011000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGrpSpPr>
           <a:grpSpLocks/>
         </xdr:cNvGrpSpPr>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="8115300" y="5038725"/>
-          <a:ext cx="1838325" cy="190500"/>
+          <a:off x="8750300" y="5067300"/>
+          <a:ext cx="2028825" cy="190500"/>
           <a:chOff x="691" y="481"/>
           <a:chExt cx="144" cy="27"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="18" name="Rectangle 16" descr="10%"/>
+          <xdr:cNvPr id="18" name="Rectangle 16" descr="10%">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000012000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr>
             <a:spLocks noChangeArrowheads="1"/>
           </xdr:cNvSpPr>
@@ -2040,7 +2155,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="19" name="Rectangle 17" descr="10%"/>
+          <xdr:cNvPr id="19" name="Rectangle 17" descr="10%">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000013000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr>
             <a:spLocks noChangeArrowheads="1"/>
           </xdr:cNvSpPr>
@@ -2073,7 +2194,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="20" name="Freeform 19"/>
+          <xdr:cNvPr id="20" name="Freeform 19">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000014000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr>
             <a:spLocks/>
           </xdr:cNvSpPr>
@@ -2150,7 +2277,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="21" name="Freeform 20"/>
+          <xdr:cNvPr id="21" name="Freeform 20">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000015000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr>
             <a:spLocks/>
           </xdr:cNvSpPr>
@@ -2243,7 +2376,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="22" name="Rectangle 22"/>
+        <xdr:cNvPr id="22" name="Rectangle 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000016000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2286,7 +2425,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="23" name="Text Box 23"/>
+        <xdr:cNvPr id="23" name="Text Box 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000017000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2382,7 +2527,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="24" name="Text Box 24"/>
+        <xdr:cNvPr id="24" name="Text Box 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000018000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2446,7 +2597,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="25" name="AutoShape 27"/>
+        <xdr:cNvPr id="25" name="AutoShape 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000019000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2513,7 +2670,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="26" name="AutoShape 28"/>
+        <xdr:cNvPr id="26" name="AutoShape 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2595,7 +2758,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="27" name="AutoShape 29"/>
+        <xdr:cNvPr id="27" name="AutoShape 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2677,7 +2846,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="28" name="AutoShape 30"/>
+        <xdr:cNvPr id="28" name="AutoShape 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2744,7 +2919,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="29" name="AutoShape 31"/>
+        <xdr:cNvPr id="29" name="AutoShape 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2811,7 +2992,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="30" name="AutoShape 32"/>
+        <xdr:cNvPr id="30" name="AutoShape 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2878,7 +3065,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="31" name="AutoShape 33"/>
+        <xdr:cNvPr id="31" name="AutoShape 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2960,7 +3153,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="32" name="AutoShape 34"/>
+        <xdr:cNvPr id="32" name="AutoShape 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000020000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3042,7 +3241,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="33" name="AutoShape 35"/>
+        <xdr:cNvPr id="33" name="AutoShape 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000021000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3109,7 +3314,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="34" name="AutoShape 36"/>
+        <xdr:cNvPr id="34" name="AutoShape 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000022000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3201,7 +3412,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="35" name="AutoShape 37"/>
+        <xdr:cNvPr id="35" name="AutoShape 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000023000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3268,7 +3485,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="36" name="AutoShape 38"/>
+        <xdr:cNvPr id="36" name="AutoShape 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000024000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3313,7 +3536,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="37" name="AutoShape 39"/>
+        <xdr:cNvPr id="37" name="AutoShape 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000025000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3380,7 +3609,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="38" name="AutoShape 40"/>
+        <xdr:cNvPr id="38" name="AutoShape 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000026000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3447,7 +3682,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="39" name="AutoShape 41"/>
+        <xdr:cNvPr id="39" name="AutoShape 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000027000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3539,7 +3780,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="40" name="AutoShape 42"/>
+        <xdr:cNvPr id="40" name="AutoShape 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000028000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3606,7 +3853,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="41" name="Text Box 44"/>
+        <xdr:cNvPr id="41" name="Text Box 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000029000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3702,7 +3955,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="42" name="AutoShape 45"/>
+        <xdr:cNvPr id="42" name="AutoShape 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00002A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3784,7 +4043,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="43" name="AutoShape 46"/>
+        <xdr:cNvPr id="43" name="AutoShape 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00002B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3851,7 +4116,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="44" name="AutoShape 47"/>
+        <xdr:cNvPr id="44" name="AutoShape 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00002C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3918,7 +4189,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="45" name="AutoShape 48"/>
+        <xdr:cNvPr id="45" name="AutoShape 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00002D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3985,7 +4262,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="46" name="AutoShape 49"/>
+        <xdr:cNvPr id="46" name="AutoShape 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00002E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4052,7 +4335,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="47" name="AutoShape 50"/>
+        <xdr:cNvPr id="47" name="AutoShape 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00002F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4119,7 +4408,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="48" name="AutoShape 51"/>
+        <xdr:cNvPr id="48" name="AutoShape 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000030000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4186,7 +4481,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="49" name="AutoShape 52"/>
+        <xdr:cNvPr id="49" name="AutoShape 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000031000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4253,7 +4554,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="50" name="AutoShape 53"/>
+        <xdr:cNvPr id="50" name="AutoShape 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000032000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4320,7 +4627,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="51" name="AutoShape 54"/>
+        <xdr:cNvPr id="51" name="AutoShape 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000033000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4387,7 +4700,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="52" name="AutoShape 55"/>
+        <xdr:cNvPr id="52" name="AutoShape 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000034000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4454,7 +4773,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="53" name="AutoShape 56"/>
+        <xdr:cNvPr id="53" name="AutoShape 56">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000035000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4521,7 +4846,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="54" name="AutoShape 57"/>
+        <xdr:cNvPr id="54" name="AutoShape 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000036000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4588,7 +4919,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="55" name="AutoShape 58"/>
+        <xdr:cNvPr id="55" name="AutoShape 58">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000037000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4655,7 +4992,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="56" name="AutoShape 59"/>
+        <xdr:cNvPr id="56" name="AutoShape 59">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000038000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4727,7 +5070,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="Rectangle 1" descr="10%"/>
+        <xdr:cNvPr id="2" name="Rectangle 1" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4775,7 +5124,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Text Box 2"/>
+        <xdr:cNvPr id="3" name="Text Box 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4825,7 +5180,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="Text Box 3"/>
+        <xdr:cNvPr id="4" name="Text Box 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4896,7 +5257,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="Line 4"/>
+        <xdr:cNvPr id="5" name="Line 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeShapeType="1"/>
         </xdr:cNvSpPr>
@@ -4944,7 +5311,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="Line 5"/>
+        <xdr:cNvPr id="6" name="Line 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeShapeType="1"/>
         </xdr:cNvSpPr>
@@ -4992,7 +5365,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="AutoShape 6"/>
+        <xdr:cNvPr id="7" name="AutoShape 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5037,7 +5416,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="AutoShape 7"/>
+        <xdr:cNvPr id="8" name="AutoShape 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5082,7 +5467,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="AutoShape 8"/>
+        <xdr:cNvPr id="9" name="AutoShape 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5127,7 +5518,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="AutoShape 9"/>
+        <xdr:cNvPr id="10" name="AutoShape 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5172,7 +5569,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="AutoShape 10"/>
+        <xdr:cNvPr id="11" name="AutoShape 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5217,7 +5620,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="Text Box 11"/>
+        <xdr:cNvPr id="12" name="Text Box 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00000C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5267,7 +5676,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="Text Box 12"/>
+        <xdr:cNvPr id="13" name="Text Box 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5317,7 +5732,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="14" name="Text Box 13"/>
+        <xdr:cNvPr id="14" name="Text Box 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00000E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5388,7 +5809,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="15" name="Rectangle 14" descr="10%"/>
+        <xdr:cNvPr id="15" name="Rectangle 14" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00000F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5436,7 +5863,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="16" name="Rectangle 15" descr="10%"/>
+        <xdr:cNvPr id="16" name="Rectangle 15" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000010000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5484,22 +5917,34 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="17" name="Group 16"/>
+        <xdr:cNvPr id="17" name="Group 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000011000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGrpSpPr>
           <a:grpSpLocks/>
         </xdr:cNvGrpSpPr>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="8115300" y="5038725"/>
-          <a:ext cx="1838325" cy="190500"/>
+          <a:off x="8750300" y="5067300"/>
+          <a:ext cx="2028825" cy="190500"/>
           <a:chOff x="691" y="481"/>
           <a:chExt cx="144" cy="27"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="18" name="Rectangle 17" descr="10%"/>
+          <xdr:cNvPr id="18" name="Rectangle 17" descr="10%">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000012000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr>
             <a:spLocks noChangeArrowheads="1"/>
           </xdr:cNvSpPr>
@@ -5532,7 +5977,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="19" name="Rectangle 18" descr="10%"/>
+          <xdr:cNvPr id="19" name="Rectangle 18" descr="10%">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000013000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr>
             <a:spLocks noChangeArrowheads="1"/>
           </xdr:cNvSpPr>
@@ -5565,7 +6016,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="20" name="Freeform 19"/>
+          <xdr:cNvPr id="20" name="Freeform 19">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000014000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr>
             <a:spLocks/>
           </xdr:cNvSpPr>
@@ -5642,7 +6099,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="21" name="Freeform 20"/>
+          <xdr:cNvPr id="21" name="Freeform 20">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000015000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr>
             <a:spLocks/>
           </xdr:cNvSpPr>
@@ -5735,7 +6198,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="22" name="Rectangle 21"/>
+        <xdr:cNvPr id="22" name="Rectangle 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000016000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5778,7 +6247,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="23" name="Text Box 22"/>
+        <xdr:cNvPr id="23" name="Text Box 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000017000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5874,7 +6349,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="24" name="Text Box 23"/>
+        <xdr:cNvPr id="24" name="Text Box 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000018000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5938,7 +6419,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="25" name="AutoShape 24"/>
+        <xdr:cNvPr id="25" name="AutoShape 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000019000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6005,7 +6492,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="26" name="AutoShape 25"/>
+        <xdr:cNvPr id="26" name="AutoShape 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00001A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6087,7 +6580,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="27" name="AutoShape 26"/>
+        <xdr:cNvPr id="27" name="AutoShape 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00001B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6169,7 +6668,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="28" name="AutoShape 27"/>
+        <xdr:cNvPr id="28" name="AutoShape 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00001C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6236,7 +6741,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="29" name="AutoShape 28"/>
+        <xdr:cNvPr id="29" name="AutoShape 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00001D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6303,7 +6814,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="30" name="AutoShape 29"/>
+        <xdr:cNvPr id="30" name="AutoShape 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00001E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6370,7 +6887,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="31" name="AutoShape 30"/>
+        <xdr:cNvPr id="31" name="AutoShape 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00001F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6452,7 +6975,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="32" name="AutoShape 31"/>
+        <xdr:cNvPr id="32" name="AutoShape 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000020000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6519,7 +7048,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="33" name="AutoShape 32"/>
+        <xdr:cNvPr id="33" name="AutoShape 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000021000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6586,7 +7121,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="34" name="AutoShape 33"/>
+        <xdr:cNvPr id="34" name="AutoShape 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000022000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6668,7 +7209,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="35" name="AutoShape 34"/>
+        <xdr:cNvPr id="35" name="AutoShape 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000023000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6750,7 +7297,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="36" name="AutoShape 35"/>
+        <xdr:cNvPr id="36" name="AutoShape 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000024000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6795,7 +7348,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="37" name="AutoShape 36"/>
+        <xdr:cNvPr id="37" name="AutoShape 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000025000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6862,7 +7421,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="38" name="AutoShape 37"/>
+        <xdr:cNvPr id="38" name="AutoShape 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000026000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6929,7 +7494,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="39" name="AutoShape 38"/>
+        <xdr:cNvPr id="39" name="AutoShape 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000027000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7026,7 +7597,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="40" name="AutoShape 39"/>
+        <xdr:cNvPr id="40" name="AutoShape 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000028000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7093,7 +7670,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="41" name="Text Box 40"/>
+        <xdr:cNvPr id="41" name="Text Box 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000029000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7189,7 +7772,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="42" name="AutoShape 41"/>
+        <xdr:cNvPr id="42" name="AutoShape 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00002A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7256,7 +7845,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="43" name="AutoShape 42"/>
+        <xdr:cNvPr id="43" name="AutoShape 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00002B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7323,7 +7918,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="44" name="AutoShape 43"/>
+        <xdr:cNvPr id="44" name="AutoShape 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00002C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7390,7 +7991,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="45" name="Rectangle 44"/>
+        <xdr:cNvPr id="45" name="Rectangle 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00002D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7433,7 +8040,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="46" name="AutoShape 45"/>
+        <xdr:cNvPr id="46" name="AutoShape 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00002E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7500,7 +8113,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="47" name="AutoShape 46"/>
+        <xdr:cNvPr id="47" name="AutoShape 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00002F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7567,7 +8186,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="48" name="AutoShape 47"/>
+        <xdr:cNvPr id="48" name="AutoShape 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000030000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7634,7 +8259,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="49" name="AutoShape 48"/>
+        <xdr:cNvPr id="49" name="AutoShape 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000031000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7701,7 +8332,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="50" name="AutoShape 49"/>
+        <xdr:cNvPr id="50" name="AutoShape 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000032000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7768,7 +8405,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="51" name="AutoShape 50"/>
+        <xdr:cNvPr id="51" name="AutoShape 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000033000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7835,7 +8478,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="52" name="AutoShape 51"/>
+        <xdr:cNvPr id="52" name="AutoShape 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000034000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7902,7 +8551,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="53" name="AutoShape 52"/>
+        <xdr:cNvPr id="53" name="AutoShape 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000035000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7969,7 +8624,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="54" name="AutoShape 53"/>
+        <xdr:cNvPr id="54" name="AutoShape 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000036000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -8036,7 +8697,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="55" name="AutoShape 54"/>
+        <xdr:cNvPr id="55" name="AutoShape 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000037000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -8103,7 +8770,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="56" name="AutoShape 55"/>
+        <xdr:cNvPr id="56" name="AutoShape 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000038000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -8170,7 +8843,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="57" name="AutoShape 56"/>
+        <xdr:cNvPr id="57" name="AutoShape 56">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000039000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -8237,7 +8916,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="58" name="AutoShape 57"/>
+        <xdr:cNvPr id="58" name="AutoShape 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00003A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -8403,7 +9088,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Report"/>
@@ -8426,9 +9111,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -8466,9 +9151,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -8503,7 +9188,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -8538,7 +9223,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -8711,20 +9396,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I78"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="55" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="24" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -8735,7 +9420,7 @@
       </c>
       <c r="I4" s="3"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>19</v>
       </c>
@@ -8747,7 +9432,7 @@
       </c>
       <c r="I5" s="7"/>
     </row>
-    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8"/>
       <c r="B6" s="9"/>
       <c r="H6" s="8" t="s">
@@ -8755,19 +9440,19 @@
       </c>
       <c r="I6" s="9"/>
     </row>
-    <row r="9" spans="1:9" ht="21" x14ac:dyDescent="0.35">
-      <c r="B9" s="62" t="s">
+    <row r="9" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="B9" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="62"/>
-      <c r="D9" s="62"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C9" s="64"/>
+      <c r="D9" s="64"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A13" s="61" t="s">
         <v>1</v>
       </c>
@@ -8781,126 +9466,126 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="21" x14ac:dyDescent="0.35">
-      <c r="A14" s="62" t="s">
+    <row r="14" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A14" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="62"/>
-      <c r="C14" s="62"/>
-      <c r="D14" s="62"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B14" s="64"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="64"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>1</v>
       </c>
-      <c r="B15" s="64" t="s">
+      <c r="B15" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="70" t="s">
+      <c r="C15" s="65" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16">
         <f t="shared" ref="A16:A78" si="0">A15+1</f>
         <v>2</v>
       </c>
-      <c r="B16" s="64" t="s">
+      <c r="B16" s="62" t="s">
         <v>92</v>
       </c>
-      <c r="C16" s="70"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C16" s="65"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B17" s="64" t="s">
+      <c r="B17" s="62" t="s">
         <v>93</v>
       </c>
-      <c r="C17" s="70"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C17" s="65"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B18" s="64" t="s">
+      <c r="B18" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="70"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C18" s="65"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B19" s="64" t="s">
+      <c r="B19" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="70"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C19" s="65"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B20" s="64" t="s">
+      <c r="B20" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="70"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C20" s="65"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B21" s="64" t="s">
+      <c r="B21" s="62" t="s">
         <v>94</v>
       </c>
-      <c r="C21" s="70"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C21" s="65"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B22" s="64" t="s">
+      <c r="B22" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="70"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C22" s="65"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B23" s="64" t="s">
+      <c r="B23" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="70"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C23" s="65"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B24" s="64" t="s">
+      <c r="B24" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="C24" s="70"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C24" s="65"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B25" s="64" t="s">
+      <c r="B25" s="62" t="s">
         <v>105</v>
       </c>
-      <c r="C25" s="70"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C25" s="65"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -8908,41 +9593,41 @@
       <c r="B26" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="68" t="s">
+      <c r="C26" s="66" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B27" s="65" t="s">
+      <c r="B27" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="68"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C27" s="66"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B28" s="65" t="s">
+      <c r="B28" t="s">
         <v>100</v>
       </c>
-      <c r="C28" s="68"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C28" s="66"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B29" s="65" t="s">
+      <c r="B29" t="s">
         <v>101</v>
       </c>
-      <c r="C29" s="68"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C29" s="66"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -8950,9 +9635,9 @@
       <c r="B30" t="s">
         <v>95</v>
       </c>
-      <c r="C30" s="68"/>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C30" s="66"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -8960,9 +9645,9 @@
       <c r="B31" t="s">
         <v>102</v>
       </c>
-      <c r="C31" s="68"/>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C31" s="66"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -8970,9 +9655,9 @@
       <c r="B32" t="s">
         <v>103</v>
       </c>
-      <c r="C32" s="68"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C32" s="66"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -8980,59 +9665,59 @@
       <c r="B33" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="68"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C33" s="66"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B34" s="64" t="s">
+      <c r="B34" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="C34" s="70" t="s">
+      <c r="C34" s="65" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B35" s="64" t="s">
+      <c r="B35" s="62" t="s">
         <v>33</v>
       </c>
-      <c r="C35" s="70"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C35" s="65"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B36" s="64" t="s">
+      <c r="B36" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="C36" s="70"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C36" s="65"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B37" s="64" t="s">
+      <c r="B37" s="62" t="s">
         <v>104</v>
       </c>
-      <c r="C37" s="70"/>
-    </row>
-    <row r="38" spans="1:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="A38" s="62" t="s">
+      <c r="C37" s="65"/>
+    </row>
+    <row r="38" spans="1:4" ht="21" x14ac:dyDescent="0.25">
+      <c r="A38" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="62"/>
-      <c r="C38" s="62"/>
-      <c r="D38" s="62"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B38" s="64"/>
+      <c r="C38" s="64"/>
+      <c r="D38" s="64"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39">
         <f>A37+1</f>
         <v>24</v>
@@ -9040,11 +9725,11 @@
       <c r="B39" t="s">
         <v>32</v>
       </c>
-      <c r="C39" s="68" t="s">
+      <c r="C39" s="66" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -9052,9 +9737,9 @@
       <c r="B40" t="s">
         <v>34</v>
       </c>
-      <c r="C40" s="68"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C40" s="66"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -9062,9 +9747,9 @@
       <c r="B41" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="68"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C41" s="66"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -9072,9 +9757,9 @@
       <c r="B42" t="s">
         <v>44</v>
       </c>
-      <c r="C42" s="68"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C42" s="66"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -9082,9 +9767,9 @@
       <c r="B43" t="s">
         <v>46</v>
       </c>
-      <c r="C43" s="68"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C43" s="66"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -9092,9 +9777,9 @@
       <c r="B44" t="s">
         <v>121</v>
       </c>
-      <c r="C44" s="68"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C44" s="66"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -9102,190 +9787,190 @@
       <c r="B45" t="s">
         <v>120</v>
       </c>
-      <c r="C45" s="68"/>
-    </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C45" s="66"/>
+    </row>
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B46" s="64" t="s">
+      <c r="B46" s="62" t="s">
         <v>106</v>
       </c>
-      <c r="C46" s="69" t="s">
+      <c r="C46" s="67" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B47" s="64" t="s">
+      <c r="B47" s="62" t="s">
         <v>107</v>
       </c>
-      <c r="C47" s="69"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C47" s="67"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B48" s="64" t="s">
+      <c r="B48" s="62" t="s">
         <v>108</v>
       </c>
-      <c r="C48" s="69"/>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C48" s="67"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B49" s="64" t="s">
+      <c r="B49" s="62" t="s">
         <v>109</v>
       </c>
-      <c r="C49" s="69"/>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C49" s="67"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B50" s="65" t="s">
+      <c r="B50" t="s">
         <v>110</v>
       </c>
-      <c r="C50" s="67" t="s">
+      <c r="C50" s="68" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B51" s="65" t="s">
+      <c r="B51" t="s">
         <v>111</v>
       </c>
-      <c r="C51" s="67"/>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C51" s="68"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="B52" s="65" t="s">
+      <c r="B52" t="s">
         <v>122</v>
       </c>
-      <c r="C52" s="67"/>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C52" s="68"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="B53" s="64" t="str">
+      <c r="B53" s="62" t="str">
         <f>[1]Report!$A$207</f>
         <v>Homework "Literature"</v>
       </c>
-      <c r="C53" s="69" t="s">
+      <c r="C53" s="67" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="B54" s="64" t="s">
+      <c r="B54" s="62" t="s">
         <v>112</v>
       </c>
-      <c r="C54" s="69"/>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C54" s="67"/>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="B55" s="64" t="s">
+      <c r="B55" s="62" t="s">
         <v>116</v>
       </c>
-      <c r="C55" s="69"/>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C55" s="67"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="B56" s="65" t="s">
+      <c r="B56" t="s">
         <v>115</v>
       </c>
-      <c r="C56" s="67" t="s">
+      <c r="C56" s="68" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="B57" s="65" t="s">
+      <c r="B57" t="s">
         <v>117</v>
       </c>
-      <c r="C57" s="67"/>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C57" s="68"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58">
         <f>A57+1</f>
         <v>43</v>
       </c>
-      <c r="B58" s="65" t="s">
+      <c r="B58" t="s">
         <v>113</v>
       </c>
-      <c r="C58" s="67"/>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C58" s="68"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="B59" s="65" t="s">
+      <c r="B59" t="s">
         <v>114</v>
       </c>
-      <c r="C59" s="67"/>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C59" s="68"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="B60" s="64" t="s">
+      <c r="B60" s="62" t="s">
         <v>118</v>
       </c>
-      <c r="C60" s="69" t="s">
+      <c r="C60" s="67" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="B61" s="64" t="s">
+      <c r="B61" s="62" t="s">
         <v>119</v>
       </c>
-      <c r="C61" s="69"/>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C61" s="67"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="B62" s="64" t="s">
+      <c r="B62" s="62" t="s">
         <v>124</v>
       </c>
-      <c r="C62" s="69"/>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C62" s="67"/>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -9293,39 +9978,39 @@
       <c r="B63" t="s">
         <v>123</v>
       </c>
-      <c r="C63" s="67" t="s">
+      <c r="C63" s="68" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="B64" s="66" t="s">
+      <c r="B64" s="63" t="s">
         <v>125</v>
       </c>
-      <c r="C64" s="67"/>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C64" s="68"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="B65" s="66" t="s">
+      <c r="B65" s="63" t="s">
         <v>126</v>
       </c>
-      <c r="C65" s="67"/>
-    </row>
-    <row r="66" spans="1:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="A66" s="62" t="s">
+      <c r="C65" s="68"/>
+    </row>
+    <row r="66" spans="1:4" ht="21" x14ac:dyDescent="0.25">
+      <c r="A66" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="B66" s="62"/>
-      <c r="C66" s="62"/>
-      <c r="D66" s="62"/>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B66" s="64"/>
+      <c r="C66" s="64"/>
+      <c r="D66" s="64"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67">
         <f>A65+1</f>
         <v>51</v>
@@ -9334,7 +10019,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -9343,7 +10028,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -9352,7 +10037,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -9361,7 +10046,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71">
         <f>A70+1</f>
         <v>55</v>
@@ -9370,7 +10055,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -9379,7 +10064,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -9388,7 +10073,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -9397,25 +10082,25 @@
         <v>48</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -9443,11 +10128,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R44"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="11"/>
       <c r="D1" s="11"/>
       <c r="E1" s="11"/>
@@ -9464,7 +10149,7 @@
       <c r="P1" s="11"/>
       <c r="Q1" s="11"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="11"/>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
@@ -9481,7 +10166,7 @@
       <c r="P2" s="11"/>
       <c r="Q2" s="11"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="11"/>
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
@@ -9498,7 +10183,7 @@
       <c r="P3" s="11"/>
       <c r="Q3" s="11"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="11"/>
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
@@ -9515,7 +10200,7 @@
       <c r="P4" s="11"/>
       <c r="Q4" s="11"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="11"/>
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
@@ -9532,7 +10217,7 @@
       <c r="P5" s="11"/>
       <c r="Q5" s="11"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="11"/>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
@@ -9549,7 +10234,7 @@
       <c r="P6" s="11"/>
       <c r="Q6" s="11"/>
     </row>
-    <row r="7" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="11"/>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -9568,28 +10253,28 @@
       <c r="P7" s="12"/>
       <c r="Q7" s="11"/>
     </row>
-    <row r="8" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" ht="18" x14ac:dyDescent="0.2">
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="63" t="s">
+      <c r="D8" s="69" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="63"/>
-      <c r="F8" s="63"/>
-      <c r="G8" s="63"/>
-      <c r="H8" s="63"/>
-      <c r="I8" s="63"/>
-      <c r="J8" s="63"/>
-      <c r="K8" s="63"/>
-      <c r="L8" s="63"/>
-      <c r="M8" s="63"/>
-      <c r="N8" s="63"/>
-      <c r="O8" s="63"/>
-      <c r="P8" s="63"/>
+      <c r="E8" s="69"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="69"/>
+      <c r="K8" s="69"/>
+      <c r="L8" s="69"/>
+      <c r="M8" s="69"/>
+      <c r="N8" s="69"/>
+      <c r="O8" s="69"/>
+      <c r="P8" s="69"/>
       <c r="Q8" s="11"/>
     </row>
-    <row r="9" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="11"/>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -9608,7 +10293,7 @@
       <c r="P9" s="12"/>
       <c r="Q9" s="11"/>
     </row>
-    <row r="10" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11"/>
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
@@ -9625,7 +10310,7 @@
       <c r="P10" s="11"/>
       <c r="Q10" s="11"/>
     </row>
-    <row r="11" spans="1:18" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A11" s="13"/>
       <c r="B11" s="14"/>
       <c r="C11" s="14" t="s">
@@ -9672,7 +10357,7 @@
       </c>
       <c r="Q11" s="11"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="18"/>
       <c r="B12" s="19"/>
       <c r="C12" s="19" t="s">
@@ -9719,7 +10404,7 @@
       </c>
       <c r="Q12" s="11"/>
     </row>
-    <row r="13" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="23" t="s">
         <v>29</v>
       </c>
@@ -9744,7 +10429,7 @@
       <c r="P13" s="28"/>
       <c r="Q13" s="11"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" s="29">
         <v>1</v>
       </c>
@@ -9770,7 +10455,7 @@
       <c r="Q14" s="35"/>
       <c r="R14" s="36"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" s="37">
         <f>A14+1</f>
         <v>2</v>
@@ -9797,7 +10482,7 @@
       <c r="Q15" s="35"/>
       <c r="R15" s="36"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" s="37">
         <f t="shared" ref="A16:A30" si="0">A15+1</f>
         <v>3</v>
@@ -9824,7 +10509,7 @@
       <c r="Q16" s="35"/>
       <c r="R16" s="36"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" s="37">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -9849,7 +10534,7 @@
       <c r="Q17" s="35"/>
       <c r="R17" s="36"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" s="37">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -9874,7 +10559,7 @@
       <c r="Q18" s="35"/>
       <c r="R18" s="36"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" s="37">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -9897,7 +10582,7 @@
       <c r="Q19" s="35"/>
       <c r="R19" s="36"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" s="37">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -9920,7 +10605,7 @@
       <c r="Q20" s="35"/>
       <c r="R20" s="36"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" s="37">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -9943,7 +10628,7 @@
       <c r="Q21" s="35"/>
       <c r="R21" s="36"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" s="37">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -9966,7 +10651,7 @@
       <c r="Q22" s="35"/>
       <c r="R22" s="36"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" s="37">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -9989,7 +10674,7 @@
       <c r="Q23" s="35"/>
       <c r="R23" s="36"/>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" s="37">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -10012,7 +10697,7 @@
       <c r="Q24" s="35"/>
       <c r="R24" s="36"/>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" s="37">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -10035,7 +10720,7 @@
       <c r="Q25" s="35"/>
       <c r="R25" s="36"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" s="37">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -10058,7 +10743,7 @@
       <c r="Q26" s="35"/>
       <c r="R26" s="36"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" s="37">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -10085,7 +10770,7 @@
       <c r="Q27" s="35"/>
       <c r="R27" s="36"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" s="37">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -10112,7 +10797,7 @@
       <c r="Q28" s="35"/>
       <c r="R28" s="36"/>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" s="37">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -10139,7 +10824,7 @@
       <c r="Q29" s="35"/>
       <c r="R29" s="36"/>
     </row>
-    <row r="30" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="43">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -10166,7 +10851,7 @@
       <c r="Q30" s="35"/>
       <c r="R30" s="36"/>
     </row>
-    <row r="31" spans="1:18" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A31" s="11"/>
       <c r="C31" s="49"/>
       <c r="D31" s="11"/>
@@ -10184,7 +10869,7 @@
       <c r="P31" s="11"/>
       <c r="Q31" s="11"/>
     </row>
-    <row r="32" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
       <c r="C32" s="49"/>
       <c r="D32" s="11"/>
@@ -10202,7 +10887,7 @@
       <c r="P32" s="11"/>
       <c r="Q32" s="11"/>
     </row>
-    <row r="33" spans="1:18" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A33" s="50"/>
       <c r="B33" s="51" t="s">
         <v>58</v>
@@ -10230,7 +10915,7 @@
       <c r="Q33" s="35"/>
       <c r="R33" s="36"/>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A34" s="37"/>
       <c r="B34" s="38" t="s">
         <v>62</v>
@@ -10256,7 +10941,7 @@
       <c r="Q34" s="35"/>
       <c r="R34" s="36"/>
     </row>
-    <row r="35" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="43"/>
       <c r="B35" s="44" t="s">
         <v>31</v>
@@ -10278,7 +10963,7 @@
       <c r="Q35" s="35"/>
       <c r="R35" s="36"/>
     </row>
-    <row r="36" spans="1:18" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A36" s="11"/>
       <c r="D36" s="11"/>
       <c r="E36" s="11"/>
@@ -10295,7 +10980,7 @@
       <c r="P36" s="11"/>
       <c r="Q36" s="11"/>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A37" s="11"/>
       <c r="D37" s="11"/>
       <c r="E37" s="11"/>
@@ -10312,7 +10997,7 @@
       <c r="P37" s="11"/>
       <c r="Q37" s="11"/>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A38" s="11"/>
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
@@ -10329,7 +11014,7 @@
       <c r="P38" s="11"/>
       <c r="Q38" s="11"/>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A39" s="11"/>
       <c r="B39" s="57" t="s">
         <v>65</v>
@@ -10349,7 +11034,7 @@
       <c r="P39" s="11"/>
       <c r="Q39" s="11"/>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A40" s="11"/>
       <c r="B40" s="57" t="s">
         <v>66</v>
@@ -10371,7 +11056,7 @@
       <c r="P40" s="11"/>
       <c r="Q40" s="11"/>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A41" s="11"/>
       <c r="B41" s="57"/>
       <c r="D41" s="11"/>
@@ -10389,7 +11074,7 @@
       <c r="P41" s="11"/>
       <c r="Q41" s="11"/>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A42" s="11"/>
       <c r="D42" s="11"/>
       <c r="E42" s="11"/>
@@ -10406,7 +11091,7 @@
       <c r="P42" s="11"/>
       <c r="Q42" s="11"/>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A43" s="11"/>
       <c r="B43" s="57"/>
       <c r="D43" s="11"/>
@@ -10424,7 +11109,7 @@
       <c r="P43" s="11"/>
       <c r="Q43" s="11"/>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A44" s="11"/>
       <c r="D44" s="11"/>
       <c r="E44" s="11"/>
@@ -10451,11 +11136,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:P44"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="11"/>
       <c r="D1" s="11"/>
       <c r="E1" s="11"/>
@@ -10471,7 +11156,7 @@
       <c r="O1" s="11"/>
       <c r="P1" s="11"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="11"/>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
@@ -10487,7 +11172,7 @@
       <c r="O2" s="11"/>
       <c r="P2" s="11"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="11"/>
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
@@ -10503,7 +11188,7 @@
       <c r="O3" s="11"/>
       <c r="P3" s="11"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="11"/>
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
@@ -10519,7 +11204,7 @@
       <c r="O4" s="11"/>
       <c r="P4" s="11"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="11"/>
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
@@ -10535,7 +11220,7 @@
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="11"/>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
@@ -10551,7 +11236,7 @@
       <c r="O6" s="11"/>
       <c r="P6" s="11"/>
     </row>
-    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="11"/>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -10569,27 +11254,27 @@
       <c r="O7" s="12"/>
       <c r="P7" s="12"/>
     </row>
-    <row r="8" spans="1:16" ht="18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" ht="18" x14ac:dyDescent="0.2">
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="63" t="s">
+      <c r="D8" s="69" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="63"/>
-      <c r="F8" s="63"/>
-      <c r="G8" s="63"/>
-      <c r="H8" s="63"/>
-      <c r="I8" s="63"/>
-      <c r="J8" s="63"/>
-      <c r="K8" s="63"/>
-      <c r="L8" s="63"/>
-      <c r="M8" s="63"/>
-      <c r="N8" s="63"/>
-      <c r="O8" s="63"/>
-      <c r="P8" s="63"/>
-    </row>
-    <row r="9" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E8" s="69"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="69"/>
+      <c r="K8" s="69"/>
+      <c r="L8" s="69"/>
+      <c r="M8" s="69"/>
+      <c r="N8" s="69"/>
+      <c r="O8" s="69"/>
+      <c r="P8" s="69"/>
+    </row>
+    <row r="9" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="11"/>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -10607,7 +11292,7 @@
       <c r="O9" s="12"/>
       <c r="P9" s="12"/>
     </row>
-    <row r="10" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11"/>
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
@@ -10623,7 +11308,7 @@
       <c r="O10" s="11"/>
       <c r="P10" s="11"/>
     </row>
-    <row r="11" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A11" s="13"/>
       <c r="B11" s="14"/>
       <c r="C11" s="14" t="s">
@@ -10669,7 +11354,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" s="18"/>
       <c r="B12" s="19"/>
       <c r="C12" s="19" t="s">
@@ -10715,7 +11400,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="23" t="s">
         <v>71</v>
       </c>
@@ -10739,7 +11424,7 @@
       <c r="O13" s="27"/>
       <c r="P13" s="28"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" s="29">
         <v>1</v>
       </c>
@@ -10763,7 +11448,7 @@
       <c r="O14" s="33"/>
       <c r="P14" s="34"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="37">
         <f>A14+1</f>
         <v>2</v>
@@ -10788,7 +11473,7 @@
       <c r="O15" s="41"/>
       <c r="P15" s="42"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" s="37">
         <f t="shared" ref="A16:A30" si="0">A15+1</f>
         <v>3</v>
@@ -10813,7 +11498,7 @@
       <c r="O16" s="41"/>
       <c r="P16" s="42"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" s="37">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -10836,7 +11521,7 @@
       <c r="O17" s="41"/>
       <c r="P17" s="42"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" s="37">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -10859,7 +11544,7 @@
       <c r="O18" s="41"/>
       <c r="P18" s="42"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" s="37">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -10880,7 +11565,7 @@
       <c r="O19" s="41"/>
       <c r="P19" s="42"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" s="37">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -10901,7 +11586,7 @@
       <c r="O20" s="41"/>
       <c r="P20" s="42"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" s="37">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -10922,7 +11607,7 @@
       <c r="O21" s="41"/>
       <c r="P21" s="42"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" s="37">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -10943,7 +11628,7 @@
       <c r="O22" s="41"/>
       <c r="P22" s="42"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" s="37">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -10964,7 +11649,7 @@
       <c r="O23" s="41"/>
       <c r="P23" s="42"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" s="37">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -10985,7 +11670,7 @@
       <c r="O24" s="41"/>
       <c r="P24" s="42"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" s="37">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -11006,7 +11691,7 @@
       <c r="O25" s="41"/>
       <c r="P25" s="42"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" s="37">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -11027,7 +11712,7 @@
       <c r="O26" s="41"/>
       <c r="P26" s="42"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" s="37">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -11052,7 +11737,7 @@
       <c r="O27" s="41"/>
       <c r="P27" s="42"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" s="37">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -11077,7 +11762,7 @@
       <c r="O28" s="41"/>
       <c r="P28" s="42"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" s="37">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -11102,7 +11787,7 @@
       <c r="O29" s="41"/>
       <c r="P29" s="42"/>
     </row>
-    <row r="30" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="43">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -11127,7 +11812,7 @@
       <c r="O30" s="47"/>
       <c r="P30" s="48"/>
     </row>
-    <row r="31" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A31" s="11"/>
       <c r="C31" s="49"/>
       <c r="D31" s="11"/>
@@ -11144,7 +11829,7 @@
       <c r="O31" s="11"/>
       <c r="P31" s="11"/>
     </row>
-    <row r="32" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
       <c r="C32" s="49"/>
       <c r="D32" s="11"/>
@@ -11161,7 +11846,7 @@
       <c r="O32" s="11"/>
       <c r="P32" s="11"/>
     </row>
-    <row r="33" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A33" s="50"/>
       <c r="B33" s="51" t="s">
         <v>79</v>
@@ -11187,7 +11872,7 @@
       <c r="O33" s="54"/>
       <c r="P33" s="55"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" s="37"/>
       <c r="B34" s="38" t="s">
         <v>83</v>
@@ -11211,7 +11896,7 @@
       </c>
       <c r="P34" s="42"/>
     </row>
-    <row r="35" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="43"/>
       <c r="B35" s="44" t="s">
         <v>86</v>
@@ -11231,7 +11916,7 @@
       <c r="O35" s="47"/>
       <c r="P35" s="48"/>
     </row>
-    <row r="36" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A36" s="11"/>
       <c r="D36" s="11"/>
       <c r="E36" s="11"/>
@@ -11247,7 +11932,7 @@
       <c r="O36" s="11"/>
       <c r="P36" s="11"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" s="11"/>
       <c r="D37" s="11"/>
       <c r="E37" s="11"/>
@@ -11263,7 +11948,7 @@
       <c r="O37" s="11"/>
       <c r="P37" s="11"/>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38" s="11"/>
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
@@ -11279,7 +11964,7 @@
       <c r="O38" s="11"/>
       <c r="P38" s="11"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" s="11"/>
       <c r="B39" s="57" t="s">
         <v>87</v>
@@ -11298,7 +11983,7 @@
       <c r="O39" s="11"/>
       <c r="P39" s="11"/>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40" s="11"/>
       <c r="D40" s="11"/>
       <c r="E40" s="11"/>
@@ -11316,7 +12001,7 @@
       <c r="O40" s="11"/>
       <c r="P40" s="11"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41" s="11"/>
       <c r="B41" s="57"/>
       <c r="D41" s="11"/>
@@ -11333,7 +12018,7 @@
       <c r="O41" s="11"/>
       <c r="P41" s="11"/>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42" s="11"/>
       <c r="D42" s="11"/>
       <c r="E42" s="11"/>
@@ -11349,7 +12034,7 @@
       <c r="O42" s="11"/>
       <c r="P42" s="11"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43" s="11"/>
       <c r="D43" s="11"/>
       <c r="E43" s="11"/>
@@ -11365,7 +12050,7 @@
       <c r="O43" s="11"/>
       <c r="P43" s="11"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44" s="11"/>
       <c r="D44" s="11"/>
       <c r="E44" s="11"/>
@@ -11391,20 +12076,20 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A7:I25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="7" spans="1:9" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="24" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
@@ -11415,7 +12100,7 @@
       </c>
       <c r="I10" s="3"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>19</v>
       </c>
@@ -11427,7 +12112,7 @@
       </c>
       <c r="I11" s="7"/>
     </row>
-    <row r="12" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8"/>
       <c r="B12" s="9"/>
       <c r="H12" s="8" t="s">
@@ -11435,14 +12120,14 @@
       </c>
       <c r="I12" s="9"/>
     </row>
-    <row r="15" spans="1:9" ht="21" x14ac:dyDescent="0.35">
-      <c r="B15" s="62" t="s">
+    <row r="15" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="B15" s="64" t="s">
         <v>89</v>
       </c>
-      <c r="C15" s="62"/>
-      <c r="D15" s="62"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C15" s="64"/>
+      <c r="D15" s="64"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="10" t="s">
         <v>14</v>
       </c>
@@ -11456,7 +12141,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>96</v>
       </c>
@@ -11464,32 +12149,32 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
         <v>90</v>
       </c>

--- a/ProjectManagement/Checklist.xlsx
+++ b/ProjectManagement/Checklist.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10112"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B585C7A-5B5C-144A-98D7-26BA12C84679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4282C8B0-6E26-7945-832C-3A61545264E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="51200" windowHeight="25260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4880" yWindow="620" windowWidth="46320" windowHeight="25260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Checklist" sheetId="1" r:id="rId1"/>
@@ -1029,7 +1029,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1214,6 +1214,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9484,6 +9485,9 @@
       <c r="C15" s="65" t="s">
         <v>127</v>
       </c>
+      <c r="D15" s="70">
+        <v>45925</v>
+      </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16">
@@ -9494,8 +9498,11 @@
         <v>92</v>
       </c>
       <c r="C16" s="65"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D16" s="70">
+        <v>45927</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -9504,8 +9511,11 @@
         <v>93</v>
       </c>
       <c r="C17" s="65"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D17" s="70">
+        <v>45926</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -9514,8 +9524,11 @@
         <v>4</v>
       </c>
       <c r="C18" s="65"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D18" s="70">
+        <v>45926</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -9524,8 +9537,11 @@
         <v>5</v>
       </c>
       <c r="C19" s="65"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D19" s="70">
+        <v>45926</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -9534,8 +9550,11 @@
         <v>7</v>
       </c>
       <c r="C20" s="65"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D20" s="70">
+        <v>45926</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -9544,8 +9563,11 @@
         <v>94</v>
       </c>
       <c r="C21" s="65"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D21" s="70">
+        <v>45957</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -9554,8 +9576,11 @@
         <v>6</v>
       </c>
       <c r="C22" s="65"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D22" s="70">
+        <v>45957</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -9564,8 +9589,11 @@
         <v>8</v>
       </c>
       <c r="C23" s="65"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D23" s="70">
+        <v>45957</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -9574,8 +9602,11 @@
         <v>9</v>
       </c>
       <c r="C24" s="65"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D24" s="70">
+        <v>45957</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -9585,7 +9616,7 @@
       </c>
       <c r="C25" s="65"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -9597,7 +9628,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -9607,7 +9638,7 @@
       </c>
       <c r="C27" s="66"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -9617,7 +9648,7 @@
       </c>
       <c r="C28" s="66"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -9627,7 +9658,7 @@
       </c>
       <c r="C29" s="66"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -9637,7 +9668,7 @@
       </c>
       <c r="C30" s="66"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -9647,7 +9678,7 @@
       </c>
       <c r="C31" s="66"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>18</v>

--- a/ProjectManagement/Checklist.xlsx
+++ b/ProjectManagement/Checklist.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10112"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4282C8B0-6E26-7945-832C-3A61545264E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BFE8972-0EBE-4BC1-95CE-F2F866F1BC1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4880" yWindow="620" windowWidth="46320" windowHeight="25260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Checklist" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="153">
   <si>
     <t>Checklist</t>
   </si>
@@ -445,13 +445,61 @@
   </si>
   <si>
     <t>10 th weeek</t>
+  </si>
+  <si>
+    <t>25.9.2025</t>
+  </si>
+  <si>
+    <t>28.9.2025</t>
+  </si>
+  <si>
+    <t>2.10.2025</t>
+  </si>
+  <si>
+    <t>6.10.2025</t>
+  </si>
+  <si>
+    <t>13.10.2025</t>
+  </si>
+  <si>
+    <t>20.10.2025</t>
+  </si>
+  <si>
+    <t>20.10.2026</t>
+  </si>
+  <si>
+    <t>20.10.2027</t>
+  </si>
+  <si>
+    <t>20.10.2028</t>
+  </si>
+  <si>
+    <t>20.10.2029</t>
+  </si>
+  <si>
+    <t>27.10.2025</t>
+  </si>
+  <si>
+    <t>27.10.2026</t>
+  </si>
+  <si>
+    <t>27.10.2027</t>
+  </si>
+  <si>
+    <t>27.10.2028</t>
+  </si>
+  <si>
+    <t>27.10.2029</t>
+  </si>
+  <si>
+    <t>27.10.2030</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -515,6 +563,12 @@
       <sz val="8"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1029,7 +1083,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1196,6 +1250,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1214,7 +1269,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2109,8 +2167,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="8750300" y="5067300"/>
-          <a:ext cx="2028825" cy="190500"/>
+          <a:off x="8420100" y="4846320"/>
+          <a:ext cx="1929765" cy="182880"/>
           <a:chOff x="691" y="481"/>
           <a:chExt cx="144" cy="27"/>
         </a:xfrm>
@@ -5931,8 +5989,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="8750300" y="5067300"/>
-          <a:ext cx="2028825" cy="190500"/>
+          <a:off x="8420100" y="4846320"/>
+          <a:ext cx="1929765" cy="182880"/>
           <a:chOff x="691" y="481"/>
           <a:chExt cx="144" cy="27"/>
         </a:xfrm>
@@ -9399,18 +9457,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I78"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="55" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -9421,7 +9479,7 @@
       </c>
       <c r="I4" s="3"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>19</v>
       </c>
@@ -9433,7 +9491,7 @@
       </c>
       <c r="I5" s="7"/>
     </row>
-    <row r="6" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="8"/>
       <c r="B6" s="9"/>
       <c r="H6" s="8" t="s">
@@ -9441,19 +9499,19 @@
       </c>
       <c r="I6" s="9"/>
     </row>
-    <row r="9" spans="1:9" ht="21" x14ac:dyDescent="0.25">
-      <c r="B9" s="64" t="s">
+    <row r="9" spans="1:9" ht="21" x14ac:dyDescent="0.4">
+      <c r="B9" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="64"/>
-      <c r="D9" s="64"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C9" s="65"/>
+      <c r="D9" s="65"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="21" x14ac:dyDescent="0.4">
       <c r="A13" s="61" t="s">
         <v>1</v>
       </c>
@@ -9467,29 +9525,29 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="21" x14ac:dyDescent="0.25">
-      <c r="A14" s="64" t="s">
+    <row r="14" spans="1:9" ht="21" x14ac:dyDescent="0.4">
+      <c r="A14" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="64"/>
-      <c r="C14" s="64"/>
-      <c r="D14" s="64"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B14" s="65"/>
+      <c r="C14" s="65"/>
+      <c r="D14" s="65"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1</v>
       </c>
       <c r="B15" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="65" t="s">
+      <c r="C15" s="66" t="s">
         <v>127</v>
       </c>
-      <c r="D15" s="70">
-        <v>45925</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D15" s="71" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16">
         <f t="shared" ref="A16:A78" si="0">A15+1</f>
         <v>2</v>
@@ -9497,12 +9555,12 @@
       <c r="B16" s="62" t="s">
         <v>92</v>
       </c>
-      <c r="C16" s="65"/>
-      <c r="D16" s="70">
-        <v>45927</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C16" s="66"/>
+      <c r="D16" s="71" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -9510,12 +9568,12 @@
       <c r="B17" s="62" t="s">
         <v>93</v>
       </c>
-      <c r="C17" s="65"/>
-      <c r="D17" s="70">
-        <v>45926</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C17" s="66"/>
+      <c r="D17" s="71" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -9523,12 +9581,12 @@
       <c r="B18" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="65"/>
-      <c r="D18" s="70">
-        <v>45926</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C18" s="66"/>
+      <c r="D18" s="71" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -9536,12 +9594,12 @@
       <c r="B19" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="65"/>
-      <c r="D19" s="70">
-        <v>45926</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C19" s="66"/>
+      <c r="D19" s="71" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -9549,12 +9607,12 @@
       <c r="B20" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="65"/>
-      <c r="D20" s="70">
-        <v>45926</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C20" s="66"/>
+      <c r="D20" s="71" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -9562,12 +9620,12 @@
       <c r="B21" s="62" t="s">
         <v>94</v>
       </c>
-      <c r="C21" s="65"/>
-      <c r="D21" s="70">
-        <v>45957</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C21" s="66"/>
+      <c r="D21" s="71" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -9575,12 +9633,12 @@
       <c r="B22" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="65"/>
-      <c r="D22" s="70">
-        <v>45957</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C22" s="66"/>
+      <c r="D22" s="71" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -9588,12 +9646,12 @@
       <c r="B23" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="65"/>
-      <c r="D23" s="70">
-        <v>45957</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C23" s="66"/>
+      <c r="D23" s="71" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -9601,12 +9659,12 @@
       <c r="B24" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="C24" s="65"/>
-      <c r="D24" s="70">
-        <v>45957</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C24" s="66"/>
+      <c r="D24" s="71" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -9614,9 +9672,12 @@
       <c r="B25" s="62" t="s">
         <v>105</v>
       </c>
-      <c r="C25" s="65"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C25" s="66"/>
+      <c r="D25" s="71" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -9624,11 +9685,14 @@
       <c r="B26" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="66" t="s">
+      <c r="C26" s="67" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D26" s="64" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -9636,9 +9700,12 @@
       <c r="B27" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="66"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C27" s="67"/>
+      <c r="D27" s="64" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -9646,9 +9713,12 @@
       <c r="B28" t="s">
         <v>100</v>
       </c>
-      <c r="C28" s="66"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C28" s="67"/>
+      <c r="D28" s="64" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -9656,9 +9726,12 @@
       <c r="B29" t="s">
         <v>101</v>
       </c>
-      <c r="C29" s="66"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C29" s="67"/>
+      <c r="D29" s="64" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -9666,9 +9739,12 @@
       <c r="B30" t="s">
         <v>95</v>
       </c>
-      <c r="C30" s="66"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C30" s="67"/>
+      <c r="D30" s="64" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -9676,9 +9752,12 @@
       <c r="B31" t="s">
         <v>102</v>
       </c>
-      <c r="C31" s="66"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C31" s="67"/>
+      <c r="D31" s="64" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -9686,9 +9765,12 @@
       <c r="B32" t="s">
         <v>103</v>
       </c>
-      <c r="C32" s="66"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C32" s="67"/>
+      <c r="D32" s="64" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -9696,9 +9778,12 @@
       <c r="B33" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="66"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C33" s="67"/>
+      <c r="D33" s="64" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -9706,11 +9791,14 @@
       <c r="B34" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="C34" s="65" t="s">
+      <c r="C34" s="66" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D34" s="64" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -9718,9 +9806,12 @@
       <c r="B35" s="62" t="s">
         <v>33</v>
       </c>
-      <c r="C35" s="65"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C35" s="66"/>
+      <c r="D35" s="64" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -9728,9 +9819,12 @@
       <c r="B36" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="C36" s="65"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C36" s="66"/>
+      <c r="D36" s="64" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -9738,17 +9832,20 @@
       <c r="B37" s="62" t="s">
         <v>104</v>
       </c>
-      <c r="C37" s="65"/>
-    </row>
-    <row r="38" spans="1:4" ht="21" x14ac:dyDescent="0.25">
-      <c r="A38" s="64" t="s">
+      <c r="C37" s="66"/>
+      <c r="D37" s="64" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="21" x14ac:dyDescent="0.4">
+      <c r="A38" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="64"/>
-      <c r="C38" s="64"/>
-      <c r="D38" s="64"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B38" s="65"/>
+      <c r="C38" s="65"/>
+      <c r="D38" s="65"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39">
         <f>A37+1</f>
         <v>24</v>
@@ -9756,11 +9853,14 @@
       <c r="B39" t="s">
         <v>32</v>
       </c>
-      <c r="C39" s="66" t="s">
+      <c r="C39" s="67" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D39" s="72" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -9768,9 +9868,12 @@
       <c r="B40" t="s">
         <v>34</v>
       </c>
-      <c r="C40" s="66"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C40" s="67"/>
+      <c r="D40" s="72" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -9778,9 +9881,12 @@
       <c r="B41" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="66"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C41" s="67"/>
+      <c r="D41" s="72" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -9788,9 +9894,12 @@
       <c r="B42" t="s">
         <v>44</v>
       </c>
-      <c r="C42" s="66"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C42" s="67"/>
+      <c r="D42" s="72" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -9798,9 +9907,12 @@
       <c r="B43" t="s">
         <v>46</v>
       </c>
-      <c r="C43" s="66"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C43" s="67"/>
+      <c r="D43" s="72" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -9808,9 +9920,12 @@
       <c r="B44" t="s">
         <v>121</v>
       </c>
-      <c r="C44" s="66"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C44" s="67"/>
+      <c r="D44" s="72" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -9818,9 +9933,12 @@
       <c r="B45" t="s">
         <v>120</v>
       </c>
-      <c r="C45" s="66"/>
-    </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C45" s="67"/>
+      <c r="D45" s="72" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -9828,11 +9946,14 @@
       <c r="B46" s="62" t="s">
         <v>106</v>
       </c>
-      <c r="C46" s="67" t="s">
+      <c r="C46" s="68" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D46" s="72" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -9840,9 +9961,12 @@
       <c r="B47" s="62" t="s">
         <v>107</v>
       </c>
-      <c r="C47" s="67"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C47" s="68"/>
+      <c r="D47" s="72" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -9850,9 +9974,12 @@
       <c r="B48" s="62" t="s">
         <v>108</v>
       </c>
-      <c r="C48" s="67"/>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C48" s="68"/>
+      <c r="D48" s="72" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -9860,9 +9987,12 @@
       <c r="B49" s="62" t="s">
         <v>109</v>
       </c>
-      <c r="C49" s="67"/>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C49" s="68"/>
+      <c r="D49" s="72" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -9870,11 +10000,11 @@
       <c r="B50" t="s">
         <v>110</v>
       </c>
-      <c r="C50" s="68" t="s">
+      <c r="C50" s="69" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -9882,9 +10012,9 @@
       <c r="B51" t="s">
         <v>111</v>
       </c>
-      <c r="C51" s="68"/>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C51" s="69"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -9892,9 +10022,9 @@
       <c r="B52" t="s">
         <v>122</v>
       </c>
-      <c r="C52" s="68"/>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C52" s="69"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -9903,11 +10033,11 @@
         <f>[1]Report!$A$207</f>
         <v>Homework "Literature"</v>
       </c>
-      <c r="C53" s="67" t="s">
+      <c r="C53" s="68" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -9915,9 +10045,9 @@
       <c r="B54" s="62" t="s">
         <v>112</v>
       </c>
-      <c r="C54" s="67"/>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C54" s="68"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -9925,9 +10055,9 @@
       <c r="B55" s="62" t="s">
         <v>116</v>
       </c>
-      <c r="C55" s="67"/>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C55" s="68"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -9935,11 +10065,11 @@
       <c r="B56" t="s">
         <v>115</v>
       </c>
-      <c r="C56" s="68" t="s">
+      <c r="C56" s="69" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -9947,9 +10077,9 @@
       <c r="B57" t="s">
         <v>117</v>
       </c>
-      <c r="C57" s="68"/>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C57" s="69"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58">
         <f>A57+1</f>
         <v>43</v>
@@ -9957,9 +10087,9 @@
       <c r="B58" t="s">
         <v>113</v>
       </c>
-      <c r="C58" s="68"/>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C58" s="69"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -9967,9 +10097,9 @@
       <c r="B59" t="s">
         <v>114</v>
       </c>
-      <c r="C59" s="68"/>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C59" s="69"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -9977,11 +10107,11 @@
       <c r="B60" s="62" t="s">
         <v>118</v>
       </c>
-      <c r="C60" s="67" t="s">
+      <c r="C60" s="68" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -9989,9 +10119,9 @@
       <c r="B61" s="62" t="s">
         <v>119</v>
       </c>
-      <c r="C61" s="67"/>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C61" s="68"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -9999,9 +10129,9 @@
       <c r="B62" s="62" t="s">
         <v>124</v>
       </c>
-      <c r="C62" s="67"/>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C62" s="68"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -10009,11 +10139,11 @@
       <c r="B63" t="s">
         <v>123</v>
       </c>
-      <c r="C63" s="68" t="s">
+      <c r="C63" s="69" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -10021,9 +10151,9 @@
       <c r="B64" s="63" t="s">
         <v>125</v>
       </c>
-      <c r="C64" s="68"/>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C64" s="69"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -10031,17 +10161,17 @@
       <c r="B65" s="63" t="s">
         <v>126</v>
       </c>
-      <c r="C65" s="68"/>
-    </row>
-    <row r="66" spans="1:4" ht="21" x14ac:dyDescent="0.25">
-      <c r="A66" s="64" t="s">
+      <c r="C65" s="69"/>
+    </row>
+    <row r="66" spans="1:4" ht="21" x14ac:dyDescent="0.4">
+      <c r="A66" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="B66" s="64"/>
-      <c r="C66" s="64"/>
-      <c r="D66" s="64"/>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B66" s="65"/>
+      <c r="C66" s="65"/>
+      <c r="D66" s="65"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67">
         <f>A65+1</f>
         <v>51</v>
@@ -10050,7 +10180,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -10059,7 +10189,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -10068,7 +10198,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -10077,7 +10207,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71">
         <f>A70+1</f>
         <v>55</v>
@@ -10086,7 +10216,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -10095,7 +10225,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -10104,7 +10234,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -10113,25 +10243,25 @@
         <v>48</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -10154,6 +10284,7 @@
     <mergeCell ref="C60:C62"/>
     <mergeCell ref="C63:C65"/>
   </mergeCells>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -10161,9 +10292,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R44"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="11"/>
       <c r="D1" s="11"/>
       <c r="E1" s="11"/>
@@ -10180,7 +10311,7 @@
       <c r="P1" s="11"/>
       <c r="Q1" s="11"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="11"/>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
@@ -10197,7 +10328,7 @@
       <c r="P2" s="11"/>
       <c r="Q2" s="11"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="11"/>
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
@@ -10214,7 +10345,7 @@
       <c r="P3" s="11"/>
       <c r="Q3" s="11"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="11"/>
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
@@ -10231,7 +10362,7 @@
       <c r="P4" s="11"/>
       <c r="Q4" s="11"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="11"/>
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
@@ -10248,7 +10379,7 @@
       <c r="P5" s="11"/>
       <c r="Q5" s="11"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="11"/>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
@@ -10265,7 +10396,7 @@
       <c r="P6" s="11"/>
       <c r="Q6" s="11"/>
     </row>
-    <row r="7" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="11"/>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -10284,28 +10415,28 @@
       <c r="P7" s="12"/>
       <c r="Q7" s="11"/>
     </row>
-    <row r="8" spans="1:18" ht="18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="69" t="s">
+      <c r="D8" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69"/>
-      <c r="J8" s="69"/>
-      <c r="K8" s="69"/>
-      <c r="L8" s="69"/>
-      <c r="M8" s="69"/>
-      <c r="N8" s="69"/>
-      <c r="O8" s="69"/>
-      <c r="P8" s="69"/>
+      <c r="E8" s="70"/>
+      <c r="F8" s="70"/>
+      <c r="G8" s="70"/>
+      <c r="H8" s="70"/>
+      <c r="I8" s="70"/>
+      <c r="J8" s="70"/>
+      <c r="K8" s="70"/>
+      <c r="L8" s="70"/>
+      <c r="M8" s="70"/>
+      <c r="N8" s="70"/>
+      <c r="O8" s="70"/>
+      <c r="P8" s="70"/>
       <c r="Q8" s="11"/>
     </row>
-    <row r="9" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="11"/>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -10324,7 +10455,7 @@
       <c r="P9" s="12"/>
       <c r="Q9" s="11"/>
     </row>
-    <row r="10" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11"/>
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
@@ -10341,7 +10472,7 @@
       <c r="P10" s="11"/>
       <c r="Q10" s="11"/>
     </row>
-    <row r="11" spans="1:18" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>
       <c r="B11" s="14"/>
       <c r="C11" s="14" t="s">
@@ -10388,7 +10519,7 @@
       </c>
       <c r="Q11" s="11"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="18"/>
       <c r="B12" s="19"/>
       <c r="C12" s="19" t="s">
@@ -10435,7 +10566,7 @@
       </c>
       <c r="Q12" s="11"/>
     </row>
-    <row r="13" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="23" t="s">
         <v>29</v>
       </c>
@@ -10460,7 +10591,7 @@
       <c r="P13" s="28"/>
       <c r="Q13" s="11"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="29">
         <v>1</v>
       </c>
@@ -10486,7 +10617,7 @@
       <c r="Q14" s="35"/>
       <c r="R14" s="36"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <f>A14+1</f>
         <v>2</v>
@@ -10513,7 +10644,7 @@
       <c r="Q15" s="35"/>
       <c r="R15" s="36"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <f t="shared" ref="A16:A30" si="0">A15+1</f>
         <v>3</v>
@@ -10540,7 +10671,7 @@
       <c r="Q16" s="35"/>
       <c r="R16" s="36"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -10565,7 +10696,7 @@
       <c r="Q17" s="35"/>
       <c r="R17" s="36"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="37">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -10590,7 +10721,7 @@
       <c r="Q18" s="35"/>
       <c r="R18" s="36"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -10613,7 +10744,7 @@
       <c r="Q19" s="35"/>
       <c r="R19" s="36"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -10636,7 +10767,7 @@
       <c r="Q20" s="35"/>
       <c r="R20" s="36"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -10659,7 +10790,7 @@
       <c r="Q21" s="35"/>
       <c r="R21" s="36"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -10682,7 +10813,7 @@
       <c r="Q22" s="35"/>
       <c r="R22" s="36"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -10705,7 +10836,7 @@
       <c r="Q23" s="35"/>
       <c r="R23" s="36"/>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="37">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -10728,7 +10859,7 @@
       <c r="Q24" s="35"/>
       <c r="R24" s="36"/>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -10751,7 +10882,7 @@
       <c r="Q25" s="35"/>
       <c r="R25" s="36"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="37">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -10774,7 +10905,7 @@
       <c r="Q26" s="35"/>
       <c r="R26" s="36"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -10801,7 +10932,7 @@
       <c r="Q27" s="35"/>
       <c r="R27" s="36"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" s="37">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -10828,7 +10959,7 @@
       <c r="Q28" s="35"/>
       <c r="R28" s="36"/>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -10855,7 +10986,7 @@
       <c r="Q29" s="35"/>
       <c r="R29" s="36"/>
     </row>
-    <row r="30" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="43">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -10882,7 +11013,7 @@
       <c r="Q30" s="35"/>
       <c r="R30" s="36"/>
     </row>
-    <row r="31" spans="1:18" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:18" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A31" s="11"/>
       <c r="C31" s="49"/>
       <c r="D31" s="11"/>
@@ -10900,7 +11031,7 @@
       <c r="P31" s="11"/>
       <c r="Q31" s="11"/>
     </row>
-    <row r="32" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="11"/>
       <c r="C32" s="49"/>
       <c r="D32" s="11"/>
@@ -10918,7 +11049,7 @@
       <c r="P32" s="11"/>
       <c r="Q32" s="11"/>
     </row>
-    <row r="33" spans="1:18" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:18" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A33" s="50"/>
       <c r="B33" s="51" t="s">
         <v>58</v>
@@ -10946,7 +11077,7 @@
       <c r="Q33" s="35"/>
       <c r="R33" s="36"/>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" s="37"/>
       <c r="B34" s="38" t="s">
         <v>62</v>
@@ -10972,7 +11103,7 @@
       <c r="Q34" s="35"/>
       <c r="R34" s="36"/>
     </row>
-    <row r="35" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="43"/>
       <c r="B35" s="44" t="s">
         <v>31</v>
@@ -10994,7 +11125,7 @@
       <c r="Q35" s="35"/>
       <c r="R35" s="36"/>
     </row>
-    <row r="36" spans="1:18" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:18" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A36" s="11"/>
       <c r="D36" s="11"/>
       <c r="E36" s="11"/>
@@ -11011,7 +11142,7 @@
       <c r="P36" s="11"/>
       <c r="Q36" s="11"/>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" s="11"/>
       <c r="D37" s="11"/>
       <c r="E37" s="11"/>
@@ -11028,7 +11159,7 @@
       <c r="P37" s="11"/>
       <c r="Q37" s="11"/>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" s="11"/>
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
@@ -11045,7 +11176,7 @@
       <c r="P38" s="11"/>
       <c r="Q38" s="11"/>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" s="11"/>
       <c r="B39" s="57" t="s">
         <v>65</v>
@@ -11065,7 +11196,7 @@
       <c r="P39" s="11"/>
       <c r="Q39" s="11"/>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" s="11"/>
       <c r="B40" s="57" t="s">
         <v>66</v>
@@ -11087,7 +11218,7 @@
       <c r="P40" s="11"/>
       <c r="Q40" s="11"/>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" s="11"/>
       <c r="B41" s="57"/>
       <c r="D41" s="11"/>
@@ -11105,7 +11236,7 @@
       <c r="P41" s="11"/>
       <c r="Q41" s="11"/>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" s="11"/>
       <c r="D42" s="11"/>
       <c r="E42" s="11"/>
@@ -11122,7 +11253,7 @@
       <c r="P42" s="11"/>
       <c r="Q42" s="11"/>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" s="11"/>
       <c r="B43" s="57"/>
       <c r="D43" s="11"/>
@@ -11140,7 +11271,7 @@
       <c r="P43" s="11"/>
       <c r="Q43" s="11"/>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" s="11"/>
       <c r="D44" s="11"/>
       <c r="E44" s="11"/>
@@ -11169,9 +11300,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:P44"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="11"/>
       <c r="D1" s="11"/>
       <c r="E1" s="11"/>
@@ -11187,7 +11318,7 @@
       <c r="O1" s="11"/>
       <c r="P1" s="11"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="11"/>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
@@ -11203,7 +11334,7 @@
       <c r="O2" s="11"/>
       <c r="P2" s="11"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="11"/>
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
@@ -11219,7 +11350,7 @@
       <c r="O3" s="11"/>
       <c r="P3" s="11"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="11"/>
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
@@ -11235,7 +11366,7 @@
       <c r="O4" s="11"/>
       <c r="P4" s="11"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="11"/>
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
@@ -11251,7 +11382,7 @@
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="11"/>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
@@ -11267,7 +11398,7 @@
       <c r="O6" s="11"/>
       <c r="P6" s="11"/>
     </row>
-    <row r="7" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="11"/>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -11285,27 +11416,27 @@
       <c r="O7" s="12"/>
       <c r="P7" s="12"/>
     </row>
-    <row r="8" spans="1:16" ht="18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="69" t="s">
+      <c r="D8" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69"/>
-      <c r="J8" s="69"/>
-      <c r="K8" s="69"/>
-      <c r="L8" s="69"/>
-      <c r="M8" s="69"/>
-      <c r="N8" s="69"/>
-      <c r="O8" s="69"/>
-      <c r="P8" s="69"/>
-    </row>
-    <row r="9" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="E8" s="70"/>
+      <c r="F8" s="70"/>
+      <c r="G8" s="70"/>
+      <c r="H8" s="70"/>
+      <c r="I8" s="70"/>
+      <c r="J8" s="70"/>
+      <c r="K8" s="70"/>
+      <c r="L8" s="70"/>
+      <c r="M8" s="70"/>
+      <c r="N8" s="70"/>
+      <c r="O8" s="70"/>
+      <c r="P8" s="70"/>
+    </row>
+    <row r="9" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="11"/>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -11323,7 +11454,7 @@
       <c r="O9" s="12"/>
       <c r="P9" s="12"/>
     </row>
-    <row r="10" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11"/>
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
@@ -11339,7 +11470,7 @@
       <c r="O10" s="11"/>
       <c r="P10" s="11"/>
     </row>
-    <row r="11" spans="1:16" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>
       <c r="B11" s="14"/>
       <c r="C11" s="14" t="s">
@@ -11385,7 +11516,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="18"/>
       <c r="B12" s="19"/>
       <c r="C12" s="19" t="s">
@@ -11431,7 +11562,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="23" t="s">
         <v>71</v>
       </c>
@@ -11455,7 +11586,7 @@
       <c r="O13" s="27"/>
       <c r="P13" s="28"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="29">
         <v>1</v>
       </c>
@@ -11479,7 +11610,7 @@
       <c r="O14" s="33"/>
       <c r="P14" s="34"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <f>A14+1</f>
         <v>2</v>
@@ -11504,7 +11635,7 @@
       <c r="O15" s="41"/>
       <c r="P15" s="42"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <f t="shared" ref="A16:A30" si="0">A15+1</f>
         <v>3</v>
@@ -11529,7 +11660,7 @@
       <c r="O16" s="41"/>
       <c r="P16" s="42"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -11552,7 +11683,7 @@
       <c r="O17" s="41"/>
       <c r="P17" s="42"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" s="37">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -11575,7 +11706,7 @@
       <c r="O18" s="41"/>
       <c r="P18" s="42"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -11596,7 +11727,7 @@
       <c r="O19" s="41"/>
       <c r="P19" s="42"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -11617,7 +11748,7 @@
       <c r="O20" s="41"/>
       <c r="P20" s="42"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -11638,7 +11769,7 @@
       <c r="O21" s="41"/>
       <c r="P21" s="42"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -11659,7 +11790,7 @@
       <c r="O22" s="41"/>
       <c r="P22" s="42"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -11680,7 +11811,7 @@
       <c r="O23" s="41"/>
       <c r="P23" s="42"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" s="37">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -11701,7 +11832,7 @@
       <c r="O24" s="41"/>
       <c r="P24" s="42"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -11722,7 +11853,7 @@
       <c r="O25" s="41"/>
       <c r="P25" s="42"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" s="37">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -11743,7 +11874,7 @@
       <c r="O26" s="41"/>
       <c r="P26" s="42"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -11768,7 +11899,7 @@
       <c r="O27" s="41"/>
       <c r="P27" s="42"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" s="37">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -11793,7 +11924,7 @@
       <c r="O28" s="41"/>
       <c r="P28" s="42"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -11818,7 +11949,7 @@
       <c r="O29" s="41"/>
       <c r="P29" s="42"/>
     </row>
-    <row r="30" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="43">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -11843,7 +11974,7 @@
       <c r="O30" s="47"/>
       <c r="P30" s="48"/>
     </row>
-    <row r="31" spans="1:16" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:16" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A31" s="11"/>
       <c r="C31" s="49"/>
       <c r="D31" s="11"/>
@@ -11860,7 +11991,7 @@
       <c r="O31" s="11"/>
       <c r="P31" s="11"/>
     </row>
-    <row r="32" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="11"/>
       <c r="C32" s="49"/>
       <c r="D32" s="11"/>
@@ -11877,7 +12008,7 @@
       <c r="O32" s="11"/>
       <c r="P32" s="11"/>
     </row>
-    <row r="33" spans="1:16" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:16" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A33" s="50"/>
       <c r="B33" s="51" t="s">
         <v>79</v>
@@ -11903,7 +12034,7 @@
       <c r="O33" s="54"/>
       <c r="P33" s="55"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" s="37"/>
       <c r="B34" s="38" t="s">
         <v>83</v>
@@ -11927,7 +12058,7 @@
       </c>
       <c r="P34" s="42"/>
     </row>
-    <row r="35" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="43"/>
       <c r="B35" s="44" t="s">
         <v>86</v>
@@ -11947,7 +12078,7 @@
       <c r="O35" s="47"/>
       <c r="P35" s="48"/>
     </row>
-    <row r="36" spans="1:16" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:16" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A36" s="11"/>
       <c r="D36" s="11"/>
       <c r="E36" s="11"/>
@@ -11963,7 +12094,7 @@
       <c r="O36" s="11"/>
       <c r="P36" s="11"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" s="11"/>
       <c r="D37" s="11"/>
       <c r="E37" s="11"/>
@@ -11979,7 +12110,7 @@
       <c r="O37" s="11"/>
       <c r="P37" s="11"/>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" s="11"/>
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
@@ -11995,7 +12126,7 @@
       <c r="O38" s="11"/>
       <c r="P38" s="11"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" s="11"/>
       <c r="B39" s="57" t="s">
         <v>87</v>
@@ -12014,7 +12145,7 @@
       <c r="O39" s="11"/>
       <c r="P39" s="11"/>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" s="11"/>
       <c r="D40" s="11"/>
       <c r="E40" s="11"/>
@@ -12032,7 +12163,7 @@
       <c r="O40" s="11"/>
       <c r="P40" s="11"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" s="11"/>
       <c r="B41" s="57"/>
       <c r="D41" s="11"/>
@@ -12049,7 +12180,7 @@
       <c r="O41" s="11"/>
       <c r="P41" s="11"/>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" s="11"/>
       <c r="D42" s="11"/>
       <c r="E42" s="11"/>
@@ -12065,7 +12196,7 @@
       <c r="O42" s="11"/>
       <c r="P42" s="11"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" s="11"/>
       <c r="D43" s="11"/>
       <c r="E43" s="11"/>
@@ -12081,7 +12212,7 @@
       <c r="O43" s="11"/>
       <c r="P43" s="11"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" s="11"/>
       <c r="D44" s="11"/>
       <c r="E44" s="11"/>
@@ -12109,18 +12240,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A7:I25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="29.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="7" spans="1:9" ht="24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B7" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
@@ -12131,7 +12262,7 @@
       </c>
       <c r="I10" s="3"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>19</v>
       </c>
@@ -12143,7 +12274,7 @@
       </c>
       <c r="I11" s="7"/>
     </row>
-    <row r="12" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="8"/>
       <c r="B12" s="9"/>
       <c r="H12" s="8" t="s">
@@ -12151,14 +12282,14 @@
       </c>
       <c r="I12" s="9"/>
     </row>
-    <row r="15" spans="1:9" ht="21" x14ac:dyDescent="0.25">
-      <c r="B15" s="64" t="s">
+    <row r="15" spans="1:9" ht="21" x14ac:dyDescent="0.4">
+      <c r="B15" s="65" t="s">
         <v>89</v>
       </c>
-      <c r="C15" s="64"/>
-      <c r="D15" s="64"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C15" s="65"/>
+      <c r="D15" s="65"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
         <v>14</v>
       </c>
@@ -12172,7 +12303,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>96</v>
       </c>
@@ -12180,32 +12311,32 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>90</v>
       </c>
@@ -12218,4 +12349,10 @@
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{defa4170-0d19-0005-0004-bc88714345d2}" enabled="1" method="Standard" siteId="{4f455e02-c0f5-4dd7-8284-c56491661975}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/ProjectManagement/Checklist.xlsx
+++ b/ProjectManagement/Checklist.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{771B8B0B-7EAA-4E8E-AF94-455804FEBA9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68133C3C-F1AB-422F-A3E8-7EA736020D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Checklist" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="164">
   <si>
     <t>Checklist</t>
   </si>
@@ -309,36 +309,6 @@
     <t>tests</t>
   </si>
   <si>
-    <t>1st Week</t>
-  </si>
-  <si>
-    <t>2nd week</t>
-  </si>
-  <si>
-    <t>3rd week</t>
-  </si>
-  <si>
-    <t>4th week</t>
-  </si>
-  <si>
-    <t>5th week</t>
-  </si>
-  <si>
-    <t>6th week</t>
-  </si>
-  <si>
-    <t>7th week</t>
-  </si>
-  <si>
-    <t>8th weeek</t>
-  </si>
-  <si>
-    <t>9th week</t>
-  </si>
-  <si>
-    <t>10 th weeek</t>
-  </si>
-  <si>
     <t>25.9.2025</t>
   </si>
   <si>
@@ -538,6 +508,24 @@
   </si>
   <si>
     <t>Professorenbesprechung- 15.12.2025</t>
+  </si>
+  <si>
+    <t>`</t>
+  </si>
+  <si>
+    <t>24.11.2025</t>
+  </si>
+  <si>
+    <t>7.12.2025</t>
+  </si>
+  <si>
+    <t>01.12.2025</t>
+  </si>
+  <si>
+    <t>14.12.2025</t>
+  </si>
+  <si>
+    <t>21.12.2025</t>
   </si>
 </sst>
 </file>
@@ -1351,24 +1339,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
@@ -1397,6 +1367,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2932,55 +2920,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>5862</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>58617</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>745951</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>104336</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="25" name="Rectangle 24">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC1A3FB7-5964-42B1-BA55-F2B4F07C6BAB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="11519682" y="3807657"/>
-          <a:ext cx="740089" cy="45719"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="008000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="17"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-          </a:solidFill>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>298944</xdr:colOff>
       <xdr:row>32</xdr:row>
@@ -3014,6 +2953,349 @@
           <a:avLst>
             <a:gd name="adj" fmla="val 50000"/>
           </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="008000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="17"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>5862</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>58617</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>745951</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>104336</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="35" name="Rectangle 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BC788C1-4FB7-42A6-8622-9BE4919A804D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="11519682" y="3807657"/>
+          <a:ext cx="740089" cy="45719"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="008000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="17"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>5862</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>58617</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>745951</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>104336</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="36" name="Rectangle 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DEE6024D-8351-4937-A5C1-EF44533331CE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="12312162" y="3990537"/>
+          <a:ext cx="740089" cy="45719"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="008000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="17"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>5862</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>58617</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>745951</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>104336</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="37" name="Rectangle 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EAB9B946-043F-47BA-8B39-E99219A76462}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="13104642" y="4173417"/>
+          <a:ext cx="740089" cy="45719"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="008000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="17"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>5862</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>58617</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>745951</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>104336</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="38" name="Rectangle 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99C7855B-BB41-4E4B-A06E-2513BD2D63DF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="14689602" y="4722057"/>
+          <a:ext cx="740089" cy="45719"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="008000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="17"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>5862</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>58617</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>745951</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>104336</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="39" name="Rectangle 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A25398F-FC21-46F3-9453-E817EA097DD3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="13897122" y="4539177"/>
+          <a:ext cx="740089" cy="45719"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="008000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="17"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>5862</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>58617</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>745951</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>104336</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="40" name="Rectangle 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41BEDE30-C3DB-48C5-940F-953FED519DA1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="14689602" y="4904937"/>
+          <a:ext cx="740089" cy="45719"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="008000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="17"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>5862</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>58617</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>745951</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>104336</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="41" name="Rectangle 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44E7BD70-5B2F-4D27-B8B8-79015288E8D3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="13104642" y="4356297"/>
+          <a:ext cx="740089" cy="45719"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
           <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="008000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="17"/>
@@ -4643,6 +4925,300 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>5862</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>58617</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>745951</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>104336</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectangle 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F53521E-9B23-4DDB-9AEF-5614DACB463C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="11519682" y="3807657"/>
+          <a:ext cx="740089" cy="45719"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="008000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="17"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>5862</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>58617</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>745951</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>104336</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Rectangle 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF904BA2-04D3-4FE8-B8CF-66F508ACD0EA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="11519682" y="3807657"/>
+          <a:ext cx="740089" cy="45719"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="008000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="17"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>5862</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>58617</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>745951</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>104336</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Rectangle 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7A56443-223D-4E27-A85B-9BAAA787B6FC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="11519682" y="3807657"/>
+          <a:ext cx="740089" cy="45719"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="008000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="17"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>5862</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>58617</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>745951</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>104336</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="Rectangle 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C535A4B-A0E4-4C3D-A859-1CE26AABCD4A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="13897122" y="4356297"/>
+          <a:ext cx="740089" cy="45719"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="008000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="17"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>5862</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>58617</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>745951</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>104336</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="Rectangle 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13412D7B-DE19-4559-BEBC-BFCE59B67956}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="13897122" y="4356297"/>
+          <a:ext cx="740089" cy="45719"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="008000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="17"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>5862</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>58617</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>745951</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>104336</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="Rectangle 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{586477E3-5420-4F43-8B6A-8D15A520A88E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="13897122" y="4356297"/>
+          <a:ext cx="740089" cy="45719"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="008000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="17"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -5071,11 +5647,12 @@
   <cols>
     <col min="1" max="1" width="15.77734375" customWidth="1"/>
     <col min="2" max="2" width="55" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B1" s="1" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
@@ -5084,7 +5661,7 @@
         <v>16</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="2" t="s">
@@ -5096,7 +5673,7 @@
       <c r="A5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="65">
+      <c r="B5" s="59">
         <v>7026787</v>
       </c>
       <c r="H5" s="5" t="s">
@@ -5113,11 +5690,11 @@
       <c r="I6" s="9"/>
     </row>
     <row r="9" spans="1:9" ht="21" x14ac:dyDescent="0.4">
-      <c r="B9" s="59" t="s">
+      <c r="B9" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="59"/>
-      <c r="D9" s="59"/>
+      <c r="C9" s="69"/>
+      <c r="D9" s="69"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
@@ -5139,12 +5716,12 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="21" x14ac:dyDescent="0.4">
-      <c r="A14" s="59" t="s">
+      <c r="A14" s="69" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="59"/>
-      <c r="C14" s="59"/>
-      <c r="D14" s="59"/>
+      <c r="B14" s="69"/>
+      <c r="C14" s="69"/>
+      <c r="D14" s="69"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15">
@@ -5153,11 +5730,9 @@
       <c r="B15" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="60" t="s">
+      <c r="C15" s="70"/>
+      <c r="D15" s="58" t="s">
         <v>91</v>
-      </c>
-      <c r="D15" s="58" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -5168,9 +5743,9 @@
       <c r="B16" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="C16" s="60"/>
+      <c r="C16" s="70"/>
       <c r="D16" s="58" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -5181,9 +5756,9 @@
       <c r="B17" s="55" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="60"/>
+      <c r="C17" s="70"/>
       <c r="D17" s="58" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -5194,9 +5769,9 @@
       <c r="B18" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="60"/>
+      <c r="C18" s="70"/>
       <c r="D18" s="58" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -5207,9 +5782,9 @@
       <c r="B19" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="60"/>
+      <c r="C19" s="70"/>
       <c r="D19" s="58" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -5220,9 +5795,9 @@
       <c r="B20" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="60"/>
+      <c r="C20" s="70"/>
       <c r="D20" s="58" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -5233,9 +5808,9 @@
       <c r="B21" s="55" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="60"/>
+      <c r="C21" s="70"/>
       <c r="D21" s="58" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -5246,9 +5821,9 @@
       <c r="B22" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="60"/>
+      <c r="C22" s="70"/>
       <c r="D22" s="58" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -5259,9 +5834,9 @@
       <c r="B23" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="60"/>
+      <c r="C23" s="70"/>
       <c r="D23" s="58" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -5272,9 +5847,9 @@
       <c r="B24" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="C24" s="60"/>
+      <c r="C24" s="70"/>
       <c r="D24" s="58" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -5285,9 +5860,9 @@
       <c r="B25" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="C25" s="60"/>
+      <c r="C25" s="70"/>
       <c r="D25" s="58" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -5298,11 +5873,9 @@
       <c r="B26" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="61" t="s">
-        <v>92</v>
-      </c>
+      <c r="C26" s="71"/>
       <c r="D26" s="57" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -5313,9 +5886,9 @@
       <c r="B27" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="61"/>
+      <c r="C27" s="71"/>
       <c r="D27" s="57" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -5326,9 +5899,9 @@
       <c r="B28" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="61"/>
+      <c r="C28" s="71"/>
       <c r="D28" s="57" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -5339,9 +5912,9 @@
       <c r="B29" t="s">
         <v>65</v>
       </c>
-      <c r="C29" s="61"/>
+      <c r="C29" s="71"/>
       <c r="D29" s="57" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -5352,9 +5925,9 @@
       <c r="B30" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="61"/>
+      <c r="C30" s="71"/>
       <c r="D30" s="57" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -5365,9 +5938,9 @@
       <c r="B31" t="s">
         <v>66</v>
       </c>
-      <c r="C31" s="61"/>
+      <c r="C31" s="71"/>
       <c r="D31" s="57" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -5378,9 +5951,9 @@
       <c r="B32" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="61"/>
+      <c r="C32" s="71"/>
       <c r="D32" s="57" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -5391,9 +5964,9 @@
       <c r="B33" t="s">
         <v>23</v>
       </c>
-      <c r="C33" s="61"/>
+      <c r="C33" s="71"/>
       <c r="D33" s="57" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -5404,11 +5977,9 @@
       <c r="B34" s="55" t="s">
         <v>24</v>
       </c>
-      <c r="C34" s="60" t="s">
-        <v>93</v>
-      </c>
+      <c r="C34" s="70"/>
       <c r="D34" s="57" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -5419,9 +5990,9 @@
       <c r="B35" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="C35" s="60"/>
+      <c r="C35" s="70"/>
       <c r="D35" s="57" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -5432,9 +6003,9 @@
       <c r="B36" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="C36" s="60"/>
+      <c r="C36" s="70"/>
       <c r="D36" s="57" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -5445,18 +6016,18 @@
       <c r="B37" s="55" t="s">
         <v>68</v>
       </c>
-      <c r="C37" s="60"/>
+      <c r="C37" s="70"/>
       <c r="D37" s="57" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="21" x14ac:dyDescent="0.4">
-      <c r="A38" s="59" t="s">
+      <c r="A38" s="69" t="s">
         <v>34</v>
       </c>
-      <c r="B38" s="59"/>
-      <c r="C38" s="59"/>
-      <c r="D38" s="59"/>
+      <c r="B38" s="69"/>
+      <c r="C38" s="69"/>
+      <c r="D38" s="69"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39">
@@ -5466,11 +6037,9 @@
       <c r="B39" t="s">
         <v>26</v>
       </c>
-      <c r="C39" s="61" t="s">
-        <v>94</v>
-      </c>
+      <c r="C39" s="71"/>
       <c r="D39" s="57" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -5481,9 +6050,9 @@
       <c r="B40" t="s">
         <v>28</v>
       </c>
-      <c r="C40" s="61"/>
+      <c r="C40" s="71"/>
       <c r="D40" s="57" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
@@ -5494,9 +6063,9 @@
       <c r="B41" t="s">
         <v>29</v>
       </c>
-      <c r="C41" s="61"/>
+      <c r="C41" s="71"/>
       <c r="D41" s="57" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
@@ -5507,9 +6076,9 @@
       <c r="B42" t="s">
         <v>38</v>
       </c>
-      <c r="C42" s="61"/>
+      <c r="C42" s="71"/>
       <c r="D42" s="57" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
@@ -5520,9 +6089,9 @@
       <c r="B43" t="s">
         <v>40</v>
       </c>
-      <c r="C43" s="61"/>
+      <c r="C43" s="71"/>
       <c r="D43" s="57" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
@@ -5533,9 +6102,9 @@
       <c r="B44" t="s">
         <v>85</v>
       </c>
-      <c r="C44" s="61"/>
+      <c r="C44" s="71"/>
       <c r="D44" s="57" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
@@ -5546,9 +6115,9 @@
       <c r="B45" t="s">
         <v>84</v>
       </c>
-      <c r="C45" s="61"/>
+      <c r="C45" s="71"/>
       <c r="D45" s="57" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -5559,11 +6128,9 @@
       <c r="B46" s="55" t="s">
         <v>70</v>
       </c>
-      <c r="C46" s="62" t="s">
-        <v>95</v>
-      </c>
+      <c r="C46" s="72"/>
       <c r="D46" s="57" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
@@ -5574,9 +6141,9 @@
       <c r="B47" s="55" t="s">
         <v>71</v>
       </c>
-      <c r="C47" s="62"/>
+      <c r="C47" s="72"/>
       <c r="D47" s="57" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
@@ -5587,9 +6154,9 @@
       <c r="B48" s="55" t="s">
         <v>72</v>
       </c>
-      <c r="C48" s="62"/>
+      <c r="C48" s="72"/>
       <c r="D48" s="57" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
@@ -5600,9 +6167,9 @@
       <c r="B49" s="55" t="s">
         <v>73</v>
       </c>
-      <c r="C49" s="62"/>
+      <c r="C49" s="72"/>
       <c r="D49" s="57" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
@@ -5613,11 +6180,9 @@
       <c r="B50" t="s">
         <v>74</v>
       </c>
-      <c r="C50" s="63" t="s">
-        <v>96</v>
-      </c>
+      <c r="C50" s="73"/>
       <c r="D50" s="57" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
@@ -5628,9 +6193,9 @@
       <c r="B51" t="s">
         <v>75</v>
       </c>
-      <c r="C51" s="63"/>
+      <c r="C51" s="73"/>
       <c r="D51" s="57" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
@@ -5641,9 +6206,9 @@
       <c r="B52" t="s">
         <v>86</v>
       </c>
-      <c r="C52" s="63"/>
+      <c r="C52" s="73"/>
       <c r="D52" s="57" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
@@ -5655,11 +6220,9 @@
         <f>[1]Report!$A$207</f>
         <v>Homework "Literature"</v>
       </c>
-      <c r="C53" s="62" t="s">
-        <v>97</v>
-      </c>
+      <c r="C53" s="72"/>
       <c r="D53" s="57" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
@@ -5670,9 +6233,9 @@
       <c r="B54" s="55" t="s">
         <v>76</v>
       </c>
-      <c r="C54" s="62"/>
+      <c r="C54" s="72"/>
       <c r="D54" s="57" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
@@ -5683,9 +6246,9 @@
       <c r="B55" s="55" t="s">
         <v>80</v>
       </c>
-      <c r="C55" s="62"/>
+      <c r="C55" s="72"/>
       <c r="D55" s="57" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
@@ -5696,11 +6259,9 @@
       <c r="B56" t="s">
         <v>79</v>
       </c>
-      <c r="C56" s="63" t="s">
-        <v>98</v>
-      </c>
+      <c r="C56" s="73"/>
       <c r="D56" s="57" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
@@ -5711,9 +6272,9 @@
       <c r="B57" t="s">
         <v>81</v>
       </c>
-      <c r="C57" s="63"/>
+      <c r="C57" s="73"/>
       <c r="D57" s="57" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
@@ -5724,9 +6285,9 @@
       <c r="B58" t="s">
         <v>77</v>
       </c>
-      <c r="C58" s="63"/>
+      <c r="C58" s="73"/>
       <c r="D58" s="57" t="s">
-        <v>110</v>
+        <v>159</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
@@ -5737,9 +6298,9 @@
       <c r="B59" t="s">
         <v>78</v>
       </c>
-      <c r="C59" s="63"/>
+      <c r="C59" s="73"/>
       <c r="D59" s="57" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
@@ -5750,8 +6311,9 @@
       <c r="B60" s="55" t="s">
         <v>82</v>
       </c>
-      <c r="C60" s="62" t="s">
-        <v>99</v>
+      <c r="C60" s="72"/>
+      <c r="D60" s="57" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
@@ -5762,7 +6324,10 @@
       <c r="B61" s="55" t="s">
         <v>83</v>
       </c>
-      <c r="C61" s="62"/>
+      <c r="C61" s="72"/>
+      <c r="D61" s="57" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62">
@@ -5772,7 +6337,10 @@
       <c r="B62" s="55" t="s">
         <v>88</v>
       </c>
-      <c r="C62" s="62"/>
+      <c r="C62" s="72"/>
+      <c r="D62" s="57" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63">
@@ -5782,8 +6350,9 @@
       <c r="B63" t="s">
         <v>87</v>
       </c>
-      <c r="C63" s="63" t="s">
-        <v>100</v>
+      <c r="C63" s="73"/>
+      <c r="D63" s="57" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
@@ -5794,7 +6363,10 @@
       <c r="B64" s="56" t="s">
         <v>89</v>
       </c>
-      <c r="C64" s="63"/>
+      <c r="C64" s="73"/>
+      <c r="D64" s="57" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65">
@@ -5804,15 +6376,18 @@
       <c r="B65" s="56" t="s">
         <v>90</v>
       </c>
-      <c r="C65" s="63"/>
+      <c r="C65" s="73"/>
+      <c r="D65" s="57" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="66" spans="1:4" ht="21" x14ac:dyDescent="0.4">
-      <c r="A66" s="59" t="s">
+      <c r="A66" s="69" t="s">
         <v>35</v>
       </c>
-      <c r="B66" s="59"/>
-      <c r="C66" s="59"/>
-      <c r="D66" s="59"/>
+      <c r="B66" s="69"/>
+      <c r="C66" s="69"/>
+      <c r="D66" s="69"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67">
@@ -6061,21 +6636,21 @@
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="64" t="s">
-        <v>161</v>
-      </c>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64"/>
-      <c r="J8" s="64"/>
-      <c r="K8" s="64"/>
-      <c r="L8" s="64"/>
-      <c r="M8" s="64"/>
-      <c r="N8" s="64"/>
-      <c r="O8" s="64"/>
-      <c r="P8" s="64"/>
+      <c r="D8" s="74" t="s">
+        <v>151</v>
+      </c>
+      <c r="E8" s="74"/>
+      <c r="F8" s="74"/>
+      <c r="G8" s="74"/>
+      <c r="H8" s="74"/>
+      <c r="I8" s="74"/>
+      <c r="J8" s="74"/>
+      <c r="K8" s="74"/>
+      <c r="L8" s="74"/>
+      <c r="M8" s="74"/>
+      <c r="N8" s="74"/>
+      <c r="O8" s="74"/>
+      <c r="P8" s="74"/>
     </row>
     <row r="9" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="11"/>
@@ -6113,11 +6688,11 @@
     </row>
     <row r="11" spans="1:16" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>
-      <c r="B11" s="67"/>
-      <c r="C11" s="74" t="s">
-        <v>162</v>
-      </c>
-      <c r="D11" s="70">
+      <c r="B11" s="61"/>
+      <c r="C11" s="68" t="s">
+        <v>152</v>
+      </c>
+      <c r="D11" s="64">
         <v>40</v>
       </c>
       <c r="E11" s="15">
@@ -6159,11 +6734,11 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="16"/>
-      <c r="B12" s="68"/>
-      <c r="C12" s="74" t="s">
-        <v>163</v>
-      </c>
-      <c r="D12" s="71">
+      <c r="B12" s="62"/>
+      <c r="C12" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="D12" s="65">
         <v>1</v>
       </c>
       <c r="E12" s="19">
@@ -6207,13 +6782,13 @@
       <c r="A13" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="69" t="s">
-        <v>164</v>
-      </c>
-      <c r="C13" s="74" t="s">
+      <c r="B13" s="63" t="s">
+        <v>154</v>
+      </c>
+      <c r="C13" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="72"/>
+      <c r="D13" s="66"/>
       <c r="E13" s="25"/>
       <c r="F13" s="25"/>
       <c r="G13" s="25"/>
@@ -6232,9 +6807,9 @@
         <v>1</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>145</v>
-      </c>
-      <c r="C14" s="73">
+        <v>135</v>
+      </c>
+      <c r="C14" s="67">
         <v>1</v>
       </c>
       <c r="D14" s="30"/>
@@ -6257,7 +6832,7 @@
         <v>2</v>
       </c>
       <c r="B15" s="34" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C15" s="35">
         <v>1</v>
@@ -6282,7 +6857,7 @@
         <v>3</v>
       </c>
       <c r="B16" s="34" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="C16" s="35">
         <v>2</v>
@@ -6307,7 +6882,7 @@
         <v>4</v>
       </c>
       <c r="B17" s="34" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C17" s="35">
         <v>3</v>
@@ -6332,7 +6907,7 @@
         <v>5</v>
       </c>
       <c r="B18" s="34" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C18" s="35">
         <v>4</v>
@@ -6357,7 +6932,7 @@
         <v>6</v>
       </c>
       <c r="B19" s="34" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="C19" s="35">
         <v>5</v>
@@ -6382,7 +6957,7 @@
         <v>7</v>
       </c>
       <c r="B20" s="34" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="C20" s="35">
         <v>5</v>
@@ -6407,7 +6982,7 @@
         <v>8</v>
       </c>
       <c r="B21" s="34" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="C21" s="35">
         <v>6</v>
@@ -6432,7 +7007,7 @@
         <v>9</v>
       </c>
       <c r="B22" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="C22" s="35">
         <v>7</v>
@@ -6457,7 +7032,7 @@
         <v>10</v>
       </c>
       <c r="B23" s="34" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="C23" s="35">
         <v>8</v>
@@ -6482,7 +7057,7 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="C24" s="35">
         <v>9</v>
@@ -6507,7 +7082,7 @@
         <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C25" s="35">
         <v>10</v>
@@ -6532,7 +7107,7 @@
         <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="C26" s="35">
         <v>11</v>
@@ -6547,7 +7122,9 @@
       <c r="K26" s="37"/>
       <c r="L26" s="37"/>
       <c r="M26" s="37"/>
-      <c r="N26" s="37"/>
+      <c r="N26" s="37" t="s">
+        <v>158</v>
+      </c>
       <c r="O26" s="37"/>
       <c r="P26" s="38"/>
     </row>
@@ -6557,7 +7134,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="C27" s="35">
         <v>12</v>
@@ -6582,7 +7159,7 @@
         <v>15</v>
       </c>
       <c r="B28" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="C28" s="35">
         <v>13</v>
@@ -6652,7 +7229,7 @@
       <c r="N31" s="49"/>
       <c r="O31" s="49"/>
       <c r="P31" s="11" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
@@ -6660,7 +7237,7 @@
       <c r="B32" s="34"/>
       <c r="C32" s="35"/>
       <c r="D32" s="36" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="E32" s="37"/>
       <c r="F32" s="37"/>
@@ -6674,7 +7251,7 @@
       <c r="N32" s="37"/>
       <c r="O32" s="51"/>
       <c r="P32" s="36" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="53.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -6682,38 +7259,38 @@
       <c r="B33" s="40"/>
       <c r="C33" s="41"/>
       <c r="D33" s="42"/>
-      <c r="E33" s="66" t="s">
-        <v>132</v>
-      </c>
-      <c r="F33" s="66" t="s">
-        <v>133</v>
-      </c>
-      <c r="G33" s="66" t="s">
+      <c r="E33" s="60" t="s">
+        <v>122</v>
+      </c>
+      <c r="F33" s="60" t="s">
+        <v>123</v>
+      </c>
+      <c r="G33" s="60" t="s">
+        <v>124</v>
+      </c>
+      <c r="H33" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="I33" s="60" t="s">
         <v>134</v>
       </c>
-      <c r="H33" s="66" t="s">
-        <v>135</v>
-      </c>
-      <c r="I33" s="66" t="s">
-        <v>144</v>
-      </c>
-      <c r="J33" s="66" t="s">
-        <v>165</v>
-      </c>
-      <c r="K33" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="L33" s="66" t="s">
-        <v>140</v>
-      </c>
-      <c r="M33" s="66" t="s">
-        <v>166</v>
-      </c>
-      <c r="N33" s="66" t="s">
-        <v>139</v>
-      </c>
-      <c r="O33" s="66" t="s">
-        <v>167</v>
+      <c r="J33" s="60" t="s">
+        <v>155</v>
+      </c>
+      <c r="K33" s="60" t="s">
+        <v>131</v>
+      </c>
+      <c r="L33" s="60" t="s">
+        <v>130</v>
+      </c>
+      <c r="M33" s="60" t="s">
+        <v>156</v>
+      </c>
+      <c r="N33" s="60" t="s">
+        <v>129</v>
+      </c>
+      <c r="O33" s="60" t="s">
+        <v>157</v>
       </c>
       <c r="P33" s="43"/>
     </row>
@@ -7002,21 +7579,21 @@
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="64" t="s">
-        <v>111</v>
-      </c>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64"/>
-      <c r="J8" s="64"/>
-      <c r="K8" s="64"/>
-      <c r="L8" s="64"/>
-      <c r="M8" s="64"/>
-      <c r="N8" s="64"/>
-      <c r="O8" s="64"/>
-      <c r="P8" s="64"/>
+      <c r="D8" s="74" t="s">
+        <v>101</v>
+      </c>
+      <c r="E8" s="74"/>
+      <c r="F8" s="74"/>
+      <c r="G8" s="74"/>
+      <c r="H8" s="74"/>
+      <c r="I8" s="74"/>
+      <c r="J8" s="74"/>
+      <c r="K8" s="74"/>
+      <c r="L8" s="74"/>
+      <c r="M8" s="74"/>
+      <c r="N8" s="74"/>
+      <c r="O8" s="74"/>
+      <c r="P8" s="74"/>
     </row>
     <row r="9" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="11"/>
@@ -7173,7 +7750,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C14" s="29">
         <v>1</v>
@@ -7198,7 +7775,7 @@
         <v>2</v>
       </c>
       <c r="B15" s="34" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="C15" s="35">
         <v>1</v>
@@ -7223,7 +7800,7 @@
         <v>3</v>
       </c>
       <c r="B16" s="34" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="C16" s="35">
         <v>2</v>
@@ -7248,7 +7825,7 @@
         <v>4</v>
       </c>
       <c r="B17" s="34" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C17" s="35">
         <v>3</v>
@@ -7273,7 +7850,7 @@
         <v>5</v>
       </c>
       <c r="B18" s="34" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="C18" s="35">
         <v>4</v>
@@ -7298,7 +7875,7 @@
         <v>6</v>
       </c>
       <c r="B19" s="34" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C19" s="35">
         <v>5</v>
@@ -7323,7 +7900,7 @@
         <v>7</v>
       </c>
       <c r="B20" s="34" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="C20" s="35">
         <v>5</v>
@@ -7348,7 +7925,7 @@
         <v>8</v>
       </c>
       <c r="B21" s="34" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C21" s="35">
         <v>6</v>
@@ -7373,7 +7950,7 @@
         <v>9</v>
       </c>
       <c r="B22" s="34" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="C22" s="35">
         <v>7</v>
@@ -7398,7 +7975,7 @@
         <v>10</v>
       </c>
       <c r="B23" s="34" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C23" s="35">
         <v>8</v>
@@ -7423,7 +8000,7 @@
         <v>11</v>
       </c>
       <c r="B24" s="34" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="C24" s="35">
         <v>9</v>
@@ -7448,7 +8025,7 @@
         <v>12</v>
       </c>
       <c r="B25" s="34" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="C25" s="35">
         <v>10</v>
@@ -7473,7 +8050,7 @@
         <v>13</v>
       </c>
       <c r="B26" s="34" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="C26" s="35">
         <v>11</v>
@@ -7488,7 +8065,9 @@
       <c r="K26" s="37"/>
       <c r="L26" s="37"/>
       <c r="M26" s="37"/>
-      <c r="N26" s="37"/>
+      <c r="N26" s="37" t="s">
+        <v>158</v>
+      </c>
       <c r="O26" s="37"/>
       <c r="P26" s="38"/>
     </row>
@@ -7498,7 +8077,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="34" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="C27" s="35">
         <v>12</v>
@@ -7523,7 +8102,7 @@
         <v>15</v>
       </c>
       <c r="B28" s="34" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C28" s="35">
         <v>13</v>
@@ -7595,7 +8174,7 @@
       <c r="N31" s="49"/>
       <c r="O31" s="49"/>
       <c r="P31" s="50" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
@@ -7605,7 +8184,7 @@
       </c>
       <c r="C32" s="35"/>
       <c r="D32" s="36" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="E32" s="37"/>
       <c r="F32" s="37"/>
@@ -7619,7 +8198,7 @@
       <c r="N32" s="37"/>
       <c r="O32" s="51"/>
       <c r="P32" s="36" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
@@ -7629,38 +8208,38 @@
       </c>
       <c r="C33" s="41"/>
       <c r="D33" s="42"/>
-      <c r="E33" s="66" t="s">
+      <c r="E33" s="60" t="s">
+        <v>122</v>
+      </c>
+      <c r="F33" s="60" t="s">
+        <v>123</v>
+      </c>
+      <c r="G33" s="60" t="s">
+        <v>124</v>
+      </c>
+      <c r="H33" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="I33" s="60" t="s">
+        <v>134</v>
+      </c>
+      <c r="J33" s="60" t="s">
         <v>132</v>
       </c>
-      <c r="F33" s="66" t="s">
-        <v>133</v>
-      </c>
-      <c r="G33" s="66" t="s">
-        <v>134</v>
-      </c>
-      <c r="H33" s="66" t="s">
-        <v>135</v>
-      </c>
-      <c r="I33" s="66" t="s">
-        <v>144</v>
-      </c>
-      <c r="J33" s="66" t="s">
-        <v>142</v>
-      </c>
-      <c r="K33" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="L33" s="66" t="s">
-        <v>140</v>
-      </c>
-      <c r="M33" s="66" t="s">
-        <v>138</v>
-      </c>
-      <c r="N33" s="66" t="s">
-        <v>139</v>
-      </c>
-      <c r="O33" s="66" t="s">
-        <v>137</v>
+      <c r="K33" s="60" t="s">
+        <v>131</v>
+      </c>
+      <c r="L33" s="60" t="s">
+        <v>130</v>
+      </c>
+      <c r="M33" s="60" t="s">
+        <v>128</v>
+      </c>
+      <c r="N33" s="60" t="s">
+        <v>129</v>
+      </c>
+      <c r="O33" s="60" t="s">
+        <v>127</v>
       </c>
       <c r="P33" s="43"/>
     </row>
@@ -7831,16 +8410,16 @@
   <sheetData>
     <row r="7" spans="1:9" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B7" s="1" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="2" t="s">
@@ -7869,11 +8448,11 @@
       <c r="I12" s="9"/>
     </row>
     <row r="15" spans="1:9" ht="21" x14ac:dyDescent="0.4">
-      <c r="B15" s="59" t="s">
+      <c r="B15" s="69" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="59"/>
-      <c r="D15" s="59"/>
+      <c r="C15" s="69"/>
+      <c r="D15" s="69"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
